--- a/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
+++ b/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
@@ -469,7 +469,7 @@
     <t xml:space="preserve">Per job matrix</t>
   </si>
   <si>
-    <t xml:space="preserve">GAP: scheduled trigger should change once per real run</t>
+    <t xml:space="preserve">DELTA: scheduler start and terminal audit change once per real run</t>
   </si>
   <si>
     <t xml:space="preserve">Every runState/history must change</t>
@@ -481,13 +481,13 @@
     <t xml:space="preserve">NOT RUN as cross-surface pack</t>
   </si>
   <si>
-    <t xml:space="preserve">Scheduler and fixture tests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Do not hide missing Monitoring delta behind domain PASS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Universal job-run telemetry is not currently wired</t>
+    <t xml:space="preserve">Lifecycle registry/projection tests; 4 real zero-work scheduler runs observed 2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capture browser delta and independent domain oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universal job-run telemetry is wired; manual all-job cross-surface pack remains</t>
   </si>
   <si>
     <t xml:space="preserve">P0 94</t>
@@ -499,7 +499,7 @@
     <t xml:space="preserve">Save and revert one parameter section</t>
   </si>
   <si>
-    <t xml:space="preserve">GAP Jobs config delta; recompute/outbox should transition</t>
+    <t xml:space="preserve">DELTA Jobs config once per persisted version; recompute/outbox should transition</t>
   </si>
   <si>
     <t xml:space="preserve">Section-dependent</t>
@@ -511,13 +511,13 @@
     <t xml:space="preserve">New config version and admin notification</t>
   </si>
   <si>
-    <t xml:space="preserve">Params HTTP E2E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Record save and revert as separate deltas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">admin.params.changed is read by Monitoring but not emitted by AdminParamsService</t>
+    <t xml:space="preserve">Params exact-once service tests; Params HTTP E2E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Record save and revert as separate browser deltas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">admin.params.changed now emits on successful save/revert and not on no-op revert</t>
   </si>
   <si>
     <t xml:space="preserve">GRAPH-002</t>
@@ -658,13 +658,13 @@
     <t xml:space="preserve">Save/reopen/history/revert one safe value per section</t>
   </si>
   <si>
-    <t xml:space="preserve">Recompute/outbox transitions; GAP Jobs config telemetry</t>
+    <t xml:space="preserve">Config delta plus recompute/outbox transitions</t>
   </si>
   <si>
     <t xml:space="preserve">Exact value, new version, actor/date/summary, notification, non-destructive revert</t>
   </si>
   <si>
-    <t xml:space="preserve">AdminParamsService tests; notification HTTP E2E</t>
+    <t xml:space="preserve">AdminParamsService exact-once tests; notification HTTP E2E</t>
   </si>
   <si>
     <t xml:space="preserve">Execute for every section and restore baseline</t>
@@ -688,7 +688,7 @@
     <t xml:space="preserve">Graph summary changes after recompute</t>
   </si>
   <si>
-    <t xml:space="preserve">Matching queue; GAP config metric</t>
+    <t xml:space="preserve">Config delta and Matching queue</t>
   </si>
   <si>
     <t xml:space="preserve">User edge/score changes predicted direction</t>
@@ -736,7 +736,7 @@
     <t xml:space="preserve">Change one event absolute/boost weight</t>
   </si>
   <si>
-    <t xml:space="preserve">Matching queue from generic config save; GAP config metric</t>
+    <t xml:space="preserve">Config delta and Matching queue from generic save</t>
   </si>
   <si>
     <t xml:space="preserve">Affinity recompute is enqueued generically</t>
@@ -808,7 +808,7 @@
     <t xml:space="preserve">Change multicast threshold and revert</t>
   </si>
   <si>
-    <t xml:space="preserve">Outbox strategy/count transition; GAP config metric</t>
+    <t xml:space="preserve">Config delta plus outbox strategy/count transition</t>
   </si>
   <si>
     <t xml:space="preserve">Direct vs multicast delivery changes and restores</t>
@@ -817,7 +817,7 @@
     <t xml:space="preserve">AUTO COVERAGE; MANUAL NOT RUN</t>
   </si>
   <si>
-    <t xml:space="preserve">BackendAdminParamsRealtimeE2ETest</t>
+    <t xml:space="preserve">BackendAdminParamsRealtimeE2ETest; exact-once telemetry tests</t>
   </si>
   <si>
     <t xml:space="preserve">Repeat through Parameters UI and inspect history</t>
@@ -835,7 +835,7 @@
     <t xml:space="preserve">Change one debounce/batch/lease value safely</t>
   </si>
   <si>
-    <t xml:space="preserve">Worker behavior plus GAP config metric</t>
+    <t xml:space="preserve">Config delta plus affected worker behavior</t>
   </si>
   <si>
     <t xml:space="preserve">Affected worker cadence/batch behavior</t>
@@ -886,7 +886,7 @@
     <t xml:space="preserve">Real scheduler executes prepared random rooms</t>
   </si>
   <si>
-    <t xml:space="preserve">INDIRECT Chat/outbox; GAP scheduled trigger</t>
+    <t xml:space="preserve">DELTA scheduler/audit; INDIRECT Chat/outbox</t>
   </si>
   <si>
     <t xml:space="preserve">DELTA status/count/duration/history</t>
@@ -898,7 +898,7 @@
     <t xml:space="preserve">MANUAL FUNCTIONAL PASS; UI PARTIAL</t>
   </si>
   <si>
-    <t xml:space="preserve">Extensive fixture/self-tests</t>
+    <t xml:space="preserve">Extensive fixture/self-tests; common lifecycle tests</t>
   </si>
   <si>
     <t xml:space="preserve">Add Monitoring and screenshot evidence, not more permutations first</t>
@@ -922,7 +922,7 @@
     <t xml:space="preserve">DELTA event/member activity when invites created</t>
   </si>
   <si>
-    <t xml:space="preserve">DELTA Events/Members/outbox; GAP scheduled trigger</t>
+    <t xml:space="preserve">DELTA scheduler/audit and Events/Members/outbox</t>
   </si>
   <si>
     <t xml:space="preserve">DELTA invites/member state/bell</t>
@@ -931,7 +931,7 @@
     <t xml:space="preserve">MANUAL UI PASS</t>
   </si>
   <si>
-    <t xml:space="preserve">Fixture/service tests</t>
+    <t xml:space="preserve">Fixture/service/common lifecycle tests</t>
   </si>
   <si>
     <t xml:space="preserve">Capture Statistics and Monitoring deltas</t>
@@ -949,7 +949,7 @@
     <t xml:space="preserve">Real scheduler reviews stage transitions</t>
   </si>
   <si>
-    <t xml:space="preserve">INDIRECT domain/outbox; GAP scheduled trigger</t>
+    <t xml:space="preserve">DELTA scheduler/audit; INDIRECT domain/outbox</t>
   </si>
   <si>
     <t xml:space="preserve">DELTA stage review/advancement/score-plan/notifications</t>
@@ -973,7 +973,7 @@
     <t xml:space="preserve">Real scheduler expires counters/tickets</t>
   </si>
   <si>
-    <t xml:space="preserve">DELTA Jobs only when non-empty; GAP universal zero/failure trace</t>
+    <t xml:space="preserve">DELTA scheduler/audit for zero/success/failure; INDIRECT domain event when non-empty</t>
   </si>
   <si>
     <t xml:space="preserve">DELTA expired counters/tickets/user counters</t>
@@ -991,13 +991,13 @@
     <t xml:space="preserve">Real scheduler purges expired basket rows</t>
   </si>
   <si>
-    <t xml:space="preserve">GAP scheduled trigger</t>
+    <t xml:space="preserve">DELTA scheduler/audit</t>
   </si>
   <si>
     <t xml:space="preserve">DELTA basket resultState deleted and pending count</t>
   </si>
   <si>
-    <t xml:space="preserve">Capture expected Monitoring GAP separately</t>
+    <t xml:space="preserve">Capture Monitoring delta in browser</t>
   </si>
   <si>
     <t xml:space="preserve">JOB-OUTBOX</t>
@@ -1009,13 +1009,13 @@
     <t xml:space="preserve">Real worker processes outbox</t>
   </si>
   <si>
-    <t xml:space="preserve">DELTA pending/running/sent/failed; GAP scheduled trigger</t>
+    <t xml:space="preserve">DELTA scheduler/audit plus pending/running/sent/failed</t>
   </si>
   <si>
     <t xml:space="preserve">DELTA terminal delivery/no-op/token cleanup as configured</t>
   </si>
   <si>
-    <t xml:space="preserve">Fixture/worker tests</t>
+    <t xml:space="preserve">Fixture/worker/common lifecycle tests</t>
   </si>
   <si>
     <t xml:space="preserve">Capture queue transition before worker consumes it</t>
@@ -1036,7 +1036,7 @@
     <t xml:space="preserve">DELTA network graph summary after refresh</t>
   </si>
   <si>
-    <t xml:space="preserve">DELTA recompute queue; GAP scheduled trigger</t>
+    <t xml:space="preserve">DELTA scheduler/audit and recompute queue</t>
   </si>
   <si>
     <t xml:space="preserve">DELTA when edge inputs changed</t>
@@ -1045,7 +1045,7 @@
     <t xml:space="preserve">DELTA terminal tasks and updated affinity/discovery</t>
   </si>
   <si>
-    <t xml:space="preserve">Fixture/worker/graph tests</t>
+    <t xml:space="preserve">Fixture/worker/graph/common lifecycle tests</t>
   </si>
   <si>
     <t xml:space="preserve">Use one changed pair and cross-surface evidence</t>
@@ -1066,7 +1066,7 @@
     <t xml:space="preserve">Real scheduler dispatches due messages</t>
   </si>
   <si>
-    <t xml:space="preserve">INDIRECT Notifications/outbox; GAP scheduled trigger</t>
+    <t xml:space="preserve">DELTA scheduler/audit; INDIRECT Notifications/outbox</t>
   </si>
   <si>
     <t xml:space="preserve">DELTA task audit plus notification/email result</t>
@@ -1087,7 +1087,7 @@
     <t xml:space="preserve">INDIRECT network graph after user removal; ordinary deletion counted earlier</t>
   </si>
   <si>
-    <t xml:space="preserve">GAP scheduled trigger; X for new profile.deleted event at purge time</t>
+    <t xml:space="preserve">DELTA scheduler/audit; X for new profile.deleted event at purge time</t>
   </si>
   <si>
     <t xml:space="preserve">INDIRECT member/edge totals after removal</t>
@@ -1096,7 +1096,7 @@
     <t xml:space="preserve">DELTA removed/anonymized data and terminal purge job</t>
   </si>
   <si>
-    <t xml:space="preserve">Capture graph totals and Monitoring gap</t>
+    <t xml:space="preserve">Capture graph totals and Monitoring delta</t>
   </si>
   <si>
     <t xml:space="preserve">P0 98</t>
@@ -1328,13 +1328,13 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="23.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="51.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="63.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="56.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="73.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="58.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="67.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="54.92"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="42.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="71.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="70.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="100.63"/>

--- a/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
+++ b/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="402">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -151,33 +151,39 @@
     <t xml:space="preserve">All sections stable; refresh reloads snapshot</t>
   </si>
   <si>
+    <t xml:space="preserve">MANUAL UI PASS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DTO/service support only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proceed with the controlled causal Statistics rows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06:05 initial and 06:06 no-action refresh screenshots: all nine KPIs, five segments, graph/timeline, event type, city and topic panels rendered and visible values stayed stable; the header timestamp advanced normally. A separate 06:02/06:07 API sample later absorbed one user restored during fixture cleanup, so that delayed materialization was excluded from the refresh oracle. Mixed Hungarian/English labels are a nonblocking i18n observation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1 68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASE-MON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open All/Watch/Domains/Delivery/Workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Categories and filter counts match contract</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOT RUN</t>
   </si>
   <si>
-    <t xml:space="preserve">DTO/service support only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Record generatedAt plus every section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Refresh does not force telemetry drain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P1 68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BASE-MON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open All/Watch/Domains/Delivery/Workers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Categories and filter counts match contract</t>
-  </si>
-  <si>
     <t xml:space="preserve">Security/DTO support only</t>
   </si>
   <si>
@@ -220,7 +226,7 @@
     <t xml:space="preserve">Causal</t>
   </si>
   <si>
-    <t xml:space="preserve">Submit one controlled rating</t>
+    <t xml:space="preserve">Stage one controlled non-zero rating, press Save once, then let the frontend batch sync it</t>
   </si>
   <si>
     <t xml:space="preserve">Ratings timeline +1; Matching rates.synced rises by row count</t>
@@ -235,78 +241,81 @@
     <t xml:space="preserve">Affinity recompute may run</t>
   </si>
   <si>
-    <t xml:space="preserve">Rating stored once</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANUAL FUNCTIONAL PASS for rating API; Statistics NOT RUN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rating and graph-science tests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capture all surface deltas in one run</t>
+    <t xml:space="preserve">Slider selection only stages; Save queues once; the Met card remains and shows the score; frontend pushes at most 50 queued ratings on its 30-second cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUAL STATISTICS + BELL UI + FUNCTIONAL PASS; MONITORING/GRAPH PENDING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rating and graph-science tests; frontend stage/save/batch timing unit contract not yet isolated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualify the same causal flow in the Monitoring and Graph packs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASS / PARTIAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casey staged 4 for Nova and pressed Save once; the Met card remained and displayed 4. The delayed frontend batch reached the backend; fixture/API oracles passed exactly one stored rating, one outbox, one unread Nova bell, matching unread projection, and no Casey bell. Nova's 06:31 screenshot showed exactly one New rating item from Casey at 06:22. Statistics screenshots at 06:37/06:38 showed today's Ratings 0-&gt;1 and Matching/Rating activity 342-&gt;343, while Events/assets 1495, Communication 426 and Moderation 14 stayed stable. English notification copy on the Hungarian page is a nonblocking i18n observation. Monitoring/Graph effects remain separate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1 78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAT-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Send one ordinary chat message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Messages timeline +1; Communication +1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chat flow +1; outbox conditional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notification outbox conditional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Message and unread/read projection correct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chat/realtime E2E support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One message, one telemetry delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System chat messages are excluded from Statistics message count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1 66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAT-012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invite or join one event member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event activity delta; Activities interaction changes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Events/Members and outbox deltas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT after affinity evidence/recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto-inviter may be the trigger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member state and notification agree</t>
   </si>
   <si>
     <t xml:space="preserve">PARTIAL</t>
   </si>
   <si>
-    <t xml:space="preserve">Historical test did not qualify Statistics/Monitoring/Graph UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P1 78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STAT-011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Send one ordinary chat message</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Messages timeline +1; Communication +1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chat flow +1; outbox conditional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notification outbox conditional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Message and unread/read projection correct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chat/realtime E2E support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One message, one telemetry delta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System chat messages are excluded from Statistics message count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P1 66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STAT-012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invite or join one event member</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Event activity delta; Activities interaction changes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Events/Members and outbox deltas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INDIRECT after affinity evidence/recompute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto-inviter may be the trigger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Member state and notification agree</t>
-  </si>
-  <si>
     <t xml:space="preserve">Service tests</t>
   </si>
   <si>
@@ -904,9 +913,6 @@
     <t xml:space="preserve">Add Monitoring and screenshot evidence, not more permutations first</t>
   </si>
   <si>
-    <t xml:space="preserve">PASS / PARTIAL</t>
-  </si>
-  <si>
     <t xml:space="preserve">All core variations passed 2026-07-29; 2 events/rooms and 6/6 users passed 2026-07-31</t>
   </si>
   <si>
@@ -928,9 +934,6 @@
     <t xml:space="preserve">DELTA invites/member state/bell</t>
   </si>
   <si>
-    <t xml:space="preserve">MANUAL UI PASS</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fixture/service/common lifecycle tests</t>
   </si>
   <si>
@@ -1129,13 +1132,16 @@
     <t xml:space="preserve">Read path, rating and feedback persist once</t>
   </si>
   <si>
+    <t xml:space="preserve">MANUAL FUNCTIONAL PASS; RATING BELL UI PASS; FEEDBACK/READ UI PARTIAL</t>
+  </si>
+  <si>
     <t xml:space="preserve">API/service tests</t>
   </si>
   <si>
-    <t xml:space="preserve">Repeat with Statistics/Monitoring screenshots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Historical API/database oracles passed</t>
+    <t xml:space="preserve">Click/read the controlled rating notification; repeat the feedback bell visually; capture Statistics/Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historical rating/feedback API and database oracles passed. On 2026-08-04 Nova's UI showed exactly one unread New rating item from Casey with the expected timestamp after the frontend batch. Rating read transition and feedback notification presentation are still pending; English notification copy on the Hungarian page is an i18n observation.</t>
   </si>
   <si>
     <t xml:space="preserve">STATIC-SMOKE</t>
@@ -1326,18 +1332,18 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="23.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="51.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="73.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="63.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="73.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="58.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="67.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="54.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="129.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="76.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="71.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="70.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="77.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="86.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="100.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="295.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16.43"/>
   </cols>
   <sheetData>
@@ -1586,37 +1592,43 @@
       <c r="J6" s="0" t="s">
         <v>43</v>
       </c>
+      <c r="K6" s="1" t="n">
+        <v>46238</v>
+      </c>
       <c r="L6" s="0" t="s">
         <v>44</v>
       </c>
       <c r="M6" s="0" t="s">
         <v>45</v>
       </c>
+      <c r="N6" s="0" t="s">
+        <v>46</v>
+      </c>
       <c r="O6" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P6" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>40</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G7" s="0" t="s">
         <v>20</v>
@@ -1628,24 +1640,24 @@
         <v>20</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L7" s="0" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M7" s="0" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O7" s="0" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P7" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>40</v>
@@ -1654,16 +1666,16 @@
         <v>6</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F8" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H8" s="0" t="s">
         <v>20</v>
@@ -1672,221 +1684,221 @@
         <v>20</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L8" s="0" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M8" s="0" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O8" s="0" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="P8" s="0" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="L9" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M9" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N9" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O9" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P9" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G10" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J10" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L10" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M10" s="0" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="O10" s="0" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="P10" s="0" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>4</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="M11" s="0" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O11" s="0" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="P11" s="0" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G12" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J12" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L12" s="0" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="M12" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="P12" s="0" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G13" s="0" t="s">
         <v>20</v>
@@ -1895,259 +1907,259 @@
         <v>20</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="M13" s="0" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="O13" s="0" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="P13" s="0" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D14" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="F14" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="H14" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="I14" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="J14" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L14" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="M14" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="O14" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="P14" s="0" t="s">
         <v>116</v>
-      </c>
-      <c r="E14" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="F14" s="0" t="s">
-        <v>118</v>
-      </c>
-      <c r="G14" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="H14" s="0" t="s">
-        <v>120</v>
-      </c>
-      <c r="I14" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="J14" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="L14" s="0" t="s">
-        <v>122</v>
-      </c>
-      <c r="M14" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="O14" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="P14" s="0" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="M15" s="0" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P15" s="0" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E16" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G16" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L16" s="0" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="M16" s="0" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="O16" s="0" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="P16" s="0" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="L17" s="0" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="M17" s="0" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O17" s="0" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="P17" s="0" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C18" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="G18" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="H18" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="I18" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="J18" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L18" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="M18" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="O18" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="P18" s="0" t="s">
         <v>146</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="E18" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="G18" s="0" t="s">
-        <v>160</v>
-      </c>
-      <c r="H18" s="0" t="s">
-        <v>161</v>
-      </c>
-      <c r="I18" s="0" t="s">
-        <v>162</v>
-      </c>
-      <c r="J18" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="L18" s="0" t="s">
-        <v>163</v>
-      </c>
-      <c r="M18" s="0" t="s">
-        <v>164</v>
-      </c>
-      <c r="O18" s="0" t="s">
-        <v>165</v>
-      </c>
-      <c r="P18" s="0" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E19" s="0" t="s">
         <v>20</v>
@@ -2156,7 +2168,7 @@
         <v>20</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H19" s="0" t="s">
         <v>20</v>
@@ -2165,30 +2177,30 @@
         <v>20</v>
       </c>
       <c r="J19" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L19" s="0" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="M19" s="0" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="P19" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E20" s="0" t="s">
         <v>20</v>
@@ -2197,48 +2209,48 @@
         <v>20</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H20" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J20" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L20" s="0" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="M20" s="0" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="P20" s="0" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F21" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H21" s="0" t="s">
         <v>20</v>
@@ -2247,30 +2259,30 @@
         <v>20</v>
       </c>
       <c r="J21" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L21" s="0" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="M21" s="0" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="P21" s="0" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E22" s="0" t="s">
         <v>20</v>
@@ -2279,80 +2291,80 @@
         <v>20</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H22" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J22" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L22" s="0" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="M22" s="0" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="P22" s="0" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J23" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L23" s="0" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="M23" s="0" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="P23" s="0" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E24" s="0" t="s">
         <v>20</v>
@@ -2361,376 +2373,376 @@
         <v>20</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H24" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="J24" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L24" s="0" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M24" s="0" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="P24" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E25" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="J25" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="M25" s="0" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="P25" s="0" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="J26" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L26" s="0" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M26" s="0" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="P26" s="0" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="J27" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="M27" s="0" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="P27" s="0" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E28" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G28" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="J28" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L28" s="0" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="M28" s="0" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="O28" s="0" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="P28" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E29" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G29" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="J29" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="M29" s="0" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="O29" s="0" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="P29" s="0" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="J30" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L30" s="0" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="M30" s="0" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="P30" s="0" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E31" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="G31" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="J31" s="0" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="L31" s="0" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="M31" s="0" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="O31" s="0" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="P31" s="0" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E32" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="G32" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="J32" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L32" s="0" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="M32" s="0" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="P32" s="0" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E33" s="0" t="s">
         <v>20</v>
@@ -2742,142 +2754,142 @@
         <v>20</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J33" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L33" s="0" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="M33" s="0" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="P33" s="0" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E34" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G34" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J34" s="0" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K34" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="L34" s="0" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="M34" s="0" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="N34" s="0" t="s">
-        <v>294</v>
+        <v>77</v>
       </c>
       <c r="O34" s="0" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P34" s="0" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H35" s="0" t="s">
         <v>26</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="J35" s="0" t="s">
-        <v>302</v>
+        <v>43</v>
       </c>
       <c r="K35" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="L35" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M35" s="0" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N35" s="0" t="s">
-        <v>294</v>
+        <v>77</v>
       </c>
       <c r="O35" s="0" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P35" s="0" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E36" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G36" s="0" t="s">
         <v>20</v>
@@ -2886,48 +2898,48 @@
         <v>26</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J36" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K36" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L36" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M36" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N36" s="0" t="s">
-        <v>294</v>
+        <v>77</v>
       </c>
       <c r="O36" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P36" s="0" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E37" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G37" s="0" t="s">
         <v>20</v>
@@ -2936,48 +2948,48 @@
         <v>26</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J37" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K37" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M37" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N37" s="0" t="s">
-        <v>294</v>
+        <v>77</v>
       </c>
       <c r="O37" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P37" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E38" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G38" s="0" t="s">
         <v>20</v>
@@ -2986,48 +2998,48 @@
         <v>26</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J38" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K38" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L38" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M38" s="0" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N38" s="0" t="s">
-        <v>294</v>
+        <v>77</v>
       </c>
       <c r="O38" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P38" s="0" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E39" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G39" s="0" t="s">
         <v>20</v>
@@ -3036,98 +3048,98 @@
         <v>26</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J39" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K39" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L39" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M39" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N39" s="0" t="s">
-        <v>294</v>
+        <v>77</v>
       </c>
       <c r="O39" s="0" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P39" s="0" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H40" s="0" t="s">
         <v>26</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J40" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K40" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L40" s="0" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M40" s="0" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N40" s="0" t="s">
-        <v>294</v>
+        <v>77</v>
       </c>
       <c r="O40" s="0" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P40" s="0" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E41" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G41" s="0" t="s">
         <v>20</v>
@@ -3136,222 +3148,222 @@
         <v>26</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J41" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K41" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L41" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M41" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N41" s="0" t="s">
-        <v>294</v>
+        <v>77</v>
       </c>
       <c r="O41" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P41" s="0" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H42" s="0" t="s">
         <v>26</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J42" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K42" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L42" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M42" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N42" s="0" t="s">
-        <v>294</v>
+        <v>77</v>
       </c>
       <c r="O42" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P42" s="0" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J43" s="0" t="s">
-        <v>291</v>
+        <v>370</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M43" s="0" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N43" s="0" t="s">
-        <v>294</v>
+        <v>77</v>
       </c>
       <c r="O43" s="0" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="P43" s="0" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="G44" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="J44" s="0" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L44" s="0" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M44" s="0" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="O44" s="0" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P44" s="0" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J45" s="0" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K45" s="1" t="n">
         <v>46238</v>
       </c>
       <c r="L45" s="0" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M45" s="0" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N45" s="0" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="O45" s="0" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P45" s="0" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>

--- a/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
+++ b/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="404">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -280,13 +280,16 @@
     <t xml:space="preserve">Message and unread/read projection correct</t>
   </si>
   <si>
+    <t xml:space="preserve">MANUAL UI + FUNCTIONAL PASS</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chat/realtime E2E support</t>
   </si>
   <si>
-    <t xml:space="preserve">One message, one telemetry delta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System chat messages are excluded from Statistics message count</t>
+    <t xml:space="preserve">Continue with STAT-012; retain this unique-message oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farkas Anna sent one unique ordinary message in Host Circle Ops. UI showed one bubble; API showed chat total 41-&gt;42 and exactly one matching non-system message. The real Statistics worker changed today's Messages 0-&gt;1, Communication/Messages 417-&gt;418 and Communication total 426-&gt;427. Browser screenshots at 06:53 confirmed Messages 1 and Messages 418; Ratings, Moderation and the pre-message Events value stayed stable.</t>
   </si>
   <si>
     <t xml:space="preserve">P1 66</t>
@@ -382,7 +385,7 @@
     <t xml:space="preserve">Finish controlled affinity recompute</t>
   </si>
   <si>
-    <t xml:space="preserve">Graph metrics/timeline change in predicted direction</t>
+    <t xml:space="preserve">Graph metrics/timeline change in predicted direction; prior dates stay immutable</t>
   </si>
   <si>
     <t xml:space="preserve">Matching queue returns terminal</t>
@@ -397,13 +400,16 @@
     <t xml:space="preserve">Discovery/affinity projection correct</t>
   </si>
   <si>
-    <t xml:space="preserve">AdminGraphScienceService tests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compare same edge set across summary and explorer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allow telemetry worker window before refresh</t>
+    <t xml:space="preserve">DEFECT FIXED; HOT-DEPLOY RUNTIME + MANUAL STATISTICS UI PASS; AFFINITY GRAPH COMPARISON PENDING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historical immutability regression unit source added; dev classes hot-deploy compiled; runtime snapshot contract passed; standalone unit run intentionally not started</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare the corresponding current edge set in Affinity Graph explorer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initial manual refresh exposed a real defect: every Jul 22-Aug 3 point was rewritten from bridgeUsers 2-&gt;0, communities 2-&gt;1 and clusterQuality 7-&gt;3. Fix preserves stored past dates and replaces only today. Hot-deploy runtime proof compared 04:51:23 to 04:58:42: today's activeEdges changed 309-&gt;313 and recurringEdges 274-&gt;278 while all 13 prior points stayed exactly unchanged. The post-fix 07:05 browser screenshot, from the 07:03 admin snapshot after another real Refresh, reselected Jul 22 and retained Active edges 16, New edges 0, Recurring 13, Weak ties 16, Network quality 67%, and Cluster quality 3%. Manual Statistics UI retest passed; direct Affinity Graph comparison remains pending and the original FAIL evidence is retained.</t>
   </si>
   <si>
     <t xml:space="preserve">MON-011</t>
@@ -1333,14 +1339,14 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="23.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="73.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="63.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="65.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="73.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="58.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="129.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="76.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="102.03"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="77.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="134.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="86.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="295.9"/>
@@ -1778,24 +1784,30 @@
         <v>85</v>
       </c>
       <c r="J10" s="0" t="s">
-        <v>53</v>
+        <v>86</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>46238</v>
       </c>
       <c r="L10" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M10" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="N10" s="0" t="s">
+        <v>46</v>
       </c>
       <c r="O10" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P10" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>67</v>
@@ -1804,45 +1816,45 @@
         <v>4</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M11" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O11" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P11" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>67</v>
@@ -1851,13 +1863,13 @@
         <v>4</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G12" s="0" t="s">
         <v>20</v>
@@ -1866,24 +1878,24 @@
         <v>72</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J12" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L12" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M12" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P12" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>67</v>
@@ -1892,13 +1904,13 @@
         <v>4</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G13" s="0" t="s">
         <v>20</v>
@@ -1907,74 +1919,80 @@
         <v>20</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M13" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O13" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P13" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>67</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>53</v>
+        <v>126</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>46238</v>
       </c>
       <c r="L14" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="M14" s="0" t="s">
-        <v>126</v>
+        <v>128</v>
+      </c>
+      <c r="N14" s="0" t="s">
+        <v>77</v>
       </c>
       <c r="O14" s="0" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="P14" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>67</v>
@@ -1983,39 +2001,39 @@
         <v>50</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J15" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M15" s="0" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="P15" s="0" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>67</v>
@@ -2024,142 +2042,142 @@
         <v>50</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E16" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G16" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L16" s="0" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="M16" s="0" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="O16" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="P16" s="0" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L17" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M17" s="0" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O17" s="0" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P17" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E18" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J18" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L18" s="0" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M18" s="0" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O18" s="0" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="P18" s="0" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E19" s="0" t="s">
         <v>20</v>
@@ -2168,7 +2186,7 @@
         <v>20</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H19" s="0" t="s">
         <v>20</v>
@@ -2180,10 +2198,10 @@
         <v>53</v>
       </c>
       <c r="L19" s="0" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M19" s="0" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="P19" s="0" t="s">
         <v>48</v>
@@ -2191,16 +2209,16 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E20" s="0" t="s">
         <v>20</v>
@@ -2209,48 +2227,48 @@
         <v>20</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H20" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J20" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L20" s="0" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M20" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P20" s="0" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F21" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H21" s="0" t="s">
         <v>20</v>
@@ -2262,27 +2280,27 @@
         <v>53</v>
       </c>
       <c r="L21" s="0" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M21" s="0" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P21" s="0" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E22" s="0" t="s">
         <v>20</v>
@@ -2291,30 +2309,30 @@
         <v>20</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H22" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J22" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L22" s="0" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M22" s="0" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P22" s="0" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>67</v>
@@ -2323,48 +2341,48 @@
         <v>6</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J23" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L23" s="0" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M23" s="0" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="P23" s="0" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E24" s="0" t="s">
         <v>20</v>
@@ -2373,22 +2391,22 @@
         <v>20</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H24" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="J24" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L24" s="0" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M24" s="0" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="P24" s="0" t="s">
         <v>79</v>
@@ -2396,166 +2414,166 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E25" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J25" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M25" s="0" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P25" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J26" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L26" s="0" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M26" s="0" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P26" s="0" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J27" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M27" s="0" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P27" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E28" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G28" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="J28" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L28" s="0" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M28" s="0" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O28" s="0" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P28" s="0" t="s">
         <v>79</v>
@@ -2563,186 +2581,186 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E29" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G29" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J29" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M29" s="0" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O29" s="0" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="P29" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J30" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L30" s="0" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M30" s="0" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P30" s="0" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B31" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="E31" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F31" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="G31" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="I31" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="J31" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="L31" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="M31" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="O31" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="P31" s="0" t="s">
         <v>221</v>
-      </c>
-      <c r="C31" s="0" t="s">
-        <v>263</v>
-      </c>
-      <c r="D31" s="0" t="s">
-        <v>264</v>
-      </c>
-      <c r="E31" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="F31" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="G31" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="I31" s="0" t="s">
-        <v>266</v>
-      </c>
-      <c r="J31" s="0" t="s">
-        <v>267</v>
-      </c>
-      <c r="L31" s="0" t="s">
-        <v>268</v>
-      </c>
-      <c r="M31" s="0" t="s">
-        <v>269</v>
-      </c>
-      <c r="O31" s="0" t="s">
-        <v>270</v>
-      </c>
-      <c r="P31" s="0" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E32" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G32" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="J32" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L32" s="0" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M32" s="0" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P32" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E33" s="0" t="s">
         <v>20</v>
@@ -2754,101 +2772,101 @@
         <v>20</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J33" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L33" s="0" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M33" s="0" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P33" s="0" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E34" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G34" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="J34" s="0" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K34" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="L34" s="0" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M34" s="0" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N34" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O34" s="0" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P34" s="0" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H35" s="0" t="s">
         <v>26</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="J35" s="0" t="s">
         <v>43</v>
@@ -2857,39 +2875,39 @@
         <v>46234</v>
       </c>
       <c r="L35" s="0" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M35" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N35" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O35" s="0" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P35" s="0" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E36" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G36" s="0" t="s">
         <v>20</v>
@@ -2898,48 +2916,48 @@
         <v>26</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J36" s="0" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K36" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L36" s="0" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M36" s="0" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N36" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O36" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="P36" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E37" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G37" s="0" t="s">
         <v>20</v>
@@ -2948,25 +2966,25 @@
         <v>26</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J37" s="0" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K37" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M37" s="0" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N37" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O37" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="P37" s="0" t="s">
         <v>57</v>
@@ -2974,22 +2992,22 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E38" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G38" s="0" t="s">
         <v>20</v>
@@ -2998,48 +3016,48 @@
         <v>26</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J38" s="0" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K38" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L38" s="0" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M38" s="0" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N38" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O38" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="P38" s="0" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E39" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G39" s="0" t="s">
         <v>20</v>
@@ -3048,98 +3066,98 @@
         <v>26</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J39" s="0" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K39" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L39" s="0" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="M39" s="0" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N39" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O39" s="0" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P39" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H40" s="0" t="s">
         <v>26</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J40" s="0" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K40" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L40" s="0" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M40" s="0" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N40" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O40" s="0" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="P40" s="0" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E41" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G41" s="0" t="s">
         <v>20</v>
@@ -3148,222 +3166,222 @@
         <v>26</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J41" s="0" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K41" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L41" s="0" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M41" s="0" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N41" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O41" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="P41" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="H42" s="0" t="s">
         <v>26</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J42" s="0" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K42" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L42" s="0" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M42" s="0" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="N42" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O42" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="P42" s="0" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="J43" s="0" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K43" s="1" t="n">
         <v>46238</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M43" s="0" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N43" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O43" s="0" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="P43" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G44" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J44" s="0" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L44" s="0" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M44" s="0" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O44" s="0" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="P44" s="0" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J45" s="0" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K45" s="1" t="n">
         <v>46238</v>
       </c>
       <c r="L45" s="0" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M45" s="0" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N45" s="0" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="O45" s="0" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="P45" s="0" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>

--- a/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
+++ b/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
@@ -1332,7 +1332,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P45"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.96"/>
@@ -3384,6 +3384,88 @@
         <v>403</v>
       </c>
     </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-POLL-JANK-001</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Performance defect retest</t>
+        </is>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin Jobs + Chat</t>
+        </is>
+      </c>
+      <c r="D46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compare pointer, scroll and input frame pacing across idle UI, Admin process list, Job Detail and Chat during periodic/live updates</t>
+        </is>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c r="F46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c r="G46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c r="H46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Detail must stay responsive during refresh; no unnecessary full-state poll or render hitch</t>
+        </is>
+      </c>
+      <c r="I46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chat must stay responsive during WebSocket and user-realtime updates</t>
+        </is>
+      </c>
+      <c r="J46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN — JOB MANUAL OBSERVED + CODE PATH CORROBORATED; CHAT REPORTED / TRACE PENDING</t>
+        </is>
+      </c>
+      <c r="K46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-04</t>
+        </is>
+      </c>
+      <c r="L46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UiTaskScheduler prevents overlapping polls; no trustworthy browser frame-time regression oracle</t>
+        </is>
+      </c>
+      <c r="M46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capture 20–30 second Performance + Network traces for idle/list/detail/chat and correlate hitches with 5s Job polling, WebSocket events and 10/30s user realtime long-poll</t>
+        </is>
+      </c>
+      <c r="N46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN</t>
+        </is>
+      </c>
+      <c r="O46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Detail visibly stutters and reloads the complete process-center state every 5 seconds; detailOpen is passed as unused task state, so it does not gate polling, and the component lacks OnPush. Chat shows a similar reported symptom but uses OnPush and WebSocket live events; the global user realtime scheduler is a separate 30-second poll, 10 seconds in demo. Shared root cause is unconfirmed. Both checkpoints must pass before closure.</t>
+        </is>
+      </c>
+      <c r="P46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1 65</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
+++ b/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="418">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -316,57 +316,60 @@
     <t xml:space="preserve">Member state and notification agree</t>
   </si>
   <si>
+    <t xml:space="preserve">Service tests; dedicated manual-helper exact oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retain as a release-change sample; UI-POLL-JANK-001 remains separate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A controlled 30-second eligibility window was picked up by the real scheduler at 08:49 without a Run button. Job Detail showed processed 1, pending 0 and 131ms. The exact machine oracle proved one Nova invitation, marker, outbox and bell with matching recipient sets. Monitoring showed membership writes 1359-&gt;1360, capacity/invites 1322-&gt;1323 and shared outbox 228-&gt;229 while event writes/model remained 59. Statistics showed Daily Events/assets 1322-&gt;1323, section total 1502-&gt;1503 and Event participation 1370-&gt;1371 while Active/Total events stayed 69/79. Nova UI showed exactly one Casey event invite. The manual bell query was corrected to accept payload.type. Guarded reset verified not-staged and restored the original rule/data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1 74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAT-013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change one asset request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset activity and asset-request delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets queue/flow delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset request state correct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use one isolated asset request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P2 58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAT-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submit feedback/report or isolated moderation action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moderation timeline/item and attention change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Users/Jobs or relevant domain delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bell/moderation state correct</t>
+  </si>
+  <si>
     <t xml:space="preserve">PARTIAL</t>
   </si>
   <si>
-    <t xml:space="preserve">Service tests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capture Statistics and Monitoring around one invite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto-inviter bell was manually visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P1 74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STAT-013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change one asset request</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asset activity and asset-request delta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assets queue/flow delta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asset request state correct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use one isolated asset request</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P2 58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STAT-014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Submit feedback/report or isolated moderation action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moderation timeline/item and attention change</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Users/Jobs or relevant domain delta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bell/moderation state correct</t>
-  </si>
-  <si>
     <t xml:space="preserve">Capture exact before/after and health direction</t>
   </si>
   <si>
@@ -457,13 +460,16 @@
     <t xml:space="preserve">Bell/Firebase/no-op and outbox row agree</t>
   </si>
   <si>
+    <t xml:space="preserve">MANUAL CAUSAL PARTIAL</t>
+  </si>
+  <si>
     <t xml:space="preserve">Outbox tests</t>
   </si>
   <si>
-    <t xml:space="preserve">Capture Monitoring transition in browser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Historical outbox domain oracle passed</t>
+    <t xml:space="preserve">Capture notification-outbox Job Detail pending-to-terminal/retained behavior and health state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAT-012 browser evidence showed the shared outbox flow 228-&gt;229 and exactly one matching Nova bell. Direct read-only evidence showed the logical outbox pending because Firebase delivery is inactive and the notification-outbox job retained pending work as documented. The dedicated outbox Job Detail lifecycle and failure/recovery UI states remain pending.</t>
   </si>
   <si>
     <t xml:space="preserve">P0 92</t>
@@ -940,33 +946,36 @@
     <t xml:space="preserve">DELTA invites/member state/bell</t>
   </si>
   <si>
+    <t xml:space="preserve">Fixture/service/common lifecycle tests; dedicated manual-helper exact oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repeat on scheduler/domain changes; retain cross-surface sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real scheduler picked up the persisted short window at 08:49 and processed exactly one eligible Nova invitation. Job Detail, invitation/marker/outbox/bell database oracle, Nova notification UI, Monitoring and Statistics all agreed. No Run button or direct job endpoint was used. Guarded reset restored the original data and rule configuration.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOB-TOURNAMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">event-tournament-review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real scheduler reviews stage transitions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA scheduler/audit; INDIRECT domain/outbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA stage review/advancement/score-plan/notifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUAL FUNCTIONAL PASS</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fixture/service/common lifecycle tests</t>
   </si>
   <si>
-    <t xml:space="preserve">Capture Statistics and Monitoring deltas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User confirmed both bell items visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOB-TOURNAMENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">event-tournament-review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real scheduler reviews stage transitions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DELTA scheduler/audit; INDIRECT domain/outbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DELTA stage review/advancement/score-plan/notifications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANUAL FUNCTIONAL PASS</t>
-  </si>
-  <si>
     <t xml:space="preserve">Capture Monitoring plus key browser state</t>
   </si>
   <si>
@@ -1232,6 +1241,39 @@
   </si>
   <si>
     <t xml:space="preserve">P0 100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-POLL-JANK-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Performance defect retest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin Jobs + Chat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare pointer, scroll and input frame pacing across idle UI, Admin process list, Job Detail and Chat during periodic/live updates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job Detail must stay responsive during refresh; no unnecessary full-state poll or render hitch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chat must stay responsive during WebSocket and user-realtime updates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPEN â€” JOB MANUAL OBSERVED + CODE PATH CORROBORATED; CHAT REPORTED / TRACE PENDING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UiTaskScheduler prevents overlapping polls; no trustworthy browser frame-time regression oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capture 20â€“30 second Performance + Network traces for idle/list/detail/chat and correlate hitches with 5s Job polling, WebSocket events and 10/30s user realtime long-poll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job Detail visibly stutters and reloads the complete process-center state every 5 seconds; detailOpen is passed as unused task state, so it does not gate polling, and the component lacks OnPush. Chat shows a similar reported symptom but uses OnPush and WebSocket live events; the global user realtime scheduler is a separate 30-second poll, 10 seconds in demo. Shared root cause is unconfirmed. Both checkpoints must pass before closure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1 65</t>
   </si>
 </sst>
 </file>
@@ -1335,19 +1377,19 @@
   <dimension ref="A1:P46"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="23.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="73.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="106.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="65.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="73.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="58.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="75.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="129.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="102.03"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="134.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="86.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="140.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="295.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16.43"/>
@@ -1834,27 +1876,30 @@
         <v>97</v>
       </c>
       <c r="J11" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L11" s="0" t="s">
         <v>98</v>
       </c>
-      <c r="K11" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="L11" s="0" t="s">
+      <c r="M11" s="0" t="s">
         <v>99</v>
       </c>
-      <c r="M11" s="0" t="s">
+      <c r="N11" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="O11" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="O11" s="0" t="s">
+      <c r="P11" s="0" t="s">
         <v>101</v>
-      </c>
-      <c r="P11" s="0" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>67</v>
@@ -1863,13 +1908,13 @@
         <v>4</v>
       </c>
       <c r="D12" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" s="0" t="s">
         <v>104</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="F12" s="0" t="s">
         <v>105</v>
-      </c>
-      <c r="F12" s="0" t="s">
-        <v>106</v>
       </c>
       <c r="G12" s="0" t="s">
         <v>20</v>
@@ -1878,13 +1923,13 @@
         <v>72</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J12" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L12" s="0" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="M12" s="0" t="s">
         <v>108</v>
@@ -1922,77 +1967,77 @@
         <v>114</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="M13" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O13" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P13" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>67</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>46238</v>
       </c>
       <c r="L14" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M14" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N14" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O14" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P14" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>67</v>
@@ -2001,39 +2046,39 @@
         <v>50</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J15" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M15" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P15" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>67</v>
@@ -2042,142 +2087,145 @@
         <v>50</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E16" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G16" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="L16" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M16" s="0" t="s">
-        <v>146</v>
+        <v>148</v>
+      </c>
+      <c r="N16" s="0" t="s">
+        <v>77</v>
       </c>
       <c r="O16" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P16" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L17" s="0" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M17" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O17" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P17" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E18" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J18" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L18" s="0" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M18" s="0" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O18" s="0" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="P18" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E19" s="0" t="s">
         <v>20</v>
@@ -2186,7 +2234,7 @@
         <v>20</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H19" s="0" t="s">
         <v>20</v>
@@ -2198,10 +2246,10 @@
         <v>53</v>
       </c>
       <c r="L19" s="0" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M19" s="0" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P19" s="0" t="s">
         <v>48</v>
@@ -2209,16 +2257,16 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E20" s="0" t="s">
         <v>20</v>
@@ -2227,48 +2275,48 @@
         <v>20</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H20" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J20" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L20" s="0" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M20" s="0" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="P20" s="0" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F21" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H21" s="0" t="s">
         <v>20</v>
@@ -2280,27 +2328,27 @@
         <v>53</v>
       </c>
       <c r="L21" s="0" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M21" s="0" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P21" s="0" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E22" s="0" t="s">
         <v>20</v>
@@ -2309,30 +2357,30 @@
         <v>20</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H22" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J22" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L22" s="0" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="M22" s="0" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P22" s="0" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>67</v>
@@ -2341,48 +2389,48 @@
         <v>6</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J23" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L23" s="0" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M23" s="0" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P23" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E24" s="0" t="s">
         <v>20</v>
@@ -2391,22 +2439,22 @@
         <v>20</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H24" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J24" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L24" s="0" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="M24" s="0" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P24" s="0" t="s">
         <v>79</v>
@@ -2414,166 +2462,166 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E25" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J25" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M25" s="0" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P25" s="0" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J26" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L26" s="0" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M26" s="0" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P26" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J27" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M27" s="0" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P27" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E28" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G28" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J28" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L28" s="0" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M28" s="0" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O28" s="0" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P28" s="0" t="s">
         <v>79</v>
@@ -2581,186 +2629,186 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E29" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G29" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J29" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M29" s="0" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O29" s="0" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P29" s="0" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="J30" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L30" s="0" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M30" s="0" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P30" s="0" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B31" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="E31" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F31" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="G31" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="I31" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="J31" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="L31" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="M31" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="O31" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="P31" s="0" t="s">
         <v>223</v>
-      </c>
-      <c r="C31" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="D31" s="0" t="s">
-        <v>266</v>
-      </c>
-      <c r="E31" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="F31" s="0" t="s">
-        <v>267</v>
-      </c>
-      <c r="G31" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="0" t="s">
-        <v>244</v>
-      </c>
-      <c r="I31" s="0" t="s">
-        <v>268</v>
-      </c>
-      <c r="J31" s="0" t="s">
-        <v>269</v>
-      </c>
-      <c r="L31" s="0" t="s">
-        <v>270</v>
-      </c>
-      <c r="M31" s="0" t="s">
-        <v>271</v>
-      </c>
-      <c r="O31" s="0" t="s">
-        <v>272</v>
-      </c>
-      <c r="P31" s="0" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E32" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G32" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J32" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L32" s="0" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M32" s="0" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="P32" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E33" s="0" t="s">
         <v>20</v>
@@ -2772,92 +2820,92 @@
         <v>20</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J33" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L33" s="0" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M33" s="0" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P33" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E34" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="G34" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J34" s="0" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K34" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="L34" s="0" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M34" s="0" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N34" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O34" s="0" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="P34" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G35" s="0" t="s">
         <v>95</v>
@@ -2866,48 +2914,48 @@
         <v>26</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="J35" s="0" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="L35" s="0" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M35" s="0" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N35" s="0" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="O35" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P35" s="0" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E36" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G36" s="0" t="s">
         <v>20</v>
@@ -2916,48 +2964,48 @@
         <v>26</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J36" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K36" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L36" s="0" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="M36" s="0" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N36" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O36" s="0" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="P36" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E37" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G37" s="0" t="s">
         <v>20</v>
@@ -2966,25 +3014,25 @@
         <v>26</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="J37" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K37" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="M37" s="0" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="N37" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O37" s="0" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="P37" s="0" t="s">
         <v>57</v>
@@ -2992,22 +3040,22 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E38" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G38" s="0" t="s">
         <v>20</v>
@@ -3016,48 +3064,48 @@
         <v>26</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="J38" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K38" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L38" s="0" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="M38" s="0" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="N38" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O38" s="0" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="P38" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E39" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G39" s="0" t="s">
         <v>20</v>
@@ -3066,98 +3114,98 @@
         <v>26</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="J39" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K39" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L39" s="0" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="M39" s="0" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="N39" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O39" s="0" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="P39" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H40" s="0" t="s">
         <v>26</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="J40" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K40" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L40" s="0" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="M40" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="N40" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O40" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="P40" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E41" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="G41" s="0" t="s">
         <v>20</v>
@@ -3166,304 +3214,272 @@
         <v>26</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="J41" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K41" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L41" s="0" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="M41" s="0" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="N41" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O41" s="0" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="P41" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="H42" s="0" t="s">
         <v>26</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="J42" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K42" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L42" s="0" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="M42" s="0" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="N42" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O42" s="0" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="P42" s="0" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J43" s="0" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K43" s="1" t="n">
         <v>46238</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="M43" s="0" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="N43" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O43" s="0" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="P43" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="G44" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="J44" s="0" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="L44" s="0" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="M44" s="0" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="O44" s="0" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="P44" s="0" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="J45" s="0" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K45" s="1" t="n">
         <v>46238</v>
       </c>
       <c r="L45" s="0" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="M45" s="0" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="N45" s="0" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="O45" s="0" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="P45" s="0" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI-POLL-JANK-001</t>
-        </is>
-      </c>
-      <c r="B46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Performance defect retest</t>
-        </is>
-      </c>
-      <c r="C46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admin Jobs + Chat</t>
-        </is>
-      </c>
-      <c r="D46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Compare pointer, scroll and input frame pacing across idle UI, Admin process list, Job Detail and Chat during periodic/live updates</t>
-        </is>
-      </c>
-      <c r="E46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
-        </is>
-      </c>
-      <c r="F46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
-        </is>
-      </c>
-      <c r="G46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
-        </is>
-      </c>
-      <c r="H46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Job Detail must stay responsive during refresh; no unnecessary full-state poll or render hitch</t>
-        </is>
-      </c>
-      <c r="I46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chat must stay responsive during WebSocket and user-realtime updates</t>
-        </is>
-      </c>
-      <c r="J46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN — JOB MANUAL OBSERVED + CODE PATH CORROBORATED; CHAT REPORTED / TRACE PENDING</t>
-        </is>
-      </c>
-      <c r="K46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-04</t>
-        </is>
-      </c>
-      <c r="L46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UiTaskScheduler prevents overlapping polls; no trustworthy browser frame-time regression oracle</t>
-        </is>
-      </c>
-      <c r="M46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Capture 20–30 second Performance + Network traces for idle/list/detail/chat and correlate hitches with 5s Job polling, WebSocket events and 10/30s user realtime long-poll</t>
-        </is>
-      </c>
-      <c r="N46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN</t>
-        </is>
-      </c>
-      <c r="O46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Job Detail visibly stutters and reloads the complete process-center state every 5 seconds; detailOpen is passed as unused task state, so it does not gate polling, and the component lacks OnPush. Chat shows a similar reported symptom but uses OnPush and WebSocket live events; the global user realtime scheduler is a separate 30-second poll, 10 seconds in demo. Shared root cause is unconfirmed. Both checkpoints must pass before closure.</t>
-        </is>
-      </c>
-      <c r="P46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1 65</t>
-        </is>
+      <c r="A46" s="0" t="s">
+        <v>407</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>408</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>409</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>410</v>
+      </c>
+      <c r="E46" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F46" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G46" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" s="0" t="s">
+        <v>411</v>
+      </c>
+      <c r="I46" s="0" t="s">
+        <v>412</v>
+      </c>
+      <c r="J46" s="0" t="s">
+        <v>413</v>
+      </c>
+      <c r="K46" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L46" s="0" t="s">
+        <v>414</v>
+      </c>
+      <c r="M46" s="0" t="s">
+        <v>415</v>
+      </c>
+      <c r="N46" s="0" t="s">
+        <v>404</v>
+      </c>
+      <c r="O46" s="0" t="s">
+        <v>416</v>
+      </c>
+      <c r="P46" s="0" t="s">
+        <v>417</v>
       </c>
     </row>
   </sheetData>

--- a/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
+++ b/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="760">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -1274,6 +1274,1032 @@
   </si>
   <si>
     <t xml:space="preserve">P1 65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-EDITOR-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event Editor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create, save and reopen one draft event</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT after the statistics snapshot worker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA event write and recompute queue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT after recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA affinity recompute task; active-only schedulers X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draft appears once in Hosting/Drafts and every saved field reopens exactly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event sync/service coverage partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capture pre-save, post-save and reopened editor plus canonical event oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One action and one state transition; no publish proof is inferred</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-EDITOR-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publish one controlled draft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT event inventory delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA event lifecycle and recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA affinity recompute; slot/reminder consumers conditional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hosting and Explore visibility obey user and visibility boundaries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publish/service coverage partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare host and unrelated-user buckets against canonical active state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publish is separate from draft save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-EDITOR-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event Editor + Auto inviter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save one eligible auto-inviter definition, then let the real scheduler consume it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT event/member activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA event save, member write and outbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT after event/member recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA event-auto-inviter real run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exactly one pending invited member and recipient invitation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto-inviter service/fixture coverage; STAT-012 scheduler path passed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage editor-produced input and prove the scheduler-created output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The fixture may stage prerequisites but must not create the invitation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-EDITOR-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event Editor + Tournament</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save and reopen one tournament definition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT event activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA event write and recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tournament review/grouping X until explicitly armed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stages, capacities and group definition survive reopen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tournament service coverage partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare editor definition with runtime stage baseline before processing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Definition persistence is not grouping proof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-EDITOR-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edit one downstream-relevant active field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT documented event delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA definition change and recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT when the field affects affinity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA affinity recompute; other consumers conditional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changed field persists; removed definition is absent; no-op reopen is X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change one field only and retain one unrelated control field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No-op navigation must not duplicate downstream effects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-LIFE-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event lifecycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unpublish active event to draft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT lifecycle inventory delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA affinity recompute; reminders/attachments conditional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explore removes it; organizer Drafts/Hosting contains it once</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lifecycle service coverage partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canonical draft status plus host/unrelated-user bucket screenshots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reopen and refresh after completion are X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-LIFE-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trash one organizer event</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT active/trash inventory delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA lifecycle, recompute and conditional notification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA affinity recompute; auto-inviter becomes ineligible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only Trash contains it; active attachments and ticket affordances unavailable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trash and bucket service tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify trashed status, preserved prior status and bucket exclusivity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global trash is distinct from participant leave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-LIFE-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restore one organizer event from Trash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT restored inventory delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA lifecycle and recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA affinity recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preserved draft/active bucket returns with no duplicate members or resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restore and bucket service tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify cleared suppression fields and exact restored bucket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refresh after restore is X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-LIFE-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event participation lifecycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Participant leave and restore without organizer authority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT participation delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA member mutation; event lifecycle X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT only if membership evidence changes affinity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONDITIONAL member recompute; organizer lifecycle job X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viewer Attending/Trash changes; canonical event stays active for others</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member suppression/restore service tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use participant and organizer sessions plus canonical event oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must not be misclassified as global event deletion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-LIFE-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event buckets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open and refresh Hosting, Drafts, Attending, Invitations and Trash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each identity appears only in its documented bucket; no writes occur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bucket query tests partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Record bucket membership and prove no domain/task/outbox change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is the explicit read-only checkpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-INV-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event membership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner/admin manually invites one controlled user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT member activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA membership write and notification outbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT after membership evidence/recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notification outbox conditional; scheduler X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One pending Event Members row and one recipient invitation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member invite service tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Match event, inviter, recipient, pending status and requestKind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manual invite is not scheduler proof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-INV-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event membership privacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inspect a pending invitation before acceptance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accepted-only controls, chat and resources are hidden and server-denied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Access-control tests partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use menu check and direct/deep-link denial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI hiding alone is insufficient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-INV-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accept an owner/admin invitation once</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT membership and later chat deltas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA accepted membership and resolved invitation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT after membership recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONDITIONAL recompute/outbox; scheduler X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pending becomes accepted once; accepted-only chat becomes available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invitation acceptance service tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Match membership, resolved bell and one unique chat write</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acceptance and chat authorization are separate oracles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-INV-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event membership approval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accept an ordinary-member invite, then approve as admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT only after terminal acceptance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA pending approval then accepted membership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT after terminal transition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chat stays denied before admin approval and appears only afterward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invitation approval service tests partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capture both pending states and the final accepted state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient acceptance alone must not bypass approval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-INV-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event membership edges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reject, cancel, capacity-block and repeat acceptance independently</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT only for real state changes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA per real mutation; no-op repeats X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONDITIONAL; duplicate tasks/outbox forbidden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No duplicate member, overbooking, stale bell or rejected-user chat access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacity/idempotence service tests partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run every branch as its own named checkpoint lineage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative branches remain independently passable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHAT-AUTH-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event chat authorization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare pending, accepted and left membership against chat access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT only for the one proof message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA chat write only after accepted state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X unless the message creates documented delivery work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Server denies pending/left users; accepted user reads and writes once</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chat/access-control coverage partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use isolated sessions and one unique message after acceptance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Readable history outside accepted membership is P0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-FEEDBACK-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross the feedback eligibility boundary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accepted non-admin participant sees one item only after start plus two hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feedback eligibility service coverage partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare before/after boundary, trashed, admin and pending controls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current code uses start plus two hours, not event end or closed status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-FEEDBACK-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submit one controlled event feedback response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA event feedback activity after snapshot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA feedback telemetry, counters and outbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT after target-user recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA affinity recompute; first-submit outbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submitted item, organizer received view and recipient notification agree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feedback submit service tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Match persisted answers, state, target IDs and first-submit notification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continue to EVENT-IMPRESSION-001 for profile propagation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-FEEDBACK-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edit and resubmit existing feedback once</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X for duplicate submitted count; answer update may be visible later</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA answer update; duplicate outbox X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT if changed target evidence recomputes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONDITIONAL target recompute; duplicate first-submit outbox X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existing answer updates; no duplicate state or first-submit bell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resubmit notification test; persistence coverage partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count answer/state/outbox before and after one changed answer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unchanged reopen/close is X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-FEEDBACK-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event feedback lifecycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove and restore one submitted feedback list item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT feedback bucket/counter only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA feedback state/counters; recompute and outbox X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Removed/restored bucket changes; saved answers and Impressions evidence stay unchanged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feedback state access tests partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare state flag, answer documents, popup trait and task/outbox counts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current aggregation ignores the removed flag for saved answer evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-FEEDBACK-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event feedback metadata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save and reopen one organizer note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT received-feedback counter refresh only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exact note persists; participant answers and profile traits remain unchanged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feedback note access tests partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use one unique note and unchanged answer/task controls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No scheduler is part of this checkpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-IMPRESSION-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profile Impressions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observe target profile after controlled event feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT normal user-realtime snapshot only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT because feedback submit queued target recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correct Host or Attendee trait evidence changes; unrelated section X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impressions merge code; frontend realtime support partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capture before popup, feedback oracle, recompute terminal and after popup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Popup open is read-only; stale data after the realtime window is a propagation defect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-TICKET-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event ticketing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable ticketing and reopen the event</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT event definition delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA event save and recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA affinity recompute; ticket scheduler X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Participant overlay and editor retain ticketing without role changes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ticket sync/service tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare canonical event, participant overlay and reopened editor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opening ticket UI is read-only with respect to jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-TICKET-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Issue or reuse one accepted-participant credential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One stable event/holder ticket; pending/rejected/admin control gets none</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventTicketService tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count credentials and match event/holder/code across repeated opens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct request path; no scheduler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-TICKET-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Authorized exact-once check-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT check-in counter only if documented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First scan succeeds once; repeat, invalid and unauthorized scans do not mutate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ticket check-in service tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare used timestamp and result codes across four scans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No notification or worker is inferred</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-TICKET-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event ticketing lifecycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disable, unpublish, trash or expire ticket use one mutation at a time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT lifecycle delta owned by the event mutation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA event lifecycle/recompute; ticket read X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT after event recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA only for the owning lifecycle mutation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ticket unavailable or revoked/expired; holder membership remains correct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ticket eligibility and lifecycle tests partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify each lifecycle result with the same credential and holder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rejected scan must not add another job</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOURNAMENT-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tournament</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inspect saved tournament definition before grouping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT event inventory only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA definition write; runtime processing X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tournament grouping/review X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parent, stages, capacities, sequence and initial counts agree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare editor definition and runtime baseline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No automatic grouping is inferred from save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOURNAMENT-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run real grouping and inspect group membership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA group/member/chat materialization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT after membership changes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA named real grouping path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each accepted user occurs once in the correct group and group chat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Random grouping fixture/service coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Match parent, stage, group, member and chat identities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pending invites are not accepted group members</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOURNAMENT-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finalize stage and let real review advance it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT stage/member activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA stage, membership and outbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT after advancement recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA event-tournament-review real run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winners advance once; losers and stale groups are removed correctly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tournament-review fixture/service coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capture pre-stage, job terminal and next-stage domain/UI oracles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Second unchanged review is X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSET-MEMBER-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset membership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invite one controlled asset member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT asset/member activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA asset membership and optional outbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One asset-scoped pending row and matching recipient invitation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset membership service tests partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Match asset owner/type/id, inviter and recipient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must not create event membership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSET-MEMBER-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accept one asset invite and reject another</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA asset membership states</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONDITIONAL outbox; scheduler X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accepted role and rejected cleanup are exact; event role stays unchanged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset acceptance/rejection service tests partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare two independent identities and event-role control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset Manager is not Event Admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSET-ASSIGN-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assign one accepted user's asset to one sub-event</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT asset/event activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA assignment and availability projection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONDITIONAL availability/outbox; scheduler X unless explicitly documented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event, sub-event, asset owner, asset ID and capacity agree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset assignment lifecycle coverage partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare assignment record, Event Resources and asset UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assignment must not create a second membership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPERATOR-FIREBASE-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operator authentication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify and activate Firebase config, observe login mode, then roll back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA operator configuration/capability only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notification delivery becomes conditional on verified Firebase capability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh session opens Firebase login; failed activation and rollback preserve recovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operator configuration/security tests partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use disposable config, fresh session and masked evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provider activation is not a demo-login form smoke test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-SLOT-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event Editor / recurring slots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save one weekly slot template with two sub-events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT event inventory after Save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA parent event write and recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X unless a named downstream job becomes eligible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upcoming list shows multiple dated sections with the same two definitions once each</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slot mapper/editor tests partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Match parent, template, occurrence and sub-event identities after reopen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">List reads and calendar navigation are X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-SLOT-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sub-event list action gating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inspect future occurrence menus as host and participant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only role/mode/time-valid member, resource and runtime actions are visible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runtime menu converter tests partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capture both roles and prove Close/Finalize absent for future stages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI hiding plus direct authorization denial where applicable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-SLOT-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Past tournament slot lifecycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Close one ended stage in one generated past occurrence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT stage activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA slot-scoped runtime mutation and recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tournament review X until separately armed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only selected slot/stage changes RS or A to SR with stage-closed reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage action and slot mapper tests partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Match recentPastSlotId, stage ID, prior/next status and unchanged sibling occurrence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct Close is not scheduler attribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-SLOT-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Past slot leaderboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open one past slot leaderboard and change one score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT score activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA score row and tournament-input recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review scheduler X until separately armed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group members and changed score remain scoped to one slot/stage/group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leaderboard service tests partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reopen score and compare a sibling weekly occurrence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leaderboard reads are X; Save is exact-once</t>
   </si>
 </sst>
 </file>
@@ -1374,12 +2400,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:P83"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="23.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="106.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="65.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="73.96"/>
@@ -3482,6 +4508,1634 @@
         <v>417</v>
       </c>
     </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0" t="s">
+        <v>418</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>420</v>
+      </c>
+      <c r="D47" s="0" t="s">
+        <v>421</v>
+      </c>
+      <c r="E47" s="0" t="s">
+        <v>422</v>
+      </c>
+      <c r="F47" s="0" t="s">
+        <v>423</v>
+      </c>
+      <c r="G47" s="0" t="s">
+        <v>424</v>
+      </c>
+      <c r="H47" s="0" t="s">
+        <v>425</v>
+      </c>
+      <c r="I47" s="0" t="s">
+        <v>426</v>
+      </c>
+      <c r="J47" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L47" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="M47" s="0" t="s">
+        <v>428</v>
+      </c>
+      <c r="O47" s="0" t="s">
+        <v>429</v>
+      </c>
+      <c r="P47" s="0" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0" t="s">
+        <v>430</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>420</v>
+      </c>
+      <c r="D48" s="0" t="s">
+        <v>431</v>
+      </c>
+      <c r="E48" s="0" t="s">
+        <v>432</v>
+      </c>
+      <c r="F48" s="0" t="s">
+        <v>433</v>
+      </c>
+      <c r="G48" s="0" t="s">
+        <v>424</v>
+      </c>
+      <c r="H48" s="0" t="s">
+        <v>434</v>
+      </c>
+      <c r="I48" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="J48" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L48" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="M48" s="0" t="s">
+        <v>437</v>
+      </c>
+      <c r="O48" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="P48" s="0" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="D49" s="0" t="s">
+        <v>441</v>
+      </c>
+      <c r="E49" s="0" t="s">
+        <v>442</v>
+      </c>
+      <c r="F49" s="0" t="s">
+        <v>443</v>
+      </c>
+      <c r="G49" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="H49" s="0" t="s">
+        <v>445</v>
+      </c>
+      <c r="I49" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="J49" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L49" s="0" t="s">
+        <v>447</v>
+      </c>
+      <c r="M49" s="0" t="s">
+        <v>448</v>
+      </c>
+      <c r="O49" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="P49" s="0" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0" t="s">
+        <v>450</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>451</v>
+      </c>
+      <c r="D50" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="E50" s="0" t="s">
+        <v>453</v>
+      </c>
+      <c r="F50" s="0" t="s">
+        <v>454</v>
+      </c>
+      <c r="G50" s="0" t="s">
+        <v>424</v>
+      </c>
+      <c r="H50" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="I50" s="0" t="s">
+        <v>456</v>
+      </c>
+      <c r="J50" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L50" s="0" t="s">
+        <v>457</v>
+      </c>
+      <c r="M50" s="0" t="s">
+        <v>458</v>
+      </c>
+      <c r="O50" s="0" t="s">
+        <v>459</v>
+      </c>
+      <c r="P50" s="0" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0" t="s">
+        <v>460</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>420</v>
+      </c>
+      <c r="D51" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="E51" s="0" t="s">
+        <v>462</v>
+      </c>
+      <c r="F51" s="0" t="s">
+        <v>463</v>
+      </c>
+      <c r="G51" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="H51" s="0" t="s">
+        <v>465</v>
+      </c>
+      <c r="I51" s="0" t="s">
+        <v>466</v>
+      </c>
+      <c r="J51" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L51" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="M51" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="O51" s="0" t="s">
+        <v>468</v>
+      </c>
+      <c r="P51" s="0" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0" t="s">
+        <v>469</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C52" s="0" t="s">
+        <v>470</v>
+      </c>
+      <c r="D52" s="0" t="s">
+        <v>471</v>
+      </c>
+      <c r="E52" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="F52" s="0" t="s">
+        <v>433</v>
+      </c>
+      <c r="G52" s="0" t="s">
+        <v>424</v>
+      </c>
+      <c r="H52" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="I52" s="0" t="s">
+        <v>474</v>
+      </c>
+      <c r="J52" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L52" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="M52" s="0" t="s">
+        <v>476</v>
+      </c>
+      <c r="O52" s="0" t="s">
+        <v>477</v>
+      </c>
+      <c r="P52" s="0" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C53" s="0" t="s">
+        <v>470</v>
+      </c>
+      <c r="D53" s="0" t="s">
+        <v>479</v>
+      </c>
+      <c r="E53" s="0" t="s">
+        <v>480</v>
+      </c>
+      <c r="F53" s="0" t="s">
+        <v>481</v>
+      </c>
+      <c r="G53" s="0" t="s">
+        <v>424</v>
+      </c>
+      <c r="H53" s="0" t="s">
+        <v>482</v>
+      </c>
+      <c r="I53" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="J53" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L53" s="0" t="s">
+        <v>484</v>
+      </c>
+      <c r="M53" s="0" t="s">
+        <v>485</v>
+      </c>
+      <c r="O53" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="P53" s="0" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0" t="s">
+        <v>487</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C54" s="0" t="s">
+        <v>470</v>
+      </c>
+      <c r="D54" s="0" t="s">
+        <v>488</v>
+      </c>
+      <c r="E54" s="0" t="s">
+        <v>489</v>
+      </c>
+      <c r="F54" s="0" t="s">
+        <v>490</v>
+      </c>
+      <c r="G54" s="0" t="s">
+        <v>424</v>
+      </c>
+      <c r="H54" s="0" t="s">
+        <v>491</v>
+      </c>
+      <c r="I54" s="0" t="s">
+        <v>492</v>
+      </c>
+      <c r="J54" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L54" s="0" t="s">
+        <v>493</v>
+      </c>
+      <c r="M54" s="0" t="s">
+        <v>494</v>
+      </c>
+      <c r="O54" s="0" t="s">
+        <v>495</v>
+      </c>
+      <c r="P54" s="0" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0" t="s">
+        <v>496</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C55" s="0" t="s">
+        <v>497</v>
+      </c>
+      <c r="D55" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="E55" s="0" t="s">
+        <v>499</v>
+      </c>
+      <c r="F55" s="0" t="s">
+        <v>500</v>
+      </c>
+      <c r="G55" s="0" t="s">
+        <v>501</v>
+      </c>
+      <c r="H55" s="0" t="s">
+        <v>502</v>
+      </c>
+      <c r="I55" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="J55" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L55" s="0" t="s">
+        <v>504</v>
+      </c>
+      <c r="M55" s="0" t="s">
+        <v>505</v>
+      </c>
+      <c r="O55" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="P55" s="0" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0" t="s">
+        <v>507</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C56" s="0" t="s">
+        <v>508</v>
+      </c>
+      <c r="D56" s="0" t="s">
+        <v>509</v>
+      </c>
+      <c r="E56" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F56" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G56" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H56" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I56" s="0" t="s">
+        <v>510</v>
+      </c>
+      <c r="J56" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L56" s="0" t="s">
+        <v>511</v>
+      </c>
+      <c r="M56" s="0" t="s">
+        <v>512</v>
+      </c>
+      <c r="O56" s="0" t="s">
+        <v>513</v>
+      </c>
+      <c r="P56" s="0" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="s">
+        <v>514</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C57" s="0" t="s">
+        <v>515</v>
+      </c>
+      <c r="D57" s="0" t="s">
+        <v>516</v>
+      </c>
+      <c r="E57" s="0" t="s">
+        <v>517</v>
+      </c>
+      <c r="F57" s="0" t="s">
+        <v>518</v>
+      </c>
+      <c r="G57" s="0" t="s">
+        <v>519</v>
+      </c>
+      <c r="H57" s="0" t="s">
+        <v>520</v>
+      </c>
+      <c r="I57" s="0" t="s">
+        <v>521</v>
+      </c>
+      <c r="J57" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L57" s="0" t="s">
+        <v>522</v>
+      </c>
+      <c r="M57" s="0" t="s">
+        <v>523</v>
+      </c>
+      <c r="O57" s="0" t="s">
+        <v>524</v>
+      </c>
+      <c r="P57" s="0" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="s">
+        <v>525</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C58" s="0" t="s">
+        <v>526</v>
+      </c>
+      <c r="D58" s="0" t="s">
+        <v>527</v>
+      </c>
+      <c r="E58" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F58" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G58" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H58" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I58" s="0" t="s">
+        <v>528</v>
+      </c>
+      <c r="J58" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L58" s="0" t="s">
+        <v>529</v>
+      </c>
+      <c r="M58" s="0" t="s">
+        <v>530</v>
+      </c>
+      <c r="O58" s="0" t="s">
+        <v>531</v>
+      </c>
+      <c r="P58" s="0" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="s">
+        <v>532</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C59" s="0" t="s">
+        <v>515</v>
+      </c>
+      <c r="D59" s="0" t="s">
+        <v>533</v>
+      </c>
+      <c r="E59" s="0" t="s">
+        <v>534</v>
+      </c>
+      <c r="F59" s="0" t="s">
+        <v>535</v>
+      </c>
+      <c r="G59" s="0" t="s">
+        <v>536</v>
+      </c>
+      <c r="H59" s="0" t="s">
+        <v>537</v>
+      </c>
+      <c r="I59" s="0" t="s">
+        <v>538</v>
+      </c>
+      <c r="J59" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L59" s="0" t="s">
+        <v>539</v>
+      </c>
+      <c r="M59" s="0" t="s">
+        <v>540</v>
+      </c>
+      <c r="O59" s="0" t="s">
+        <v>541</v>
+      </c>
+      <c r="P59" s="0" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0" t="s">
+        <v>542</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C60" s="0" t="s">
+        <v>543</v>
+      </c>
+      <c r="D60" s="0" t="s">
+        <v>544</v>
+      </c>
+      <c r="E60" s="0" t="s">
+        <v>545</v>
+      </c>
+      <c r="F60" s="0" t="s">
+        <v>546</v>
+      </c>
+      <c r="G60" s="0" t="s">
+        <v>547</v>
+      </c>
+      <c r="H60" s="0" t="s">
+        <v>537</v>
+      </c>
+      <c r="I60" s="0" t="s">
+        <v>548</v>
+      </c>
+      <c r="J60" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L60" s="0" t="s">
+        <v>549</v>
+      </c>
+      <c r="M60" s="0" t="s">
+        <v>550</v>
+      </c>
+      <c r="O60" s="0" t="s">
+        <v>551</v>
+      </c>
+      <c r="P60" s="0" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0" t="s">
+        <v>552</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C61" s="0" t="s">
+        <v>553</v>
+      </c>
+      <c r="D61" s="0" t="s">
+        <v>554</v>
+      </c>
+      <c r="E61" s="0" t="s">
+        <v>555</v>
+      </c>
+      <c r="F61" s="0" t="s">
+        <v>556</v>
+      </c>
+      <c r="G61" s="0" t="s">
+        <v>555</v>
+      </c>
+      <c r="H61" s="0" t="s">
+        <v>557</v>
+      </c>
+      <c r="I61" s="0" t="s">
+        <v>558</v>
+      </c>
+      <c r="J61" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L61" s="0" t="s">
+        <v>559</v>
+      </c>
+      <c r="M61" s="0" t="s">
+        <v>560</v>
+      </c>
+      <c r="O61" s="0" t="s">
+        <v>561</v>
+      </c>
+      <c r="P61" s="0" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0" t="s">
+        <v>562</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C62" s="0" t="s">
+        <v>563</v>
+      </c>
+      <c r="D62" s="0" t="s">
+        <v>564</v>
+      </c>
+      <c r="E62" s="0" t="s">
+        <v>565</v>
+      </c>
+      <c r="F62" s="0" t="s">
+        <v>566</v>
+      </c>
+      <c r="G62" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H62" s="0" t="s">
+        <v>567</v>
+      </c>
+      <c r="I62" s="0" t="s">
+        <v>568</v>
+      </c>
+      <c r="J62" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L62" s="0" t="s">
+        <v>569</v>
+      </c>
+      <c r="M62" s="0" t="s">
+        <v>570</v>
+      </c>
+      <c r="O62" s="0" t="s">
+        <v>571</v>
+      </c>
+      <c r="P62" s="0" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0" t="s">
+        <v>572</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C63" s="0" t="s">
+        <v>573</v>
+      </c>
+      <c r="D63" s="0" t="s">
+        <v>574</v>
+      </c>
+      <c r="E63" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F63" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G63" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H63" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I63" s="0" t="s">
+        <v>575</v>
+      </c>
+      <c r="J63" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L63" s="0" t="s">
+        <v>576</v>
+      </c>
+      <c r="M63" s="0" t="s">
+        <v>577</v>
+      </c>
+      <c r="O63" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="P63" s="0" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="s">
+        <v>579</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C64" s="0" t="s">
+        <v>573</v>
+      </c>
+      <c r="D64" s="0" t="s">
+        <v>580</v>
+      </c>
+      <c r="E64" s="0" t="s">
+        <v>581</v>
+      </c>
+      <c r="F64" s="0" t="s">
+        <v>582</v>
+      </c>
+      <c r="G64" s="0" t="s">
+        <v>583</v>
+      </c>
+      <c r="H64" s="0" t="s">
+        <v>584</v>
+      </c>
+      <c r="I64" s="0" t="s">
+        <v>585</v>
+      </c>
+      <c r="J64" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L64" s="0" t="s">
+        <v>586</v>
+      </c>
+      <c r="M64" s="0" t="s">
+        <v>587</v>
+      </c>
+      <c r="O64" s="0" t="s">
+        <v>588</v>
+      </c>
+      <c r="P64" s="0" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="s">
+        <v>589</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C65" s="0" t="s">
+        <v>573</v>
+      </c>
+      <c r="D65" s="0" t="s">
+        <v>590</v>
+      </c>
+      <c r="E65" s="0" t="s">
+        <v>591</v>
+      </c>
+      <c r="F65" s="0" t="s">
+        <v>592</v>
+      </c>
+      <c r="G65" s="0" t="s">
+        <v>593</v>
+      </c>
+      <c r="H65" s="0" t="s">
+        <v>594</v>
+      </c>
+      <c r="I65" s="0" t="s">
+        <v>595</v>
+      </c>
+      <c r="J65" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L65" s="0" t="s">
+        <v>596</v>
+      </c>
+      <c r="M65" s="0" t="s">
+        <v>597</v>
+      </c>
+      <c r="O65" s="0" t="s">
+        <v>598</v>
+      </c>
+      <c r="P65" s="0" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="0" t="s">
+        <v>599</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C66" s="0" t="s">
+        <v>600</v>
+      </c>
+      <c r="D66" s="0" t="s">
+        <v>601</v>
+      </c>
+      <c r="E66" s="0" t="s">
+        <v>602</v>
+      </c>
+      <c r="F66" s="0" t="s">
+        <v>603</v>
+      </c>
+      <c r="G66" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H66" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" s="0" t="s">
+        <v>604</v>
+      </c>
+      <c r="J66" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L66" s="0" t="s">
+        <v>605</v>
+      </c>
+      <c r="M66" s="0" t="s">
+        <v>606</v>
+      </c>
+      <c r="O66" s="0" t="s">
+        <v>607</v>
+      </c>
+      <c r="P66" s="0" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="0" t="s">
+        <v>608</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C67" s="0" t="s">
+        <v>609</v>
+      </c>
+      <c r="D67" s="0" t="s">
+        <v>610</v>
+      </c>
+      <c r="E67" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F67" s="0" t="s">
+        <v>611</v>
+      </c>
+      <c r="G67" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H67" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I67" s="0" t="s">
+        <v>612</v>
+      </c>
+      <c r="J67" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L67" s="0" t="s">
+        <v>613</v>
+      </c>
+      <c r="M67" s="0" t="s">
+        <v>614</v>
+      </c>
+      <c r="O67" s="0" t="s">
+        <v>615</v>
+      </c>
+      <c r="P67" s="0" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="0" t="s">
+        <v>616</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C68" s="0" t="s">
+        <v>617</v>
+      </c>
+      <c r="D68" s="0" t="s">
+        <v>618</v>
+      </c>
+      <c r="E68" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F68" s="0" t="s">
+        <v>619</v>
+      </c>
+      <c r="G68" s="0" t="s">
+        <v>620</v>
+      </c>
+      <c r="H68" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I68" s="0" t="s">
+        <v>621</v>
+      </c>
+      <c r="J68" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L68" s="0" t="s">
+        <v>622</v>
+      </c>
+      <c r="M68" s="0" t="s">
+        <v>623</v>
+      </c>
+      <c r="O68" s="0" t="s">
+        <v>624</v>
+      </c>
+      <c r="P68" s="0" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="0" t="s">
+        <v>625</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C69" s="0" t="s">
+        <v>626</v>
+      </c>
+      <c r="D69" s="0" t="s">
+        <v>627</v>
+      </c>
+      <c r="E69" s="0" t="s">
+        <v>628</v>
+      </c>
+      <c r="F69" s="0" t="s">
+        <v>629</v>
+      </c>
+      <c r="G69" s="0" t="s">
+        <v>424</v>
+      </c>
+      <c r="H69" s="0" t="s">
+        <v>630</v>
+      </c>
+      <c r="I69" s="0" t="s">
+        <v>631</v>
+      </c>
+      <c r="J69" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L69" s="0" t="s">
+        <v>632</v>
+      </c>
+      <c r="M69" s="0" t="s">
+        <v>633</v>
+      </c>
+      <c r="O69" s="0" t="s">
+        <v>634</v>
+      </c>
+      <c r="P69" s="0" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="0" t="s">
+        <v>635</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C70" s="0" t="s">
+        <v>626</v>
+      </c>
+      <c r="D70" s="0" t="s">
+        <v>636</v>
+      </c>
+      <c r="E70" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F70" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G70" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H70" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I70" s="0" t="s">
+        <v>637</v>
+      </c>
+      <c r="J70" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L70" s="0" t="s">
+        <v>638</v>
+      </c>
+      <c r="M70" s="0" t="s">
+        <v>639</v>
+      </c>
+      <c r="O70" s="0" t="s">
+        <v>640</v>
+      </c>
+      <c r="P70" s="0" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="0" t="s">
+        <v>641</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C71" s="0" t="s">
+        <v>626</v>
+      </c>
+      <c r="D71" s="0" t="s">
+        <v>642</v>
+      </c>
+      <c r="E71" s="0" t="s">
+        <v>643</v>
+      </c>
+      <c r="F71" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G71" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H71" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I71" s="0" t="s">
+        <v>644</v>
+      </c>
+      <c r="J71" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L71" s="0" t="s">
+        <v>645</v>
+      </c>
+      <c r="M71" s="0" t="s">
+        <v>646</v>
+      </c>
+      <c r="O71" s="0" t="s">
+        <v>647</v>
+      </c>
+      <c r="P71" s="0" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="0" t="s">
+        <v>648</v>
+      </c>
+      <c r="B72" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C72" s="0" t="s">
+        <v>649</v>
+      </c>
+      <c r="D72" s="0" t="s">
+        <v>650</v>
+      </c>
+      <c r="E72" s="0" t="s">
+        <v>651</v>
+      </c>
+      <c r="F72" s="0" t="s">
+        <v>652</v>
+      </c>
+      <c r="G72" s="0" t="s">
+        <v>653</v>
+      </c>
+      <c r="H72" s="0" t="s">
+        <v>654</v>
+      </c>
+      <c r="I72" s="0" t="s">
+        <v>655</v>
+      </c>
+      <c r="J72" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L72" s="0" t="s">
+        <v>656</v>
+      </c>
+      <c r="M72" s="0" t="s">
+        <v>657</v>
+      </c>
+      <c r="O72" s="0" t="s">
+        <v>658</v>
+      </c>
+      <c r="P72" s="0" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="0" t="s">
+        <v>659</v>
+      </c>
+      <c r="B73" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C73" s="0" t="s">
+        <v>660</v>
+      </c>
+      <c r="D73" s="0" t="s">
+        <v>661</v>
+      </c>
+      <c r="E73" s="0" t="s">
+        <v>662</v>
+      </c>
+      <c r="F73" s="0" t="s">
+        <v>663</v>
+      </c>
+      <c r="G73" s="0" t="s">
+        <v>653</v>
+      </c>
+      <c r="H73" s="0" t="s">
+        <v>664</v>
+      </c>
+      <c r="I73" s="0" t="s">
+        <v>665</v>
+      </c>
+      <c r="J73" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L73" s="0" t="s">
+        <v>457</v>
+      </c>
+      <c r="M73" s="0" t="s">
+        <v>666</v>
+      </c>
+      <c r="O73" s="0" t="s">
+        <v>667</v>
+      </c>
+      <c r="P73" s="0" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="0" t="s">
+        <v>668</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C74" s="0" t="s">
+        <v>660</v>
+      </c>
+      <c r="D74" s="0" t="s">
+        <v>669</v>
+      </c>
+      <c r="E74" s="0" t="s">
+        <v>442</v>
+      </c>
+      <c r="F74" s="0" t="s">
+        <v>670</v>
+      </c>
+      <c r="G74" s="0" t="s">
+        <v>671</v>
+      </c>
+      <c r="H74" s="0" t="s">
+        <v>672</v>
+      </c>
+      <c r="I74" s="0" t="s">
+        <v>673</v>
+      </c>
+      <c r="J74" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L74" s="0" t="s">
+        <v>674</v>
+      </c>
+      <c r="M74" s="0" t="s">
+        <v>675</v>
+      </c>
+      <c r="O74" s="0" t="s">
+        <v>676</v>
+      </c>
+      <c r="P74" s="0" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="0" t="s">
+        <v>677</v>
+      </c>
+      <c r="B75" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C75" s="0" t="s">
+        <v>660</v>
+      </c>
+      <c r="D75" s="0" t="s">
+        <v>678</v>
+      </c>
+      <c r="E75" s="0" t="s">
+        <v>679</v>
+      </c>
+      <c r="F75" s="0" t="s">
+        <v>680</v>
+      </c>
+      <c r="G75" s="0" t="s">
+        <v>681</v>
+      </c>
+      <c r="H75" s="0" t="s">
+        <v>682</v>
+      </c>
+      <c r="I75" s="0" t="s">
+        <v>683</v>
+      </c>
+      <c r="J75" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L75" s="0" t="s">
+        <v>684</v>
+      </c>
+      <c r="M75" s="0" t="s">
+        <v>685</v>
+      </c>
+      <c r="O75" s="0" t="s">
+        <v>686</v>
+      </c>
+      <c r="P75" s="0" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="0" t="s">
+        <v>687</v>
+      </c>
+      <c r="B76" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C76" s="0" t="s">
+        <v>688</v>
+      </c>
+      <c r="D76" s="0" t="s">
+        <v>689</v>
+      </c>
+      <c r="E76" s="0" t="s">
+        <v>690</v>
+      </c>
+      <c r="F76" s="0" t="s">
+        <v>691</v>
+      </c>
+      <c r="G76" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H76" s="0" t="s">
+        <v>520</v>
+      </c>
+      <c r="I76" s="0" t="s">
+        <v>692</v>
+      </c>
+      <c r="J76" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L76" s="0" t="s">
+        <v>693</v>
+      </c>
+      <c r="M76" s="0" t="s">
+        <v>694</v>
+      </c>
+      <c r="O76" s="0" t="s">
+        <v>695</v>
+      </c>
+      <c r="P76" s="0" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="0" t="s">
+        <v>696</v>
+      </c>
+      <c r="B77" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C77" s="0" t="s">
+        <v>688</v>
+      </c>
+      <c r="D77" s="0" t="s">
+        <v>697</v>
+      </c>
+      <c r="E77" s="0" t="s">
+        <v>690</v>
+      </c>
+      <c r="F77" s="0" t="s">
+        <v>698</v>
+      </c>
+      <c r="G77" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H77" s="0" t="s">
+        <v>699</v>
+      </c>
+      <c r="I77" s="0" t="s">
+        <v>700</v>
+      </c>
+      <c r="J77" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L77" s="0" t="s">
+        <v>701</v>
+      </c>
+      <c r="M77" s="0" t="s">
+        <v>702</v>
+      </c>
+      <c r="O77" s="0" t="s">
+        <v>703</v>
+      </c>
+      <c r="P77" s="0" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="0" t="s">
+        <v>704</v>
+      </c>
+      <c r="B78" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C78" s="0" t="s">
+        <v>705</v>
+      </c>
+      <c r="D78" s="0" t="s">
+        <v>706</v>
+      </c>
+      <c r="E78" s="0" t="s">
+        <v>707</v>
+      </c>
+      <c r="F78" s="0" t="s">
+        <v>708</v>
+      </c>
+      <c r="G78" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H78" s="0" t="s">
+        <v>709</v>
+      </c>
+      <c r="I78" s="0" t="s">
+        <v>710</v>
+      </c>
+      <c r="J78" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L78" s="0" t="s">
+        <v>711</v>
+      </c>
+      <c r="M78" s="0" t="s">
+        <v>712</v>
+      </c>
+      <c r="O78" s="0" t="s">
+        <v>713</v>
+      </c>
+      <c r="P78" s="0" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="0" t="s">
+        <v>714</v>
+      </c>
+      <c r="B79" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C79" s="0" t="s">
+        <v>715</v>
+      </c>
+      <c r="D79" s="0" t="s">
+        <v>716</v>
+      </c>
+      <c r="E79" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F79" s="0" t="s">
+        <v>717</v>
+      </c>
+      <c r="G79" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H79" s="0" t="s">
+        <v>718</v>
+      </c>
+      <c r="I79" s="0" t="s">
+        <v>719</v>
+      </c>
+      <c r="J79" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L79" s="0" t="s">
+        <v>720</v>
+      </c>
+      <c r="M79" s="0" t="s">
+        <v>721</v>
+      </c>
+      <c r="O79" s="0" t="s">
+        <v>722</v>
+      </c>
+      <c r="P79" s="0" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="0" t="s">
+        <v>723</v>
+      </c>
+      <c r="B80" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C80" s="0" t="s">
+        <v>724</v>
+      </c>
+      <c r="D80" s="0" t="s">
+        <v>725</v>
+      </c>
+      <c r="E80" s="0" t="s">
+        <v>726</v>
+      </c>
+      <c r="F80" s="0" t="s">
+        <v>727</v>
+      </c>
+      <c r="G80" s="0" t="s">
+        <v>653</v>
+      </c>
+      <c r="H80" s="0" t="s">
+        <v>728</v>
+      </c>
+      <c r="I80" s="0" t="s">
+        <v>729</v>
+      </c>
+      <c r="J80" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L80" s="0" t="s">
+        <v>730</v>
+      </c>
+      <c r="M80" s="0" t="s">
+        <v>731</v>
+      </c>
+      <c r="O80" s="0" t="s">
+        <v>732</v>
+      </c>
+      <c r="P80" s="0" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="0" t="s">
+        <v>733</v>
+      </c>
+      <c r="B81" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C81" s="0" t="s">
+        <v>734</v>
+      </c>
+      <c r="D81" s="0" t="s">
+        <v>735</v>
+      </c>
+      <c r="E81" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F81" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G81" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H81" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I81" s="0" t="s">
+        <v>736</v>
+      </c>
+      <c r="J81" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L81" s="0" t="s">
+        <v>737</v>
+      </c>
+      <c r="M81" s="0" t="s">
+        <v>738</v>
+      </c>
+      <c r="O81" s="0" t="s">
+        <v>739</v>
+      </c>
+      <c r="P81" s="0" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="0" t="s">
+        <v>740</v>
+      </c>
+      <c r="B82" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C82" s="0" t="s">
+        <v>741</v>
+      </c>
+      <c r="D82" s="0" t="s">
+        <v>742</v>
+      </c>
+      <c r="E82" s="0" t="s">
+        <v>743</v>
+      </c>
+      <c r="F82" s="0" t="s">
+        <v>744</v>
+      </c>
+      <c r="G82" s="0" t="s">
+        <v>424</v>
+      </c>
+      <c r="H82" s="0" t="s">
+        <v>745</v>
+      </c>
+      <c r="I82" s="0" t="s">
+        <v>746</v>
+      </c>
+      <c r="J82" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L82" s="0" t="s">
+        <v>747</v>
+      </c>
+      <c r="M82" s="0" t="s">
+        <v>748</v>
+      </c>
+      <c r="O82" s="0" t="s">
+        <v>749</v>
+      </c>
+      <c r="P82" s="0" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="0" t="s">
+        <v>750</v>
+      </c>
+      <c r="B83" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C83" s="0" t="s">
+        <v>751</v>
+      </c>
+      <c r="D83" s="0" t="s">
+        <v>752</v>
+      </c>
+      <c r="E83" s="0" t="s">
+        <v>753</v>
+      </c>
+      <c r="F83" s="0" t="s">
+        <v>754</v>
+      </c>
+      <c r="G83" s="0" t="s">
+        <v>424</v>
+      </c>
+      <c r="H83" s="0" t="s">
+        <v>755</v>
+      </c>
+      <c r="I83" s="0" t="s">
+        <v>756</v>
+      </c>
+      <c r="J83" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L83" s="0" t="s">
+        <v>757</v>
+      </c>
+      <c r="M83" s="0" t="s">
+        <v>758</v>
+      </c>
+      <c r="O83" s="0" t="s">
+        <v>759</v>
+      </c>
+      <c r="P83" s="0" t="s">
+        <v>365</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
+++ b/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="761">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -1255,22 +1255,25 @@
     <t xml:space="preserve">Compare pointer, scroll and input frame pacing across idle UI, Admin process list, Job Detail and Chat during periodic/live updates</t>
   </si>
   <si>
-    <t xml:space="preserve">Job Detail must stay responsive during refresh; no unnecessary full-state poll or render hitch</t>
+    <t xml:space="preserve">Job Detail must stay responsive during SmartList refresh; unchanged polls must not mutate rows; only the selected changed rule may reach the detail signal</t>
   </si>
   <si>
     <t xml:space="preserve">Chat must stay responsive during WebSocket and user-realtime updates</t>
   </si>
   <si>
-    <t xml:space="preserve">OPEN â€” JOB MANUAL OBSERVED + CODE PATH CORROBORATED; CHAT REPORTED / TRACE PENDING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UiTaskScheduler prevents overlapping polls; no trustworthy browser frame-time regression oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capture 20â€“30 second Performance + Network traces for idle/list/detail/chat and correlate hitches with 5s Job polling, WebSocket events and 10/30s user realtime long-poll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job Detail visibly stutters and reloads the complete process-center state every 5 seconds; detailOpen is passed as unused task state, so it does not gate polling, and the component lacks OnPush. Chat shows a similar reported symptom but uses OnPush and WebSocket live events; the global user realtime scheduler is a separate 30-second poll, 10 seconds in demo. Shared root cause is unconfirmed. Both checkpoints must pass before closure.</t>
+    <t xml:space="preserve">ADMIN JOB MANUAL VISUAL PASS; PERFORMANCE TRACE + CHAT RETEST PENDING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focused component tests pass 6/6 for SmartList loading, keyed equality, row patching, detail isolation and local patch routing; running hot-deploy build manually showed no prior Job Detail stutter; browser frame-time trace not captured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capture 20â€“30 second Performance + Network traces for idle/list/detail/chat; prove unchanged Job polls preserve DOM rows and non-selected updates do not re-render detail; correlate Chat hitches independently</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPEN / PARTIAL PASS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin Jobs now uses SmartList-owned five-second polling, cancellation, keyed equality, visible-row patching and re-sorting with OnPush. Job Detail receives only its selected changed rule through a separate signal; the complete list is not pushed into detail. The full center remains the table data source. The 2026-08-04 hot-deployed build no longer showed the reported stutter during manual use, but no Performance trace was captured. Chat remains a separate reported symptom using OnPush, WebSocket live events and a 30-second global user realtime poll, shortened to 10 seconds in demo; its root cause remains unconfirmed. Both checkpoints must pass before closure.</t>
   </si>
   <si>
     <t xml:space="preserve">P1 65</t>
@@ -2410,13 +2413,13 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="65.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="73.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="58.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="75.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="127.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="129.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="102.03"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="134.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="140.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="189.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="173.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="21.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="295.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16.43"/>
   </cols>
@@ -4499,54 +4502,54 @@
         <v>415</v>
       </c>
       <c r="N46" s="0" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="O46" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P46" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J47" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L47" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M47" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O47" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P47" s="0" t="s">
         <v>223</v>
@@ -4554,43 +4557,43 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J48" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L48" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M48" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O48" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P48" s="0" t="s">
         <v>140</v>
@@ -4598,43 +4601,43 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J49" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L49" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M49" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O49" s="0" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P49" s="0" t="s">
         <v>163</v>
@@ -4642,43 +4645,43 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J50" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L50" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M50" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O50" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="P50" s="0" t="s">
         <v>140</v>
@@ -4686,43 +4689,43 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G51" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J51" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L51" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M51" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O51" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="P51" s="0" t="s">
         <v>118</v>
@@ -4730,43 +4733,43 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J52" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L52" s="0" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M52" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O52" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P52" s="0" t="s">
         <v>150</v>
@@ -4774,43 +4777,43 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J53" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M53" s="0" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O53" s="0" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P53" s="0" t="s">
         <v>350</v>
@@ -4818,43 +4821,43 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J54" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L54" s="0" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M54" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O54" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="P54" s="0" t="s">
         <v>163</v>
@@ -4862,43 +4865,43 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="J55" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M55" s="0" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O55" s="0" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P55" s="0" t="s">
         <v>350</v>
@@ -4906,16 +4909,16 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E56" s="0" t="s">
         <v>20</v>
@@ -4930,19 +4933,19 @@
         <v>20</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="J56" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L56" s="0" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M56" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O56" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="P56" s="0" t="s">
         <v>101</v>
@@ -4950,43 +4953,43 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="J57" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M57" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="O57" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P57" s="0" t="s">
         <v>163</v>
@@ -4994,16 +4997,16 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E58" s="0" t="s">
         <v>20</v>
@@ -5018,19 +5021,19 @@
         <v>20</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J58" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L58" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M58" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O58" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P58" s="0" t="s">
         <v>406</v>
@@ -5038,43 +5041,43 @@
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="J59" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M59" s="0" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="O59" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="P59" s="0" t="s">
         <v>365</v>
@@ -5082,43 +5085,43 @@
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="J60" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L60" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M60" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O60" s="0" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P60" s="0" t="s">
         <v>406</v>
@@ -5126,43 +5129,43 @@
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F61" s="0" t="s">
+        <v>557</v>
+      </c>
+      <c r="G61" s="0" t="s">
         <v>556</v>
       </c>
-      <c r="G61" s="0" t="s">
-        <v>555</v>
-      </c>
       <c r="H61" s="0" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="J61" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M61" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O61" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="P61" s="0" t="s">
         <v>365</v>
@@ -5170,43 +5173,43 @@
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="G62" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="J62" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L62" s="0" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M62" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O62" s="0" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P62" s="0" t="s">
         <v>406</v>
@@ -5214,16 +5217,16 @@
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E63" s="0" t="s">
         <v>20</v>
@@ -5238,19 +5241,19 @@
         <v>20</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="J63" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M63" s="0" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="O63" s="0" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="P63" s="0" t="s">
         <v>140</v>
@@ -5258,43 +5261,43 @@
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="J64" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L64" s="0" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M64" s="0" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O64" s="0" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P64" s="0" t="s">
         <v>350</v>
@@ -5302,43 +5305,43 @@
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="J65" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M65" s="0" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="O65" s="0" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="P65" s="0" t="s">
         <v>140</v>
@@ -5346,22 +5349,22 @@
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="G66" s="0" t="s">
         <v>20</v>
@@ -5370,19 +5373,19 @@
         <v>20</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="J66" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L66" s="0" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M66" s="0" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O66" s="0" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="P66" s="0" t="s">
         <v>150</v>
@@ -5390,22 +5393,22 @@
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E67" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="G67" s="0" t="s">
         <v>20</v>
@@ -5414,19 +5417,19 @@
         <v>20</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="J67" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M67" s="0" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="O67" s="0" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="P67" s="0" t="s">
         <v>185</v>
@@ -5434,43 +5437,43 @@
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E68" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H68" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="J68" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L68" s="0" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M68" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O68" s="0" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="P68" s="0" t="s">
         <v>163</v>
@@ -5478,43 +5481,43 @@
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="J69" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M69" s="0" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="O69" s="0" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="P69" s="0" t="s">
         <v>150</v>
@@ -5522,16 +5525,16 @@
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E70" s="0" t="s">
         <v>20</v>
@@ -5546,19 +5549,19 @@
         <v>20</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="J70" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L70" s="0" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M70" s="0" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O70" s="0" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="P70" s="0" t="s">
         <v>350</v>
@@ -5566,19 +5569,19 @@
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F71" s="0" t="s">
         <v>20</v>
@@ -5590,19 +5593,19 @@
         <v>20</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="J71" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M71" s="0" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="O71" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="P71" s="0" t="s">
         <v>365</v>
@@ -5610,43 +5613,43 @@
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="J72" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L72" s="0" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M72" s="0" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="O72" s="0" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="P72" s="0" t="s">
         <v>365</v>
@@ -5654,43 +5657,43 @@
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="J73" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M73" s="0" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O73" s="0" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="P73" s="0" t="s">
         <v>140</v>
@@ -5698,43 +5701,43 @@
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="J74" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M74" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="O74" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="P74" s="0" t="s">
         <v>350</v>
@@ -5742,43 +5745,43 @@
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="J75" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="M75" s="0" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="O75" s="0" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="P75" s="0" t="s">
         <v>365</v>
@@ -5786,43 +5789,43 @@
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="G76" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="J76" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L76" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M76" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="O76" s="0" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="P76" s="0" t="s">
         <v>140</v>
@@ -5830,43 +5833,43 @@
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="G77" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="J77" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M77" s="0" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="O77" s="0" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="P77" s="0" t="s">
         <v>163</v>
@@ -5874,43 +5877,43 @@
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="G78" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="J78" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L78" s="0" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="M78" s="0" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="O78" s="0" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="P78" s="0" t="s">
         <v>163</v>
@@ -5918,43 +5921,43 @@
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E79" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="G79" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="J79" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L79" s="0" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M79" s="0" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="O79" s="0" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="P79" s="0" t="s">
         <v>406</v>
@@ -5962,43 +5965,43 @@
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="J80" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L80" s="0" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M80" s="0" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="O80" s="0" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="P80" s="0" t="s">
         <v>163</v>
@@ -6006,16 +6009,16 @@
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E81" s="0" t="s">
         <v>20</v>
@@ -6030,19 +6033,19 @@
         <v>20</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="J81" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="M81" s="0" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="O81" s="0" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="P81" s="0" t="s">
         <v>350</v>
@@ -6050,43 +6053,43 @@
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="J82" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L82" s="0" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="M82" s="0" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="O82" s="0" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="P82" s="0" t="s">
         <v>365</v>
@@ -6094,43 +6097,43 @@
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="J83" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M83" s="0" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="O83" s="0" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="P83" s="0" t="s">
         <v>365</v>

--- a/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
+++ b/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="771">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -2303,6 +2303,36 @@
   </si>
   <si>
     <t xml:space="preserve">Leaderboard reads are X; Save is exact-once</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA-RESET-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harness defect retest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manual QA isolation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reset a scheduler scenario after it creates an invitation and notification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reloaded invitee shows the exact pre-stage Invitations and Notifications badge values and no fixture-owned rows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXED; MANUAL UI RECHECK PENDING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAT-012 helper snapshots and restores both selected users' activity projections; JavaScript syntax check passed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reload Nova after the current guarded repair; verify both empty lists have zero badges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPEN / PARTIAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initial STAT-012 reset removed the event, member and notification rows but left Nova activities.invitations, activities.event.all, activities.event.invitations and activities.notifications at 1. Read-only evidence proved no remaining Nova event membership, owned/admin event or notification. A guarded exact-state update repaired all four counters, and the reusable reset now restores the pre-stage activities projections. Cleanup isolation is P0 by policy.</t>
   </si>
 </sst>
 </file>
@@ -2403,7 +2433,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P83"/>
+  <dimension ref="A1:P84"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.78"/>
@@ -6139,6 +6169,56 @@
         <v>365</v>
       </c>
     </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="0" t="s">
+        <v>761</v>
+      </c>
+      <c r="B84" s="0" t="s">
+        <v>762</v>
+      </c>
+      <c r="C84" s="0" t="s">
+        <v>763</v>
+      </c>
+      <c r="D84" s="0" t="s">
+        <v>764</v>
+      </c>
+      <c r="E84" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F84" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G84" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H84" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I84" s="0" t="s">
+        <v>765</v>
+      </c>
+      <c r="J84" s="0" t="s">
+        <v>766</v>
+      </c>
+      <c r="K84" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L84" s="0" t="s">
+        <v>767</v>
+      </c>
+      <c r="M84" s="0" t="s">
+        <v>768</v>
+      </c>
+      <c r="N84" s="0" t="s">
+        <v>769</v>
+      </c>
+      <c r="O84" s="0" t="s">
+        <v>770</v>
+      </c>
+      <c r="P84" s="0" t="s">
+        <v>223</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
+++ b/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="783">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -646,6 +646,45 @@
     <t xml:space="preserve">One changed pair plus one control pair</t>
   </si>
   <si>
+    <t xml:space="preserve">GRAPH-RATING-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Causal checkpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rating + Affinity Graph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save one single rating in each direction using two isolated sessions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT two rating deltas after Statistics refresh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA rating sync and recompute flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA mutualSingleCount and pair weight; same pair visible at depth 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Affinity recompute may run for both users; direct edge recompute also occurs during each sync</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both directional rating rows, reciprocal score, notifications and pair identity agree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rating/affinity service tests and graph endpoint tests exist; assembled two-browser to graph projection is manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capture one-way oracle, reciprocal oracle, direct edge, graph source/layout version and reopened depth-1 pair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do not require a brand-new edge: seeded Met evidence may already create one. Active config currently weights mutual rating 10, mutual edge evidence 1, one-sided edge evidence 0 and Met evidence 0.5. Old materialized layout is a separate projection checkpoint.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P0 96</t>
+  </si>
+  <si>
     <t xml:space="preserve">GRAPH-007</t>
   </si>
   <si>
@@ -1070,9 +1109,6 @@
   </si>
   <si>
     <t xml:space="preserve">Primary domain oracle passed; graph UI not manually qualified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P0 96</t>
   </si>
   <si>
     <t xml:space="preserve">JOB-MESSAGES</t>
@@ -2433,7 +2469,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P84"/>
+  <dimension ref="A1:P85"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.78"/>
@@ -2442,7 +2478,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="106.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="65.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="73.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="58.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="58.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="127.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="129.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="102.03"/>
@@ -3486,585 +3522,579 @@
         <v>209</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>6</v>
+        <v>210</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>20</v>
+        <v>212</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>20</v>
+        <v>213</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>20</v>
+        <v>215</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="J24" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L24" s="0" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M24" s="0" t="s">
-        <v>214</v>
+        <v>218</v>
+      </c>
+      <c r="O24" s="0" t="s">
+        <v>219</v>
       </c>
       <c r="P24" s="0" t="s">
-        <v>79</v>
+        <v>220</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>217</v>
+        <v>6</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E25" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>219</v>
+        <v>20</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>167</v>
+        <v>224</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>168</v>
+        <v>20</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="J25" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="M25" s="0" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="P25" s="0" t="s">
-        <v>223</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>228</v>
+        <v>20</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>230</v>
+        <v>167</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="J26" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L26" s="0" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M26" s="0" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P26" s="0" t="s">
-        <v>140</v>
+        <v>236</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="H27" s="0" t="s">
         <v>125</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="J27" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="M27" s="0" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="P27" s="0" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
+        <v>247</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="D28" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="E28" s="0" t="s">
+        <v>250</v>
+      </c>
+      <c r="F28" s="0" t="s">
         <v>242</v>
       </c>
-      <c r="B28" s="0" t="s">
-        <v>225</v>
-      </c>
-      <c r="C28" s="0" t="s">
-        <v>243</v>
-      </c>
-      <c r="D28" s="0" t="s">
-        <v>244</v>
-      </c>
-      <c r="E28" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="F28" s="0" t="s">
-        <v>245</v>
-      </c>
       <c r="G28" s="0" t="s">
-        <v>20</v>
+        <v>251</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>246</v>
+        <v>125</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="J28" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L28" s="0" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="M28" s="0" t="s">
-        <v>249</v>
-      </c>
-      <c r="O28" s="0" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="P28" s="0" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E29" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="G29" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="J29" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="M29" s="0" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="O29" s="0" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="P29" s="0" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="E30" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="0" t="s">
         <v>258</v>
       </c>
-      <c r="B30" s="0" t="s">
-        <v>225</v>
-      </c>
-      <c r="C30" s="0" t="s">
+      <c r="G30" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="0" t="s">
         <v>259</v>
       </c>
-      <c r="D30" s="0" t="s">
-        <v>260</v>
-      </c>
-      <c r="E30" s="0" t="s">
-        <v>237</v>
-      </c>
-      <c r="F30" s="0" t="s">
-        <v>229</v>
-      </c>
-      <c r="G30" s="0" t="s">
-        <v>261</v>
-      </c>
-      <c r="H30" s="0" t="s">
-        <v>125</v>
-      </c>
       <c r="I30" s="0" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="J30" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L30" s="0" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="M30" s="0" t="s">
-        <v>264</v>
+        <v>269</v>
+      </c>
+      <c r="O30" s="0" t="s">
+        <v>270</v>
       </c>
       <c r="P30" s="0" t="s">
-        <v>265</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>20</v>
+        <v>274</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>246</v>
+        <v>125</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="J31" s="0" t="s">
-        <v>271</v>
+        <v>53</v>
       </c>
       <c r="L31" s="0" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="M31" s="0" t="s">
-        <v>273</v>
-      </c>
-      <c r="O31" s="0" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="P31" s="0" t="s">
-        <v>223</v>
+        <v>278</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E32" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="G32" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J32" s="0" t="s">
-        <v>53</v>
+        <v>284</v>
       </c>
       <c r="L32" s="0" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="M32" s="0" t="s">
-        <v>282</v>
+        <v>286</v>
+      </c>
+      <c r="O32" s="0" t="s">
+        <v>287</v>
       </c>
       <c r="P32" s="0" t="s">
-        <v>163</v>
+        <v>236</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>284</v>
+        <v>238</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>217</v>
+        <v>289</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E33" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>20</v>
+        <v>291</v>
       </c>
       <c r="G33" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="J33" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L33" s="0" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="M33" s="0" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="P33" s="0" t="s">
-        <v>290</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>293</v>
+        <v>230</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E34" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>295</v>
+        <v>20</v>
       </c>
       <c r="G34" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="J34" s="0" t="s">
-        <v>298</v>
-      </c>
-      <c r="K34" s="1" t="n">
-        <v>46234</v>
+        <v>53</v>
       </c>
       <c r="L34" s="0" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M34" s="0" t="s">
-        <v>300</v>
-      </c>
-      <c r="N34" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="O34" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P34" s="0" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="C35" s="0" t="s">
+        <v>306</v>
+      </c>
+      <c r="D35" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="E35" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F35" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="G35" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="I35" s="0" t="s">
+        <v>310</v>
+      </c>
+      <c r="J35" s="0" t="s">
+        <v>311</v>
+      </c>
+      <c r="K35" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="L35" s="0" t="s">
+        <v>312</v>
+      </c>
+      <c r="M35" s="0" t="s">
+        <v>313</v>
+      </c>
+      <c r="N35" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="O35" s="0" t="s">
+        <v>314</v>
+      </c>
+      <c r="P35" s="0" t="s">
         <v>303</v>
-      </c>
-      <c r="D35" s="0" t="s">
-        <v>304</v>
-      </c>
-      <c r="E35" s="0" t="s">
-        <v>305</v>
-      </c>
-      <c r="F35" s="0" t="s">
-        <v>306</v>
-      </c>
-      <c r="G35" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="H35" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="I35" s="0" t="s">
-        <v>307</v>
-      </c>
-      <c r="J35" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="K35" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="L35" s="0" t="s">
-        <v>308</v>
-      </c>
-      <c r="M35" s="0" t="s">
-        <v>309</v>
-      </c>
-      <c r="N35" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="O35" s="0" t="s">
-        <v>310</v>
-      </c>
-      <c r="P35" s="0" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>20</v>
+        <v>318</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="H36" s="0" t="s">
         <v>26</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="J36" s="0" t="s">
-        <v>316</v>
+        <v>86</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="L36" s="0" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="M36" s="0" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="N36" s="0" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="O36" s="0" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="P36" s="0" t="s">
-        <v>118</v>
+        <v>278</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E37" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G37" s="0" t="s">
         <v>20</v>
@@ -4073,48 +4103,48 @@
         <v>26</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="J37" s="0" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="K37" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="M37" s="0" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="N37" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O37" s="0" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="P37" s="0" t="s">
-        <v>57</v>
+        <v>118</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="E38" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="G38" s="0" t="s">
         <v>20</v>
@@ -4123,48 +4153,48 @@
         <v>26</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="J38" s="0" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="K38" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L38" s="0" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="M38" s="0" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="N38" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O38" s="0" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="P38" s="0" t="s">
-        <v>290</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="E39" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="G39" s="0" t="s">
         <v>20</v>
@@ -4173,251 +4203,251 @@
         <v>26</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="J39" s="0" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="K39" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L39" s="0" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="M39" s="0" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="N39" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O39" s="0" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="P39" s="0" t="s">
-        <v>163</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>343</v>
+        <v>20</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="H40" s="0" t="s">
         <v>26</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="J40" s="0" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="K40" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L40" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="M40" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="N40" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O40" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="P40" s="0" t="s">
-        <v>350</v>
+        <v>163</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>20</v>
+        <v>356</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>20</v>
+        <v>358</v>
       </c>
       <c r="H41" s="0" t="s">
         <v>26</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J41" s="0" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="K41" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L41" s="0" t="s">
-        <v>317</v>
+        <v>360</v>
       </c>
       <c r="M41" s="0" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="N41" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O41" s="0" t="s">
-        <v>319</v>
+        <v>362</v>
       </c>
       <c r="P41" s="0" t="s">
-        <v>118</v>
+        <v>220</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>360</v>
+        <v>20</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>362</v>
+        <v>20</v>
       </c>
       <c r="H42" s="0" t="s">
         <v>26</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="J42" s="0" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="K42" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="L42" s="0" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="M42" s="0" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="N42" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O42" s="0" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="P42" s="0" t="s">
-        <v>365</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>367</v>
+        <v>305</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>373</v>
+        <v>26</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J43" s="0" t="s">
-        <v>375</v>
+        <v>329</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46238</v>
+        <v>46232</v>
       </c>
       <c r="L43" s="0" t="s">
+        <v>330</v>
+      </c>
+      <c r="M43" s="0" t="s">
         <v>376</v>
-      </c>
-      <c r="M43" s="0" t="s">
-        <v>377</v>
       </c>
       <c r="N43" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O43" s="0" t="s">
-        <v>378</v>
+        <v>332</v>
       </c>
       <c r="P43" s="0" t="s">
-        <v>118</v>
+        <v>377</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="B44" s="0" t="s">
         <v>379</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="C44" s="0" t="s">
         <v>380</v>
       </c>
-      <c r="C44" s="0" t="s">
+      <c r="D44" s="0" t="s">
         <v>381</v>
       </c>
-      <c r="D44" s="0" t="s">
+      <c r="E44" s="0" t="s">
         <v>382</v>
       </c>
-      <c r="E44" s="0" t="s">
+      <c r="F44" s="0" t="s">
         <v>383</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="G44" s="0" t="s">
         <v>384</v>
-      </c>
-      <c r="G44" s="0" t="s">
-        <v>20</v>
       </c>
       <c r="H44" s="0" t="s">
         <v>385</v>
@@ -4428,90 +4458,90 @@
       <c r="J44" s="0" t="s">
         <v>387</v>
       </c>
+      <c r="K44" s="1" t="n">
+        <v>46238</v>
+      </c>
       <c r="L44" s="0" t="s">
         <v>388</v>
       </c>
       <c r="M44" s="0" t="s">
         <v>389</v>
       </c>
+      <c r="N44" s="0" t="s">
+        <v>77</v>
+      </c>
       <c r="O44" s="0" t="s">
         <v>390</v>
       </c>
       <c r="P44" s="0" t="s">
-        <v>391</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
+        <v>391</v>
+      </c>
+      <c r="B45" s="0" t="s">
         <v>392</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="C45" s="0" t="s">
         <v>393</v>
       </c>
-      <c r="C45" s="0" t="s">
+      <c r="D45" s="0" t="s">
         <v>394</v>
       </c>
-      <c r="D45" s="0" t="s">
+      <c r="E45" s="0" t="s">
         <v>395</v>
       </c>
-      <c r="E45" s="0" t="s">
+      <c r="F45" s="0" t="s">
         <v>396</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="G45" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H45" s="0" t="s">
         <v>397</v>
       </c>
-      <c r="G45" s="0" t="s">
+      <c r="I45" s="0" t="s">
         <v>398</v>
       </c>
-      <c r="H45" s="0" t="s">
+      <c r="J45" s="0" t="s">
         <v>399</v>
       </c>
-      <c r="I45" s="0" t="s">
+      <c r="L45" s="0" t="s">
         <v>400</v>
       </c>
-      <c r="J45" s="0" t="s">
+      <c r="M45" s="0" t="s">
         <v>401</v>
       </c>
-      <c r="K45" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="L45" s="0" t="s">
+      <c r="O45" s="0" t="s">
         <v>402</v>
       </c>
-      <c r="M45" s="0" t="s">
+      <c r="P45" s="0" t="s">
         <v>403</v>
-      </c>
-      <c r="N45" s="0" t="s">
-        <v>404</v>
-      </c>
-      <c r="O45" s="0" t="s">
-        <v>405</v>
-      </c>
-      <c r="P45" s="0" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
+        <v>404</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>405</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>406</v>
+      </c>
+      <c r="D46" s="0" t="s">
         <v>407</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="E46" s="0" t="s">
         <v>408</v>
       </c>
-      <c r="C46" s="0" t="s">
+      <c r="F46" s="0" t="s">
         <v>409</v>
       </c>
-      <c r="D46" s="0" t="s">
+      <c r="G46" s="0" t="s">
         <v>410</v>
-      </c>
-      <c r="E46" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="F46" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="G46" s="0" t="s">
-        <v>20</v>
       </c>
       <c r="H46" s="0" t="s">
         <v>411</v>
@@ -4555,34 +4585,40 @@
         <v>422</v>
       </c>
       <c r="E47" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F47" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G47" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H47" s="0" t="s">
         <v>423</v>
       </c>
-      <c r="F47" s="0" t="s">
+      <c r="I47" s="0" t="s">
         <v>424</v>
       </c>
-      <c r="G47" s="0" t="s">
+      <c r="J47" s="0" t="s">
         <v>425</v>
       </c>
-      <c r="H47" s="0" t="s">
+      <c r="K47" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L47" s="0" t="s">
         <v>426</v>
       </c>
-      <c r="I47" s="0" t="s">
+      <c r="M47" s="0" t="s">
         <v>427</v>
       </c>
-      <c r="J47" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="L47" s="0" t="s">
+      <c r="N47" s="0" t="s">
         <v>428</v>
       </c>
-      <c r="M47" s="0" t="s">
+      <c r="O47" s="0" t="s">
         <v>429</v>
       </c>
-      <c r="O47" s="0" t="s">
+      <c r="P47" s="0" t="s">
         <v>430</v>
-      </c>
-      <c r="P47" s="0" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4590,855 +4626,855 @@
         <v>431</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="J48" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L48" s="0" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="M48" s="0" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="O48" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="P48" s="0" t="s">
-        <v>140</v>
+        <v>236</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J49" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L49" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M49" s="0" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O49" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P49" s="0" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>425</v>
+        <v>457</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="J50" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L50" s="0" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="M50" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="O50" s="0" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="P50" s="0" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>421</v>
+        <v>464</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="G51" s="0" t="s">
-        <v>465</v>
+        <v>437</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="J51" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L51" s="0" t="s">
-        <v>428</v>
+        <v>470</v>
       </c>
       <c r="M51" s="0" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="O51" s="0" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="P51" s="0" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>471</v>
+        <v>433</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>434</v>
+        <v>476</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>425</v>
+        <v>477</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="J52" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L52" s="0" t="s">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="M52" s="0" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="O52" s="0" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="P52" s="0" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>482</v>
+        <v>446</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="J53" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="M53" s="0" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="O53" s="0" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="P53" s="0" t="s">
-        <v>350</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="J54" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L54" s="0" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="M54" s="0" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="O54" s="0" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="P54" s="0" t="s">
-        <v>163</v>
+        <v>220</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>498</v>
+        <v>483</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>502</v>
+        <v>437</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="J55" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M55" s="0" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O55" s="0" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P55" s="0" t="s">
-        <v>350</v>
+        <v>163</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>20</v>
+        <v>512</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>20</v>
+        <v>513</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>20</v>
+        <v>514</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>20</v>
+        <v>515</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="J56" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L56" s="0" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="M56" s="0" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="O56" s="0" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="P56" s="0" t="s">
-        <v>101</v>
+        <v>220</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>518</v>
+        <v>20</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>519</v>
+        <v>20</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>520</v>
+        <v>20</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="J57" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M57" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O57" s="0" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P57" s="0" t="s">
-        <v>163</v>
+        <v>101</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>20</v>
+        <v>530</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>20</v>
+        <v>531</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>20</v>
+        <v>532</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>20</v>
+        <v>533</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="J58" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L58" s="0" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M58" s="0" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="O58" s="0" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="P58" s="0" t="s">
-        <v>406</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>516</v>
+        <v>539</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>535</v>
+        <v>20</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>536</v>
+        <v>20</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>537</v>
+        <v>20</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>538</v>
+        <v>20</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="J59" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="M59" s="0" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O59" s="0" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="P59" s="0" t="s">
-        <v>365</v>
+        <v>418</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="J60" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L60" s="0" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M60" s="0" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="O60" s="0" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="P60" s="0" t="s">
-        <v>406</v>
+        <v>377</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="J61" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="M61" s="0" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="O61" s="0" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="P61" s="0" t="s">
-        <v>365</v>
+        <v>418</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>20</v>
+        <v>568</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="J62" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L62" s="0" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="M62" s="0" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="O62" s="0" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="P62" s="0" t="s">
-        <v>406</v>
+        <v>377</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>20</v>
+        <v>578</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>20</v>
+        <v>579</v>
       </c>
       <c r="G63" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>20</v>
+        <v>580</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="J63" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="M63" s="0" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="O63" s="0" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="P63" s="0" t="s">
-        <v>140</v>
+        <v>418</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>582</v>
+        <v>20</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>583</v>
+        <v>20</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>584</v>
+        <v>20</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>585</v>
+        <v>20</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="J64" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L64" s="0" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="M64" s="0" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="O64" s="0" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="P64" s="0" t="s">
-        <v>350</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="J65" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="M65" s="0" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="O65" s="0" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="P65" s="0" t="s">
-        <v>140</v>
+        <v>220</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>601</v>
+        <v>586</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>20</v>
+        <v>606</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>20</v>
+        <v>607</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="J66" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L66" s="0" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="M66" s="0" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="O66" s="0" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="P66" s="0" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>20</v>
+        <v>615</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="G67" s="0" t="s">
         <v>20</v>
@@ -5447,171 +5483,171 @@
         <v>20</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="J67" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="M67" s="0" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="O67" s="0" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="P67" s="0" t="s">
-        <v>185</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E68" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>621</v>
+        <v>20</v>
       </c>
       <c r="H68" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="J68" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L68" s="0" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="M68" s="0" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="O68" s="0" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="P68" s="0" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>629</v>
+        <v>20</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>425</v>
+        <v>633</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>631</v>
+        <v>20</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="J69" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="M69" s="0" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="O69" s="0" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="P69" s="0" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>20</v>
+        <v>641</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>20</v>
+        <v>642</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>20</v>
+        <v>437</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>20</v>
+        <v>643</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="J70" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L70" s="0" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="M70" s="0" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="O70" s="0" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="P70" s="0" t="s">
-        <v>350</v>
+        <v>150</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>644</v>
+        <v>20</v>
       </c>
       <c r="F71" s="0" t="s">
         <v>20</v>
@@ -5623,327 +5659,327 @@
         <v>20</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="J71" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="M71" s="0" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="O71" s="0" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="P71" s="0" t="s">
-        <v>365</v>
+        <v>220</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>650</v>
+        <v>639</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>653</v>
+        <v>20</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>654</v>
+        <v>20</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>655</v>
+        <v>20</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="J72" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L72" s="0" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M72" s="0" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="O72" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="P72" s="0" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="J73" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>458</v>
+        <v>669</v>
       </c>
       <c r="M73" s="0" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="O73" s="0" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="P73" s="0" t="s">
-        <v>140</v>
+        <v>377</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>443</v>
+        <v>675</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="J74" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>675</v>
+        <v>470</v>
       </c>
       <c r="M74" s="0" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="O74" s="0" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="P74" s="0" t="s">
-        <v>350</v>
+        <v>140</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>680</v>
+        <v>455</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="J75" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="M75" s="0" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="O75" s="0" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="P75" s="0" t="s">
-        <v>365</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>689</v>
+        <v>673</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>20</v>
+        <v>694</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>521</v>
+        <v>695</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="J76" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L76" s="0" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="M76" s="0" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="O76" s="0" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="P76" s="0" t="s">
-        <v>140</v>
+        <v>377</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="G77" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>700</v>
+        <v>533</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="J77" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="M77" s="0" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="O77" s="0" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="P77" s="0" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="G78" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="J78" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L78" s="0" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="M78" s="0" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="O78" s="0" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="P78" s="0" t="s">
         <v>163</v>
@@ -5951,272 +5987,316 @@
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>20</v>
+        <v>720</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="G79" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="J79" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L79" s="0" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="M79" s="0" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="O79" s="0" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="P79" s="0" t="s">
-        <v>406</v>
+        <v>163</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>727</v>
+        <v>20</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>654</v>
+        <v>20</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="J80" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L80" s="0" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="M80" s="0" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="O80" s="0" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="P80" s="0" t="s">
-        <v>163</v>
+        <v>418</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>20</v>
+        <v>739</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>20</v>
+        <v>740</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>20</v>
+        <v>666</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>20</v>
+        <v>741</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="J81" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="M81" s="0" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="O81" s="0" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="P81" s="0" t="s">
-        <v>350</v>
+        <v>163</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>744</v>
+        <v>20</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>745</v>
+        <v>20</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>425</v>
+        <v>20</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>746</v>
+        <v>20</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="J82" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L82" s="0" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="M82" s="0" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="O82" s="0" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="P82" s="0" t="s">
-        <v>365</v>
+        <v>220</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="J83" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="M83" s="0" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="O83" s="0" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="P83" s="0" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>762</v>
+        <v>432</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>20</v>
+        <v>766</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>20</v>
+        <v>767</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>20</v>
+        <v>437</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>20</v>
+        <v>768</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="J84" s="0" t="s">
-        <v>766</v>
-      </c>
-      <c r="K84" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="L84" s="0" t="s">
+        <v>770</v>
+      </c>
+      <c r="M84" s="0" t="s">
+        <v>771</v>
+      </c>
+      <c r="O84" s="0" t="s">
+        <v>772</v>
+      </c>
+      <c r="P84" s="0" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="0" t="s">
+        <v>773</v>
+      </c>
+      <c r="B85" s="0" t="s">
+        <v>774</v>
+      </c>
+      <c r="C85" s="0" t="s">
+        <v>775</v>
+      </c>
+      <c r="D85" s="0" t="s">
+        <v>776</v>
+      </c>
+      <c r="E85" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F85" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G85" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H85" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I85" s="0" t="s">
+        <v>777</v>
+      </c>
+      <c r="J85" s="0" t="s">
+        <v>778</v>
+      </c>
+      <c r="K85" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="L84" s="0" t="s">
-        <v>767</v>
-      </c>
-      <c r="M84" s="0" t="s">
-        <v>768</v>
-      </c>
-      <c r="N84" s="0" t="s">
-        <v>769</v>
-      </c>
-      <c r="O84" s="0" t="s">
-        <v>770</v>
-      </c>
-      <c r="P84" s="0" t="s">
-        <v>223</v>
+      <c r="L85" s="0" t="s">
+        <v>779</v>
+      </c>
+      <c r="M85" s="0" t="s">
+        <v>780</v>
+      </c>
+      <c r="N85" s="0" t="s">
+        <v>781</v>
+      </c>
+      <c r="O85" s="0" t="s">
+        <v>782</v>
+      </c>
+      <c r="P85" s="0" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
+++ b/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="790">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -1109,6 +1109,27 @@
   </si>
   <si>
     <t xml:space="preserve">Primary domain oracle passed; graph UI not manually qualified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOB-GRAPH-LAYOUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">affinity-graph-layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real daily worker materializes the current Admin Affinity Graph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA new layoutVersion and matching node/edge/forest totals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focused worker and graph materialization tests; real dev scheduler smoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hold the daily rule, shorten the persisted schedule, capture the scheduled run, then reopen the graph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The same worker and persisted one-day rule run in demo_db and myscoutee_db; the manual helper never calls the rebuild endpoint. Non-manual runtime evidence on 2026-08-04: automatic demo seed sync imported the tenth rule and the real scheduler completed it in 231 ms, publishing one version with 54 nodes, 1126 edges and 4 forests whose stored counts matched the layout header. Manual screenshot checkpoints remain NOT RUN.</t>
   </si>
   <si>
     <t xml:space="preserve">JOB-MESSAGES</t>
@@ -2384,6 +2405,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2469,14 +2491,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P85"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:P86"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="106.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="65.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="106.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="65.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="73.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="58.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="127.59"/>
@@ -4344,66 +4366,61 @@
         <v>20</v>
       </c>
       <c r="F42" s="0" t="s">
+        <v>342</v>
+      </c>
+      <c r="G42" s="0" t="s">
         <v>366</v>
-      </c>
-      <c r="G42" s="0" t="s">
-        <v>20</v>
       </c>
       <c r="H42" s="0" t="s">
         <v>26</v>
       </c>
       <c r="I42" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="K42" s="1"/>
+      <c r="L42" s="0" t="s">
         <v>367</v>
-      </c>
-      <c r="J42" s="0" t="s">
-        <v>329</v>
-      </c>
-      <c r="K42" s="1" t="n">
-        <v>46232</v>
-      </c>
-      <c r="L42" s="0" t="s">
-        <v>330</v>
       </c>
       <c r="M42" s="0" t="s">
         <v>368</v>
       </c>
-      <c r="N42" s="0" t="s">
-        <v>77</v>
-      </c>
       <c r="O42" s="0" t="s">
-        <v>332</v>
+        <v>369</v>
       </c>
       <c r="P42" s="0" t="s">
-        <v>118</v>
+        <v>220</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B43" s="0" t="s">
         <v>305</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>372</v>
+        <v>20</v>
       </c>
       <c r="F43" s="0" t="s">
         <v>373</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>374</v>
+        <v>20</v>
       </c>
       <c r="H43" s="0" t="s">
         <v>26</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J43" s="0" t="s">
         <v>329</v>
@@ -4415,7 +4432,7 @@
         <v>330</v>
       </c>
       <c r="M43" s="0" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N43" s="0" t="s">
         <v>77</v>
@@ -4424,623 +4441,629 @@
         <v>332</v>
       </c>
       <c r="P43" s="0" t="s">
-        <v>377</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
+        <v>376</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>305</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="D44" s="0" t="s">
         <v>378</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="E44" s="0" t="s">
         <v>379</v>
       </c>
-      <c r="C44" s="0" t="s">
+      <c r="F44" s="0" t="s">
         <v>380</v>
       </c>
-      <c r="D44" s="0" t="s">
+      <c r="G44" s="0" t="s">
         <v>381</v>
       </c>
-      <c r="E44" s="0" t="s">
+      <c r="H44" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="I44" s="0" t="s">
         <v>382</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="J44" s="0" t="s">
+        <v>329</v>
+      </c>
+      <c r="K44" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="L44" s="0" t="s">
+        <v>330</v>
+      </c>
+      <c r="M44" s="0" t="s">
         <v>383</v>
-      </c>
-      <c r="G44" s="0" t="s">
-        <v>384</v>
-      </c>
-      <c r="H44" s="0" t="s">
-        <v>385</v>
-      </c>
-      <c r="I44" s="0" t="s">
-        <v>386</v>
-      </c>
-      <c r="J44" s="0" t="s">
-        <v>387</v>
-      </c>
-      <c r="K44" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="L44" s="0" t="s">
-        <v>388</v>
-      </c>
-      <c r="M44" s="0" t="s">
-        <v>389</v>
       </c>
       <c r="N44" s="0" t="s">
         <v>77</v>
       </c>
       <c r="O44" s="0" t="s">
-        <v>390</v>
+        <v>332</v>
       </c>
       <c r="P44" s="0" t="s">
-        <v>118</v>
+        <v>384</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
+        <v>385</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>386</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>387</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>388</v>
+      </c>
+      <c r="E45" s="0" t="s">
+        <v>389</v>
+      </c>
+      <c r="F45" s="0" t="s">
+        <v>390</v>
+      </c>
+      <c r="G45" s="0" t="s">
         <v>391</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="H45" s="0" t="s">
         <v>392</v>
       </c>
-      <c r="C45" s="0" t="s">
+      <c r="I45" s="0" t="s">
         <v>393</v>
       </c>
-      <c r="D45" s="0" t="s">
+      <c r="J45" s="0" t="s">
         <v>394</v>
       </c>
-      <c r="E45" s="0" t="s">
+      <c r="K45" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L45" s="0" t="s">
         <v>395</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="M45" s="0" t="s">
         <v>396</v>
       </c>
-      <c r="G45" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="H45" s="0" t="s">
+      <c r="N45" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="O45" s="0" t="s">
         <v>397</v>
       </c>
-      <c r="I45" s="0" t="s">
-        <v>398</v>
-      </c>
-      <c r="J45" s="0" t="s">
-        <v>399</v>
-      </c>
-      <c r="L45" s="0" t="s">
-        <v>400</v>
-      </c>
-      <c r="M45" s="0" t="s">
-        <v>401</v>
-      </c>
-      <c r="O45" s="0" t="s">
-        <v>402</v>
-      </c>
       <c r="P45" s="0" t="s">
-        <v>403</v>
+        <v>118</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
+        <v>398</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>399</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>400</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>401</v>
+      </c>
+      <c r="E46" s="0" t="s">
+        <v>402</v>
+      </c>
+      <c r="F46" s="0" t="s">
+        <v>403</v>
+      </c>
+      <c r="G46" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" s="0" t="s">
         <v>404</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="I46" s="0" t="s">
         <v>405</v>
       </c>
-      <c r="C46" s="0" t="s">
+      <c r="J46" s="0" t="s">
         <v>406</v>
       </c>
-      <c r="D46" s="0" t="s">
+      <c r="L46" s="0" t="s">
         <v>407</v>
       </c>
-      <c r="E46" s="0" t="s">
+      <c r="M46" s="0" t="s">
         <v>408</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="O46" s="0" t="s">
         <v>409</v>
       </c>
-      <c r="G46" s="0" t="s">
+      <c r="P46" s="0" t="s">
         <v>410</v>
-      </c>
-      <c r="H46" s="0" t="s">
-        <v>411</v>
-      </c>
-      <c r="I46" s="0" t="s">
-        <v>412</v>
-      </c>
-      <c r="J46" s="0" t="s">
-        <v>413</v>
-      </c>
-      <c r="K46" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="L46" s="0" t="s">
-        <v>414</v>
-      </c>
-      <c r="M46" s="0" t="s">
-        <v>415</v>
-      </c>
-      <c r="N46" s="0" t="s">
-        <v>416</v>
-      </c>
-      <c r="O46" s="0" t="s">
-        <v>417</v>
-      </c>
-      <c r="P46" s="0" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
+        <v>411</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>412</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>413</v>
+      </c>
+      <c r="D47" s="0" t="s">
+        <v>414</v>
+      </c>
+      <c r="E47" s="0" t="s">
+        <v>415</v>
+      </c>
+      <c r="F47" s="0" t="s">
+        <v>416</v>
+      </c>
+      <c r="G47" s="0" t="s">
+        <v>417</v>
+      </c>
+      <c r="H47" s="0" t="s">
+        <v>418</v>
+      </c>
+      <c r="I47" s="0" t="s">
         <v>419</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="J47" s="0" t="s">
         <v>420</v>
-      </c>
-      <c r="C47" s="0" t="s">
-        <v>421</v>
-      </c>
-      <c r="D47" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="E47" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="F47" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="G47" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="H47" s="0" t="s">
-        <v>423</v>
-      </c>
-      <c r="I47" s="0" t="s">
-        <v>424</v>
-      </c>
-      <c r="J47" s="0" t="s">
-        <v>425</v>
       </c>
       <c r="K47" s="1" t="n">
         <v>46238</v>
       </c>
       <c r="L47" s="0" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="M47" s="0" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="N47" s="0" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="O47" s="0" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="P47" s="0" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
+        <v>426</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>428</v>
+      </c>
+      <c r="D48" s="0" t="s">
+        <v>429</v>
+      </c>
+      <c r="E48" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F48" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G48" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H48" s="0" t="s">
+        <v>430</v>
+      </c>
+      <c r="I48" s="0" t="s">
         <v>431</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="J48" s="0" t="s">
         <v>432</v>
       </c>
-      <c r="C48" s="0" t="s">
+      <c r="K48" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L48" s="0" t="s">
         <v>433</v>
       </c>
-      <c r="D48" s="0" t="s">
+      <c r="M48" s="0" t="s">
         <v>434</v>
       </c>
-      <c r="E48" s="0" t="s">
+      <c r="N48" s="0" t="s">
         <v>435</v>
       </c>
-      <c r="F48" s="0" t="s">
+      <c r="O48" s="0" t="s">
         <v>436</v>
       </c>
-      <c r="G48" s="0" t="s">
+      <c r="P48" s="0" t="s">
         <v>437</v>
-      </c>
-      <c r="H48" s="0" t="s">
-        <v>438</v>
-      </c>
-      <c r="I48" s="0" t="s">
-        <v>439</v>
-      </c>
-      <c r="J48" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="L48" s="0" t="s">
-        <v>440</v>
-      </c>
-      <c r="M48" s="0" t="s">
-        <v>441</v>
-      </c>
-      <c r="O48" s="0" t="s">
-        <v>442</v>
-      </c>
-      <c r="P48" s="0" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="D49" s="0" t="s">
+        <v>441</v>
+      </c>
+      <c r="E49" s="0" t="s">
+        <v>442</v>
+      </c>
+      <c r="F49" s="0" t="s">
         <v>443</v>
       </c>
-      <c r="B49" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C49" s="0" t="s">
-        <v>433</v>
-      </c>
-      <c r="D49" s="0" t="s">
+      <c r="G49" s="0" t="s">
         <v>444</v>
       </c>
-      <c r="E49" s="0" t="s">
+      <c r="H49" s="0" t="s">
         <v>445</v>
       </c>
-      <c r="F49" s="0" t="s">
+      <c r="I49" s="0" t="s">
         <v>446</v>
-      </c>
-      <c r="G49" s="0" t="s">
-        <v>437</v>
-      </c>
-      <c r="H49" s="0" t="s">
-        <v>447</v>
-      </c>
-      <c r="I49" s="0" t="s">
-        <v>448</v>
       </c>
       <c r="J49" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L49" s="0" t="s">
+        <v>447</v>
+      </c>
+      <c r="M49" s="0" t="s">
+        <v>448</v>
+      </c>
+      <c r="O49" s="0" t="s">
         <v>449</v>
       </c>
-      <c r="M49" s="0" t="s">
-        <v>450</v>
-      </c>
-      <c r="O49" s="0" t="s">
-        <v>451</v>
-      </c>
       <c r="P49" s="0" t="s">
-        <v>140</v>
+        <v>236</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
+        <v>450</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="D50" s="0" t="s">
+        <v>451</v>
+      </c>
+      <c r="E50" s="0" t="s">
         <v>452</v>
       </c>
-      <c r="B50" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C50" s="0" t="s">
+      <c r="F50" s="0" t="s">
         <v>453</v>
       </c>
-      <c r="D50" s="0" t="s">
+      <c r="G50" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="H50" s="0" t="s">
         <v>454</v>
       </c>
-      <c r="E50" s="0" t="s">
+      <c r="I50" s="0" t="s">
         <v>455</v>
-      </c>
-      <c r="F50" s="0" t="s">
-        <v>456</v>
-      </c>
-      <c r="G50" s="0" t="s">
-        <v>457</v>
-      </c>
-      <c r="H50" s="0" t="s">
-        <v>458</v>
-      </c>
-      <c r="I50" s="0" t="s">
-        <v>459</v>
       </c>
       <c r="J50" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L50" s="0" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="M50" s="0" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="O50" s="0" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="P50" s="0" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
+        <v>459</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>460</v>
+      </c>
+      <c r="D51" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="E51" s="0" t="s">
+        <v>462</v>
+      </c>
+      <c r="F51" s="0" t="s">
         <v>463</v>
       </c>
-      <c r="B51" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C51" s="0" t="s">
+      <c r="G51" s="0" t="s">
         <v>464</v>
       </c>
-      <c r="D51" s="0" t="s">
+      <c r="H51" s="0" t="s">
         <v>465</v>
       </c>
-      <c r="E51" s="0" t="s">
+      <c r="I51" s="0" t="s">
         <v>466</v>
-      </c>
-      <c r="F51" s="0" t="s">
-        <v>467</v>
-      </c>
-      <c r="G51" s="0" t="s">
-        <v>437</v>
-      </c>
-      <c r="H51" s="0" t="s">
-        <v>468</v>
-      </c>
-      <c r="I51" s="0" t="s">
-        <v>469</v>
       </c>
       <c r="J51" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L51" s="0" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="M51" s="0" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="O51" s="0" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="P51" s="0" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
+        <v>470</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C52" s="0" t="s">
+        <v>471</v>
+      </c>
+      <c r="D52" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="E52" s="0" t="s">
         <v>473</v>
       </c>
-      <c r="B52" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C52" s="0" t="s">
-        <v>433</v>
-      </c>
-      <c r="D52" s="0" t="s">
+      <c r="F52" s="0" t="s">
         <v>474</v>
       </c>
-      <c r="E52" s="0" t="s">
+      <c r="G52" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="H52" s="0" t="s">
         <v>475</v>
       </c>
-      <c r="F52" s="0" t="s">
+      <c r="I52" s="0" t="s">
         <v>476</v>
-      </c>
-      <c r="G52" s="0" t="s">
-        <v>477</v>
-      </c>
-      <c r="H52" s="0" t="s">
-        <v>478</v>
-      </c>
-      <c r="I52" s="0" t="s">
-        <v>479</v>
       </c>
       <c r="J52" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L52" s="0" t="s">
-        <v>440</v>
+        <v>477</v>
       </c>
       <c r="M52" s="0" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="O52" s="0" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="P52" s="0" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
+        <v>480</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C53" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="D53" s="0" t="s">
+        <v>481</v>
+      </c>
+      <c r="E53" s="0" t="s">
         <v>482</v>
       </c>
-      <c r="B53" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C53" s="0" t="s">
+      <c r="F53" s="0" t="s">
         <v>483</v>
       </c>
-      <c r="D53" s="0" t="s">
+      <c r="G53" s="0" t="s">
         <v>484</v>
       </c>
-      <c r="E53" s="0" t="s">
+      <c r="H53" s="0" t="s">
         <v>485</v>
       </c>
-      <c r="F53" s="0" t="s">
-        <v>446</v>
-      </c>
-      <c r="G53" s="0" t="s">
-        <v>437</v>
-      </c>
-      <c r="H53" s="0" t="s">
+      <c r="I53" s="0" t="s">
         <v>486</v>
-      </c>
-      <c r="I53" s="0" t="s">
-        <v>487</v>
       </c>
       <c r="J53" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L53" s="0" t="s">
+        <v>447</v>
+      </c>
+      <c r="M53" s="0" t="s">
+        <v>487</v>
+      </c>
+      <c r="O53" s="0" t="s">
         <v>488</v>
       </c>
-      <c r="M53" s="0" t="s">
-        <v>489</v>
-      </c>
-      <c r="O53" s="0" t="s">
-        <v>490</v>
-      </c>
       <c r="P53" s="0" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
+        <v>489</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C54" s="0" t="s">
+        <v>490</v>
+      </c>
+      <c r="D54" s="0" t="s">
         <v>491</v>
       </c>
-      <c r="B54" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C54" s="0" t="s">
-        <v>483</v>
-      </c>
-      <c r="D54" s="0" t="s">
+      <c r="E54" s="0" t="s">
         <v>492</v>
       </c>
-      <c r="E54" s="0" t="s">
+      <c r="F54" s="0" t="s">
+        <v>453</v>
+      </c>
+      <c r="G54" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="H54" s="0" t="s">
         <v>493</v>
       </c>
-      <c r="F54" s="0" t="s">
+      <c r="I54" s="0" t="s">
         <v>494</v>
-      </c>
-      <c r="G54" s="0" t="s">
-        <v>437</v>
-      </c>
-      <c r="H54" s="0" t="s">
-        <v>495</v>
-      </c>
-      <c r="I54" s="0" t="s">
-        <v>496</v>
       </c>
       <c r="J54" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L54" s="0" t="s">
+        <v>495</v>
+      </c>
+      <c r="M54" s="0" t="s">
+        <v>496</v>
+      </c>
+      <c r="O54" s="0" t="s">
         <v>497</v>
       </c>
-      <c r="M54" s="0" t="s">
-        <v>498</v>
-      </c>
-      <c r="O54" s="0" t="s">
-        <v>499</v>
-      </c>
       <c r="P54" s="0" t="s">
-        <v>220</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C55" s="0" t="s">
+        <v>490</v>
+      </c>
+      <c r="D55" s="0" t="s">
+        <v>499</v>
+      </c>
+      <c r="E55" s="0" t="s">
         <v>500</v>
       </c>
-      <c r="B55" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C55" s="0" t="s">
-        <v>483</v>
-      </c>
-      <c r="D55" s="0" t="s">
+      <c r="F55" s="0" t="s">
         <v>501</v>
       </c>
-      <c r="E55" s="0" t="s">
+      <c r="G55" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="H55" s="0" t="s">
         <v>502</v>
       </c>
-      <c r="F55" s="0" t="s">
+      <c r="I55" s="0" t="s">
         <v>503</v>
-      </c>
-      <c r="G55" s="0" t="s">
-        <v>437</v>
-      </c>
-      <c r="H55" s="0" t="s">
-        <v>504</v>
-      </c>
-      <c r="I55" s="0" t="s">
-        <v>505</v>
       </c>
       <c r="J55" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L55" s="0" t="s">
+        <v>504</v>
+      </c>
+      <c r="M55" s="0" t="s">
+        <v>505</v>
+      </c>
+      <c r="O55" s="0" t="s">
         <v>506</v>
       </c>
-      <c r="M55" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="O55" s="0" t="s">
-        <v>508</v>
-      </c>
       <c r="P55" s="0" t="s">
-        <v>163</v>
+        <v>220</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
+        <v>507</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C56" s="0" t="s">
+        <v>490</v>
+      </c>
+      <c r="D56" s="0" t="s">
+        <v>508</v>
+      </c>
+      <c r="E56" s="0" t="s">
         <v>509</v>
       </c>
-      <c r="B56" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C56" s="0" t="s">
+      <c r="F56" s="0" t="s">
         <v>510</v>
       </c>
-      <c r="D56" s="0" t="s">
+      <c r="G56" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="H56" s="0" t="s">
         <v>511</v>
       </c>
-      <c r="E56" s="0" t="s">
+      <c r="I56" s="0" t="s">
         <v>512</v>
-      </c>
-      <c r="F56" s="0" t="s">
-        <v>513</v>
-      </c>
-      <c r="G56" s="0" t="s">
-        <v>514</v>
-      </c>
-      <c r="H56" s="0" t="s">
-        <v>515</v>
-      </c>
-      <c r="I56" s="0" t="s">
-        <v>516</v>
       </c>
       <c r="J56" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L56" s="0" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="M56" s="0" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="O56" s="0" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="P56" s="0" t="s">
-        <v>220</v>
+        <v>163</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
+        <v>516</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C57" s="0" t="s">
+        <v>517</v>
+      </c>
+      <c r="D57" s="0" t="s">
+        <v>518</v>
+      </c>
+      <c r="E57" s="0" t="s">
+        <v>519</v>
+      </c>
+      <c r="F57" s="0" t="s">
         <v>520</v>
       </c>
-      <c r="B57" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C57" s="0" t="s">
+      <c r="G57" s="0" t="s">
         <v>521</v>
       </c>
-      <c r="D57" s="0" t="s">
+      <c r="H57" s="0" t="s">
         <v>522</v>
-      </c>
-      <c r="E57" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="F57" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="G57" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="H57" s="0" t="s">
-        <v>20</v>
       </c>
       <c r="I57" s="0" t="s">
         <v>523</v>
@@ -5058,7 +5081,7 @@
         <v>526</v>
       </c>
       <c r="P57" s="0" t="s">
-        <v>101</v>
+        <v>220</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5066,7 +5089,7 @@
         <v>527</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="C58" s="0" t="s">
         <v>528</v>
@@ -5075,60 +5098,60 @@
         <v>529</v>
       </c>
       <c r="E58" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F58" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G58" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H58" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I58" s="0" t="s">
         <v>530</v>
-      </c>
-      <c r="F58" s="0" t="s">
-        <v>531</v>
-      </c>
-      <c r="G58" s="0" t="s">
-        <v>532</v>
-      </c>
-      <c r="H58" s="0" t="s">
-        <v>533</v>
-      </c>
-      <c r="I58" s="0" t="s">
-        <v>534</v>
       </c>
       <c r="J58" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L58" s="0" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="M58" s="0" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="O58" s="0" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="P58" s="0" t="s">
-        <v>163</v>
+        <v>101</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
+        <v>534</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C59" s="0" t="s">
+        <v>535</v>
+      </c>
+      <c r="D59" s="0" t="s">
+        <v>536</v>
+      </c>
+      <c r="E59" s="0" t="s">
+        <v>537</v>
+      </c>
+      <c r="F59" s="0" t="s">
         <v>538</v>
       </c>
-      <c r="B59" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C59" s="0" t="s">
+      <c r="G59" s="0" t="s">
         <v>539</v>
       </c>
-      <c r="D59" s="0" t="s">
+      <c r="H59" s="0" t="s">
         <v>540</v>
-      </c>
-      <c r="E59" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="F59" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="G59" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="H59" s="0" t="s">
-        <v>20</v>
       </c>
       <c r="I59" s="0" t="s">
         <v>541</v>
@@ -5146,7 +5169,7 @@
         <v>544</v>
       </c>
       <c r="P59" s="0" t="s">
-        <v>418</v>
+        <v>163</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5154,201 +5177,201 @@
         <v>545</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>528</v>
+        <v>546</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>547</v>
+        <v>20</v>
       </c>
       <c r="F60" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G60" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H60" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I60" s="0" t="s">
         <v>548</v>
-      </c>
-      <c r="G60" s="0" t="s">
-        <v>549</v>
-      </c>
-      <c r="H60" s="0" t="s">
-        <v>550</v>
-      </c>
-      <c r="I60" s="0" t="s">
-        <v>551</v>
       </c>
       <c r="J60" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L60" s="0" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="M60" s="0" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="O60" s="0" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="P60" s="0" t="s">
-        <v>377</v>
+        <v>425</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
+        <v>552</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C61" s="0" t="s">
+        <v>535</v>
+      </c>
+      <c r="D61" s="0" t="s">
+        <v>553</v>
+      </c>
+      <c r="E61" s="0" t="s">
+        <v>554</v>
+      </c>
+      <c r="F61" s="0" t="s">
         <v>555</v>
       </c>
-      <c r="B61" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C61" s="0" t="s">
+      <c r="G61" s="0" t="s">
         <v>556</v>
       </c>
-      <c r="D61" s="0" t="s">
+      <c r="H61" s="0" t="s">
         <v>557</v>
       </c>
-      <c r="E61" s="0" t="s">
+      <c r="I61" s="0" t="s">
         <v>558</v>
-      </c>
-      <c r="F61" s="0" t="s">
-        <v>559</v>
-      </c>
-      <c r="G61" s="0" t="s">
-        <v>560</v>
-      </c>
-      <c r="H61" s="0" t="s">
-        <v>550</v>
-      </c>
-      <c r="I61" s="0" t="s">
-        <v>561</v>
       </c>
       <c r="J61" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="M61" s="0" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="O61" s="0" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="P61" s="0" t="s">
-        <v>418</v>
+        <v>384</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
+        <v>562</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C62" s="0" t="s">
+        <v>563</v>
+      </c>
+      <c r="D62" s="0" t="s">
+        <v>564</v>
+      </c>
+      <c r="E62" s="0" t="s">
         <v>565</v>
       </c>
-      <c r="B62" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C62" s="0" t="s">
+      <c r="F62" s="0" t="s">
         <v>566</v>
       </c>
-      <c r="D62" s="0" t="s">
+      <c r="G62" s="0" t="s">
         <v>567</v>
       </c>
-      <c r="E62" s="0" t="s">
+      <c r="H62" s="0" t="s">
+        <v>557</v>
+      </c>
+      <c r="I62" s="0" t="s">
         <v>568</v>
-      </c>
-      <c r="F62" s="0" t="s">
-        <v>569</v>
-      </c>
-      <c r="G62" s="0" t="s">
-        <v>568</v>
-      </c>
-      <c r="H62" s="0" t="s">
-        <v>570</v>
-      </c>
-      <c r="I62" s="0" t="s">
-        <v>571</v>
       </c>
       <c r="J62" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L62" s="0" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="M62" s="0" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="O62" s="0" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="P62" s="0" t="s">
-        <v>377</v>
+        <v>425</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
+        <v>572</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C63" s="0" t="s">
+        <v>573</v>
+      </c>
+      <c r="D63" s="0" t="s">
+        <v>574</v>
+      </c>
+      <c r="E63" s="0" t="s">
         <v>575</v>
       </c>
-      <c r="B63" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C63" s="0" t="s">
+      <c r="F63" s="0" t="s">
         <v>576</v>
       </c>
-      <c r="D63" s="0" t="s">
+      <c r="G63" s="0" t="s">
+        <v>575</v>
+      </c>
+      <c r="H63" s="0" t="s">
         <v>577</v>
       </c>
-      <c r="E63" s="0" t="s">
+      <c r="I63" s="0" t="s">
         <v>578</v>
-      </c>
-      <c r="F63" s="0" t="s">
-        <v>579</v>
-      </c>
-      <c r="G63" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="H63" s="0" t="s">
-        <v>580</v>
-      </c>
-      <c r="I63" s="0" t="s">
-        <v>581</v>
       </c>
       <c r="J63" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="M63" s="0" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="O63" s="0" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="P63" s="0" t="s">
-        <v>418</v>
+        <v>384</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
+        <v>582</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C64" s="0" t="s">
+        <v>583</v>
+      </c>
+      <c r="D64" s="0" t="s">
+        <v>584</v>
+      </c>
+      <c r="E64" s="0" t="s">
         <v>585</v>
       </c>
-      <c r="B64" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C64" s="0" t="s">
+      <c r="F64" s="0" t="s">
         <v>586</v>
       </c>
-      <c r="D64" s="0" t="s">
+      <c r="G64" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H64" s="0" t="s">
         <v>587</v>
-      </c>
-      <c r="E64" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="F64" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="G64" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="H64" s="0" t="s">
-        <v>20</v>
       </c>
       <c r="I64" s="0" t="s">
         <v>588</v>
@@ -5366,7 +5389,7 @@
         <v>591</v>
       </c>
       <c r="P64" s="0" t="s">
-        <v>140</v>
+        <v>425</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5374,324 +5397,324 @@
         <v>592</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>594</v>
+        <v>20</v>
       </c>
       <c r="F65" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G65" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H65" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I65" s="0" t="s">
         <v>595</v>
-      </c>
-      <c r="G65" s="0" t="s">
-        <v>596</v>
-      </c>
-      <c r="H65" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="I65" s="0" t="s">
-        <v>598</v>
       </c>
       <c r="J65" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="M65" s="0" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="O65" s="0" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="P65" s="0" t="s">
-        <v>220</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
+        <v>599</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C66" s="0" t="s">
+        <v>593</v>
+      </c>
+      <c r="D66" s="0" t="s">
+        <v>600</v>
+      </c>
+      <c r="E66" s="0" t="s">
+        <v>601</v>
+      </c>
+      <c r="F66" s="0" t="s">
         <v>602</v>
       </c>
-      <c r="B66" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C66" s="0" t="s">
-        <v>586</v>
-      </c>
-      <c r="D66" s="0" t="s">
+      <c r="G66" s="0" t="s">
         <v>603</v>
       </c>
-      <c r="E66" s="0" t="s">
+      <c r="H66" s="0" t="s">
         <v>604</v>
       </c>
-      <c r="F66" s="0" t="s">
+      <c r="I66" s="0" t="s">
         <v>605</v>
-      </c>
-      <c r="G66" s="0" t="s">
-        <v>606</v>
-      </c>
-      <c r="H66" s="0" t="s">
-        <v>607</v>
-      </c>
-      <c r="I66" s="0" t="s">
-        <v>608</v>
       </c>
       <c r="J66" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L66" s="0" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="M66" s="0" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="O66" s="0" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="P66" s="0" t="s">
-        <v>140</v>
+        <v>220</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
+        <v>609</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C67" s="0" t="s">
+        <v>593</v>
+      </c>
+      <c r="D67" s="0" t="s">
+        <v>610</v>
+      </c>
+      <c r="E67" s="0" t="s">
+        <v>611</v>
+      </c>
+      <c r="F67" s="0" t="s">
         <v>612</v>
       </c>
-      <c r="B67" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C67" s="0" t="s">
+      <c r="G67" s="0" t="s">
         <v>613</v>
       </c>
-      <c r="D67" s="0" t="s">
+      <c r="H67" s="0" t="s">
         <v>614</v>
       </c>
-      <c r="E67" s="0" t="s">
+      <c r="I67" s="0" t="s">
         <v>615</v>
-      </c>
-      <c r="F67" s="0" t="s">
-        <v>616</v>
-      </c>
-      <c r="G67" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="H67" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I67" s="0" t="s">
-        <v>617</v>
       </c>
       <c r="J67" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L67" s="0" t="s">
+        <v>616</v>
+      </c>
+      <c r="M67" s="0" t="s">
+        <v>617</v>
+      </c>
+      <c r="O67" s="0" t="s">
         <v>618</v>
       </c>
-      <c r="M67" s="0" t="s">
-        <v>619</v>
-      </c>
-      <c r="O67" s="0" t="s">
-        <v>620</v>
-      </c>
       <c r="P67" s="0" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
+        <v>619</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C68" s="0" t="s">
+        <v>620</v>
+      </c>
+      <c r="D68" s="0" t="s">
         <v>621</v>
       </c>
-      <c r="B68" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C68" s="0" t="s">
+      <c r="E68" s="0" t="s">
         <v>622</v>
       </c>
-      <c r="D68" s="0" t="s">
+      <c r="F68" s="0" t="s">
         <v>623</v>
       </c>
-      <c r="E68" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="F68" s="0" t="s">
+      <c r="G68" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H68" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I68" s="0" t="s">
         <v>624</v>
-      </c>
-      <c r="G68" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="H68" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I68" s="0" t="s">
-        <v>625</v>
       </c>
       <c r="J68" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L68" s="0" t="s">
+        <v>625</v>
+      </c>
+      <c r="M68" s="0" t="s">
         <v>626</v>
       </c>
-      <c r="M68" s="0" t="s">
+      <c r="O68" s="0" t="s">
         <v>627</v>
       </c>
-      <c r="O68" s="0" t="s">
-        <v>628</v>
-      </c>
       <c r="P68" s="0" t="s">
-        <v>185</v>
+        <v>150</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
+        <v>628</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C69" s="0" t="s">
         <v>629</v>
       </c>
-      <c r="B69" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C69" s="0" t="s">
+      <c r="D69" s="0" t="s">
         <v>630</v>
       </c>
-      <c r="D69" s="0" t="s">
+      <c r="E69" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F69" s="0" t="s">
         <v>631</v>
       </c>
-      <c r="E69" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="F69" s="0" t="s">
+      <c r="G69" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H69" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I69" s="0" t="s">
         <v>632</v>
-      </c>
-      <c r="G69" s="0" t="s">
-        <v>633</v>
-      </c>
-      <c r="H69" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I69" s="0" t="s">
-        <v>634</v>
       </c>
       <c r="J69" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L69" s="0" t="s">
+        <v>633</v>
+      </c>
+      <c r="M69" s="0" t="s">
+        <v>634</v>
+      </c>
+      <c r="O69" s="0" t="s">
         <v>635</v>
       </c>
-      <c r="M69" s="0" t="s">
-        <v>636</v>
-      </c>
-      <c r="O69" s="0" t="s">
-        <v>637</v>
-      </c>
       <c r="P69" s="0" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
+        <v>636</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C70" s="0" t="s">
+        <v>637</v>
+      </c>
+      <c r="D70" s="0" t="s">
         <v>638</v>
       </c>
-      <c r="B70" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C70" s="0" t="s">
+      <c r="E70" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F70" s="0" t="s">
         <v>639</v>
       </c>
-      <c r="D70" s="0" t="s">
+      <c r="G70" s="0" t="s">
         <v>640</v>
       </c>
-      <c r="E70" s="0" t="s">
+      <c r="H70" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I70" s="0" t="s">
         <v>641</v>
-      </c>
-      <c r="F70" s="0" t="s">
-        <v>642</v>
-      </c>
-      <c r="G70" s="0" t="s">
-        <v>437</v>
-      </c>
-      <c r="H70" s="0" t="s">
-        <v>643</v>
-      </c>
-      <c r="I70" s="0" t="s">
-        <v>644</v>
       </c>
       <c r="J70" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L70" s="0" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="M70" s="0" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="O70" s="0" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="P70" s="0" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
+        <v>645</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C71" s="0" t="s">
+        <v>646</v>
+      </c>
+      <c r="D71" s="0" t="s">
+        <v>647</v>
+      </c>
+      <c r="E71" s="0" t="s">
         <v>648</v>
       </c>
-      <c r="B71" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C71" s="0" t="s">
-        <v>639</v>
-      </c>
-      <c r="D71" s="0" t="s">
+      <c r="F71" s="0" t="s">
         <v>649</v>
       </c>
-      <c r="E71" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="F71" s="0" t="s">
-        <v>20</v>
-      </c>
       <c r="G71" s="0" t="s">
-        <v>20</v>
+        <v>444</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>20</v>
+        <v>650</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="J71" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M71" s="0" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="O71" s="0" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="P71" s="0" t="s">
-        <v>220</v>
+        <v>150</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>656</v>
+        <v>20</v>
       </c>
       <c r="F72" s="0" t="s">
         <v>20</v>
@@ -5718,7 +5741,7 @@
         <v>660</v>
       </c>
       <c r="P72" s="0" t="s">
-        <v>377</v>
+        <v>220</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5726,236 +5749,236 @@
         <v>661</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="C73" s="0" t="s">
+        <v>646</v>
+      </c>
+      <c r="D73" s="0" t="s">
         <v>662</v>
       </c>
-      <c r="D73" s="0" t="s">
+      <c r="E73" s="0" t="s">
         <v>663</v>
       </c>
-      <c r="E73" s="0" t="s">
+      <c r="F73" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G73" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H73" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I73" s="0" t="s">
         <v>664</v>
-      </c>
-      <c r="F73" s="0" t="s">
-        <v>665</v>
-      </c>
-      <c r="G73" s="0" t="s">
-        <v>666</v>
-      </c>
-      <c r="H73" s="0" t="s">
-        <v>667</v>
-      </c>
-      <c r="I73" s="0" t="s">
-        <v>668</v>
       </c>
       <c r="J73" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="M73" s="0" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="O73" s="0" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="P73" s="0" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
+        <v>668</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C74" s="0" t="s">
+        <v>669</v>
+      </c>
+      <c r="D74" s="0" t="s">
+        <v>670</v>
+      </c>
+      <c r="E74" s="0" t="s">
+        <v>671</v>
+      </c>
+      <c r="F74" s="0" t="s">
         <v>672</v>
       </c>
-      <c r="B74" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C74" s="0" t="s">
+      <c r="G74" s="0" t="s">
         <v>673</v>
       </c>
-      <c r="D74" s="0" t="s">
+      <c r="H74" s="0" t="s">
         <v>674</v>
       </c>
-      <c r="E74" s="0" t="s">
+      <c r="I74" s="0" t="s">
         <v>675</v>
-      </c>
-      <c r="F74" s="0" t="s">
-        <v>676</v>
-      </c>
-      <c r="G74" s="0" t="s">
-        <v>666</v>
-      </c>
-      <c r="H74" s="0" t="s">
-        <v>677</v>
-      </c>
-      <c r="I74" s="0" t="s">
-        <v>678</v>
       </c>
       <c r="J74" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>470</v>
+        <v>676</v>
       </c>
       <c r="M74" s="0" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="O74" s="0" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="P74" s="0" t="s">
-        <v>140</v>
+        <v>384</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
+        <v>679</v>
+      </c>
+      <c r="B75" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C75" s="0" t="s">
+        <v>680</v>
+      </c>
+      <c r="D75" s="0" t="s">
         <v>681</v>
       </c>
-      <c r="B75" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C75" s="0" t="s">
-        <v>673</v>
-      </c>
-      <c r="D75" s="0" t="s">
+      <c r="E75" s="0" t="s">
         <v>682</v>
-      </c>
-      <c r="E75" s="0" t="s">
-        <v>455</v>
       </c>
       <c r="F75" s="0" t="s">
         <v>683</v>
       </c>
       <c r="G75" s="0" t="s">
+        <v>673</v>
+      </c>
+      <c r="H75" s="0" t="s">
         <v>684</v>
       </c>
-      <c r="H75" s="0" t="s">
+      <c r="I75" s="0" t="s">
         <v>685</v>
-      </c>
-      <c r="I75" s="0" t="s">
-        <v>686</v>
       </c>
       <c r="J75" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L75" s="0" t="s">
+        <v>477</v>
+      </c>
+      <c r="M75" s="0" t="s">
+        <v>686</v>
+      </c>
+      <c r="O75" s="0" t="s">
         <v>687</v>
       </c>
-      <c r="M75" s="0" t="s">
-        <v>688</v>
-      </c>
-      <c r="O75" s="0" t="s">
-        <v>689</v>
-      </c>
       <c r="P75" s="0" t="s">
-        <v>220</v>
+        <v>140</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
+        <v>688</v>
+      </c>
+      <c r="B76" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C76" s="0" t="s">
+        <v>680</v>
+      </c>
+      <c r="D76" s="0" t="s">
+        <v>689</v>
+      </c>
+      <c r="E76" s="0" t="s">
+        <v>462</v>
+      </c>
+      <c r="F76" s="0" t="s">
         <v>690</v>
       </c>
-      <c r="B76" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C76" s="0" t="s">
-        <v>673</v>
-      </c>
-      <c r="D76" s="0" t="s">
+      <c r="G76" s="0" t="s">
         <v>691</v>
       </c>
-      <c r="E76" s="0" t="s">
+      <c r="H76" s="0" t="s">
         <v>692</v>
       </c>
-      <c r="F76" s="0" t="s">
+      <c r="I76" s="0" t="s">
         <v>693</v>
-      </c>
-      <c r="G76" s="0" t="s">
-        <v>694</v>
-      </c>
-      <c r="H76" s="0" t="s">
-        <v>695</v>
-      </c>
-      <c r="I76" s="0" t="s">
-        <v>696</v>
       </c>
       <c r="J76" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L76" s="0" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="M76" s="0" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="O76" s="0" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="P76" s="0" t="s">
-        <v>377</v>
+        <v>220</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
+        <v>697</v>
+      </c>
+      <c r="B77" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C77" s="0" t="s">
+        <v>680</v>
+      </c>
+      <c r="D77" s="0" t="s">
+        <v>698</v>
+      </c>
+      <c r="E77" s="0" t="s">
+        <v>699</v>
+      </c>
+      <c r="F77" s="0" t="s">
         <v>700</v>
       </c>
-      <c r="B77" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C77" s="0" t="s">
+      <c r="G77" s="0" t="s">
         <v>701</v>
       </c>
-      <c r="D77" s="0" t="s">
+      <c r="H77" s="0" t="s">
         <v>702</v>
       </c>
-      <c r="E77" s="0" t="s">
+      <c r="I77" s="0" t="s">
         <v>703</v>
-      </c>
-      <c r="F77" s="0" t="s">
-        <v>704</v>
-      </c>
-      <c r="G77" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="H77" s="0" t="s">
-        <v>533</v>
-      </c>
-      <c r="I77" s="0" t="s">
-        <v>705</v>
       </c>
       <c r="J77" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L77" s="0" t="s">
+        <v>704</v>
+      </c>
+      <c r="M77" s="0" t="s">
+        <v>705</v>
+      </c>
+      <c r="O77" s="0" t="s">
         <v>706</v>
       </c>
-      <c r="M77" s="0" t="s">
-        <v>707</v>
-      </c>
-      <c r="O77" s="0" t="s">
-        <v>708</v>
-      </c>
       <c r="P77" s="0" t="s">
-        <v>140</v>
+        <v>384</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
+        <v>707</v>
+      </c>
+      <c r="B78" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C78" s="0" t="s">
+        <v>708</v>
+      </c>
+      <c r="D78" s="0" t="s">
         <v>709</v>
       </c>
-      <c r="B78" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C78" s="0" t="s">
-        <v>701</v>
-      </c>
-      <c r="D78" s="0" t="s">
+      <c r="E78" s="0" t="s">
         <v>710</v>
-      </c>
-      <c r="E78" s="0" t="s">
-        <v>703</v>
       </c>
       <c r="F78" s="0" t="s">
         <v>711</v>
@@ -5964,66 +5987,66 @@
         <v>20</v>
       </c>
       <c r="H78" s="0" t="s">
+        <v>540</v>
+      </c>
+      <c r="I78" s="0" t="s">
         <v>712</v>
-      </c>
-      <c r="I78" s="0" t="s">
-        <v>713</v>
       </c>
       <c r="J78" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L78" s="0" t="s">
+        <v>713</v>
+      </c>
+      <c r="M78" s="0" t="s">
         <v>714</v>
       </c>
-      <c r="M78" s="0" t="s">
+      <c r="O78" s="0" t="s">
         <v>715</v>
       </c>
-      <c r="O78" s="0" t="s">
-        <v>716</v>
-      </c>
       <c r="P78" s="0" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
+        <v>716</v>
+      </c>
+      <c r="B79" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C79" s="0" t="s">
+        <v>708</v>
+      </c>
+      <c r="D79" s="0" t="s">
         <v>717</v>
       </c>
-      <c r="B79" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C79" s="0" t="s">
+      <c r="E79" s="0" t="s">
+        <v>710</v>
+      </c>
+      <c r="F79" s="0" t="s">
         <v>718</v>
       </c>
-      <c r="D79" s="0" t="s">
+      <c r="G79" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H79" s="0" t="s">
         <v>719</v>
       </c>
-      <c r="E79" s="0" t="s">
+      <c r="I79" s="0" t="s">
         <v>720</v>
-      </c>
-      <c r="F79" s="0" t="s">
-        <v>721</v>
-      </c>
-      <c r="G79" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="H79" s="0" t="s">
-        <v>722</v>
-      </c>
-      <c r="I79" s="0" t="s">
-        <v>723</v>
       </c>
       <c r="J79" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L79" s="0" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="M79" s="0" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="O79" s="0" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="P79" s="0" t="s">
         <v>163</v>
@@ -6031,116 +6054,116 @@
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
+        <v>724</v>
+      </c>
+      <c r="B80" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C80" s="0" t="s">
+        <v>725</v>
+      </c>
+      <c r="D80" s="0" t="s">
+        <v>726</v>
+      </c>
+      <c r="E80" s="0" t="s">
         <v>727</v>
       </c>
-      <c r="B80" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C80" s="0" t="s">
+      <c r="F80" s="0" t="s">
         <v>728</v>
       </c>
-      <c r="D80" s="0" t="s">
+      <c r="G80" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H80" s="0" t="s">
         <v>729</v>
       </c>
-      <c r="E80" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="F80" s="0" t="s">
+      <c r="I80" s="0" t="s">
         <v>730</v>
-      </c>
-      <c r="G80" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="H80" s="0" t="s">
-        <v>731</v>
-      </c>
-      <c r="I80" s="0" t="s">
-        <v>732</v>
       </c>
       <c r="J80" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L80" s="0" t="s">
+        <v>731</v>
+      </c>
+      <c r="M80" s="0" t="s">
+        <v>732</v>
+      </c>
+      <c r="O80" s="0" t="s">
         <v>733</v>
       </c>
-      <c r="M80" s="0" t="s">
-        <v>734</v>
-      </c>
-      <c r="O80" s="0" t="s">
-        <v>735</v>
-      </c>
       <c r="P80" s="0" t="s">
-        <v>418</v>
+        <v>163</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
+        <v>734</v>
+      </c>
+      <c r="B81" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C81" s="0" t="s">
+        <v>735</v>
+      </c>
+      <c r="D81" s="0" t="s">
         <v>736</v>
       </c>
-      <c r="B81" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C81" s="0" t="s">
+      <c r="E81" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F81" s="0" t="s">
         <v>737</v>
       </c>
-      <c r="D81" s="0" t="s">
+      <c r="G81" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H81" s="0" t="s">
         <v>738</v>
       </c>
-      <c r="E81" s="0" t="s">
+      <c r="I81" s="0" t="s">
         <v>739</v>
-      </c>
-      <c r="F81" s="0" t="s">
-        <v>740</v>
-      </c>
-      <c r="G81" s="0" t="s">
-        <v>666</v>
-      </c>
-      <c r="H81" s="0" t="s">
-        <v>741</v>
-      </c>
-      <c r="I81" s="0" t="s">
-        <v>742</v>
       </c>
       <c r="J81" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="M81" s="0" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="O81" s="0" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="P81" s="0" t="s">
-        <v>163</v>
+        <v>425</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
+        <v>743</v>
+      </c>
+      <c r="B82" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C82" s="0" t="s">
+        <v>744</v>
+      </c>
+      <c r="D82" s="0" t="s">
+        <v>745</v>
+      </c>
+      <c r="E82" s="0" t="s">
         <v>746</v>
       </c>
-      <c r="B82" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C82" s="0" t="s">
+      <c r="F82" s="0" t="s">
         <v>747</v>
       </c>
-      <c r="D82" s="0" t="s">
+      <c r="G82" s="0" t="s">
+        <v>673</v>
+      </c>
+      <c r="H82" s="0" t="s">
         <v>748</v>
-      </c>
-      <c r="E82" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="F82" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="G82" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="H82" s="0" t="s">
-        <v>20</v>
       </c>
       <c r="I82" s="0" t="s">
         <v>749</v>
@@ -6158,7 +6181,7 @@
         <v>752</v>
       </c>
       <c r="P82" s="0" t="s">
-        <v>220</v>
+        <v>163</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6166,7 +6189,7 @@
         <v>753</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="C83" s="0" t="s">
         <v>754</v>
@@ -6175,127 +6198,171 @@
         <v>755</v>
       </c>
       <c r="E83" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F83" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G83" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H83" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I83" s="0" t="s">
         <v>756</v>
-      </c>
-      <c r="F83" s="0" t="s">
-        <v>757</v>
-      </c>
-      <c r="G83" s="0" t="s">
-        <v>437</v>
-      </c>
-      <c r="H83" s="0" t="s">
-        <v>758</v>
-      </c>
-      <c r="I83" s="0" t="s">
-        <v>759</v>
       </c>
       <c r="J83" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="M83" s="0" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="O83" s="0" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="P83" s="0" t="s">
-        <v>377</v>
+        <v>220</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
+        <v>760</v>
+      </c>
+      <c r="B84" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C84" s="0" t="s">
+        <v>761</v>
+      </c>
+      <c r="D84" s="0" t="s">
+        <v>762</v>
+      </c>
+      <c r="E84" s="0" t="s">
         <v>763</v>
       </c>
-      <c r="B84" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C84" s="0" t="s">
+      <c r="F84" s="0" t="s">
         <v>764</v>
       </c>
-      <c r="D84" s="0" t="s">
+      <c r="G84" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="H84" s="0" t="s">
         <v>765</v>
       </c>
-      <c r="E84" s="0" t="s">
+      <c r="I84" s="0" t="s">
         <v>766</v>
-      </c>
-      <c r="F84" s="0" t="s">
-        <v>767</v>
-      </c>
-      <c r="G84" s="0" t="s">
-        <v>437</v>
-      </c>
-      <c r="H84" s="0" t="s">
-        <v>768</v>
-      </c>
-      <c r="I84" s="0" t="s">
-        <v>769</v>
       </c>
       <c r="J84" s="0" t="s">
         <v>53</v>
       </c>
       <c r="L84" s="0" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="M84" s="0" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="O84" s="0" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="P84" s="0" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
+        <v>770</v>
+      </c>
+      <c r="B85" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="C85" s="0" t="s">
+        <v>771</v>
+      </c>
+      <c r="D85" s="0" t="s">
+        <v>772</v>
+      </c>
+      <c r="E85" s="0" t="s">
         <v>773</v>
       </c>
-      <c r="B85" s="0" t="s">
+      <c r="F85" s="0" t="s">
         <v>774</v>
       </c>
-      <c r="C85" s="0" t="s">
+      <c r="G85" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="H85" s="0" t="s">
         <v>775</v>
       </c>
-      <c r="D85" s="0" t="s">
+      <c r="I85" s="0" t="s">
         <v>776</v>
       </c>
-      <c r="E85" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="F85" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="G85" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="H85" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I85" s="0" t="s">
+      <c r="J85" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L85" s="0" t="s">
         <v>777</v>
       </c>
-      <c r="J85" s="0" t="s">
+      <c r="M85" s="0" t="s">
         <v>778</v>
       </c>
-      <c r="K85" s="1" t="n">
+      <c r="O85" s="0" t="s">
+        <v>779</v>
+      </c>
+      <c r="P85" s="0" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="0" t="s">
+        <v>780</v>
+      </c>
+      <c r="B86" s="0" t="s">
+        <v>781</v>
+      </c>
+      <c r="C86" s="0" t="s">
+        <v>782</v>
+      </c>
+      <c r="D86" s="0" t="s">
+        <v>783</v>
+      </c>
+      <c r="E86" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F86" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G86" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H86" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I86" s="0" t="s">
+        <v>784</v>
+      </c>
+      <c r="J86" s="0" t="s">
+        <v>785</v>
+      </c>
+      <c r="K86" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="L85" s="0" t="s">
-        <v>779</v>
-      </c>
-      <c r="M85" s="0" t="s">
-        <v>780</v>
-      </c>
-      <c r="N85" s="0" t="s">
-        <v>781</v>
-      </c>
-      <c r="O85" s="0" t="s">
-        <v>782</v>
-      </c>
-      <c r="P85" s="0" t="s">
+      <c r="L86" s="0" t="s">
+        <v>786</v>
+      </c>
+      <c r="M86" s="0" t="s">
+        <v>787</v>
+      </c>
+      <c r="N86" s="0" t="s">
+        <v>788</v>
+      </c>
+      <c r="O86" s="0" t="s">
+        <v>789</v>
+      </c>
+      <c r="P86" s="0" t="s">
         <v>236</v>
       </c>
     </row>

--- a/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
+++ b/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="806">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -154,6 +154,9 @@
     <t xml:space="preserve">MANUAL UI PASS</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
     <t xml:space="preserve">DTO/service support only</t>
   </si>
   <si>
@@ -370,6 +373,9 @@
     <t xml:space="preserve">PARTIAL</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
     <t xml:space="preserve">Capture exact before/after and health direction</t>
   </si>
   <si>
@@ -958,6 +964,9 @@
     <t xml:space="preserve">MANUAL FUNCTIONAL PASS; UI PARTIAL</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extensive fixture/self-tests; common lifecycle tests</t>
   </si>
   <si>
@@ -1324,7 +1333,7 @@
     <t xml:space="preserve">Focused component tests pass 6/6 for SmartList loading, keyed equality, row patching, detail isolation and local patch routing; running hot-deploy build manually showed no prior Job Detail stutter; browser frame-time trace not captured</t>
   </si>
   <si>
-    <t xml:space="preserve">Capture 20â€“30 second Performance + Network traces for idle/list/detail/chat; prove unchanged Job polls preserve DOM rows and non-selected updates do not re-render detail; correlate Chat hitches independently</t>
+    <t xml:space="preserve">Capture 20–30 second Performance + Network traces for idle/list/detail/chat; prove unchanged Job polls preserve DOM rows and non-selected updates do not re-render detail; correlate Chat hitches independently</t>
   </si>
   <si>
     <t xml:space="preserve">OPEN / PARTIAL PASS</t>
@@ -1363,124 +1372,163 @@
     <t xml:space="preserve">Draft appears once in Hosting/Drafts and every saved field reopens exactly</t>
   </si>
   <si>
+    <t xml:space="preserve">Event sync/service coverage partial; focused HTTP/local timezone regressions pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retain as a release-change sample; continue the same canonical draft into EVENT-EDITOR-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One canonical draft, one deduplicated recompute task, zero outbox, no read-only duplicate, and no Nova All/Active/Invitations visibility. Venue label remained Austin while proximity coordinates exactly matched Casey. The fixed retest stored local 18:00-20:00 as 16:00Z-18:00Z and both card and reopened editor showed 18:00-20:00.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-TIMEZONE-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defect retest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event Editor date/time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preserve a locally entered event range across UTC persistence and editor reopen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT only after the normal snapshot worker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA only for the intentional corrective Save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT only after recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time-dependent jobs consume the corrected UTC instant; no job is invoked by reopen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Europe/Bratislava 18:00-20:00 persists as 16:00Z-18:00Z and reopens as 18:00-20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focused HTTP and local IndexedDB service regressions pass 12/12 under Europe/Bratislava</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retain as a release-change timezone sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initial failure was a timezone-free local datetime sent unchanged to a backend UTC field. After the shared persistence-payload fix and hot deploy, MongoDB contained 16:00Z-18:00Z while the card and reopened editor both showed 18:00-20:00; the editor model remained local and unchanged before persistence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-EDITOR-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publish one controlled draft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT event inventory delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA event lifecycle and recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA affinity recompute; slot/reminder consumers conditional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hosting and Explore visibility obey user and visibility boundaries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publish/service coverage partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare host and unrelated-user buckets against canonical active state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publish is separate from draft save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-EDITOR-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event Editor + Auto inviter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save one eligible auto-inviter definition, then let the real scheduler consume it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT event/member activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA event save, member write and outbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT after event/member recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA event-auto-inviter real run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exactly one pending invited member and recipient invitation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto-inviter service/fixture coverage; STAT-012 scheduler path passed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage editor-produced input and prove the scheduler-created output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The fixture may stage prerequisites but must not create the invitation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-EDITOR-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event Editor + Tournament</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save and reopen one tournament definition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT event activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA event write and recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tournament review/grouping X until explicitly armed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stages, capacities and group definition survive reopen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tournament service coverage partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare editor definition with runtime stage baseline before processing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Definition persistence is not grouping proof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVENT-EDITOR-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edit one downstream-relevant active field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT documented event delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA definition change and recompute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIRECT when the field affects affinity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELTA affinity recompute; other consumers conditional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changed field persists; removed definition is absent; no-op reopen is X</t>
+  </si>
+  <si>
     <t xml:space="preserve">Event sync/service coverage partial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capture pre-save, post-save and reopened editor plus canonical event oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One action and one state transition; no publish proof is inferred</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EVENT-EDITOR-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Publish one controlled draft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INDIRECT event inventory delta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DELTA event lifecycle and recompute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DELTA affinity recompute; slot/reminder consumers conditional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hosting and Explore visibility obey user and visibility boundaries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Publish/service coverage partial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compare host and unrelated-user buckets against canonical active state</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Publish is separate from draft save</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EVENT-EDITOR-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Event Editor + Auto inviter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Save one eligible auto-inviter definition, then let the real scheduler consume it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INDIRECT event/member activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DELTA event save, member write and outbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INDIRECT after event/member recompute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DELTA event-auto-inviter real run</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exactly one pending invited member and recipient invitation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto-inviter service/fixture coverage; STAT-012 scheduler path passed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stage editor-produced input and prove the scheduler-created output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The fixture may stage prerequisites but must not create the invitation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EVENT-EDITOR-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Event Editor + Tournament</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Save and reopen one tournament definition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INDIRECT event activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DELTA event write and recompute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tournament review/grouping X until explicitly armed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stages, capacities and group definition survive reopen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tournament service coverage partial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compare editor definition with runtime stage baseline before processing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Definition persistence is not grouping proof</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EVENT-EDITOR-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edit one downstream-relevant active field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INDIRECT documented event delta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DELTA definition change and recompute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INDIRECT when the field affects affinity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DELTA affinity recompute; other consumers conditional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Changed field persists; removed definition is absent; no-op reopen is X</t>
   </si>
   <si>
     <t xml:space="preserve">Change one field only and retain one unrelated control field</t>
@@ -2396,9 +2444,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="@"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -2465,12 +2514,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2491,8 +2544,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P86"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:P87"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22.55"/>
@@ -2757,43 +2810,43 @@
       <c r="J6" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="K6" s="1" t="n">
-        <v>46238</v>
+      <c r="K6" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="L6" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M6" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N6" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O6" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P6" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>40</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G7" s="0" t="s">
         <v>20</v>
@@ -2805,24 +2858,24 @@
         <v>20</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L7" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M7" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O7" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P7" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>40</v>
@@ -2831,16 +2884,16 @@
         <v>6</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F8" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H8" s="0" t="s">
         <v>20</v>
@@ -2849,230 +2902,230 @@
         <v>20</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L8" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M8" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O8" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P8" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <v>46238</v>
+        <v>75</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="L9" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M9" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N9" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O9" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P9" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G10" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J10" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="K10" s="1" t="n">
-        <v>46238</v>
+        <v>87</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="L10" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M10" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N10" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O10" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P10" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>4</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="K11" s="1" t="n">
-        <v>46238</v>
+        <v>87</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M11" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N11" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O11" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P11" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G12" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J12" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L12" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M12" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P12" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G13" s="0" t="s">
         <v>20</v>
@@ -3081,268 +3134,268 @@
         <v>20</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>115</v>
-      </c>
-      <c r="K13" s="1" t="n">
-        <v>46232</v>
+        <v>116</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M13" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="O13" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="P13" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C14" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="H14" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="I14" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="J14" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L14" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="M14" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="N14" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="O14" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="P14" s="0" t="s">
         <v>120</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="E14" s="0" t="s">
-        <v>122</v>
-      </c>
-      <c r="F14" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="G14" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="H14" s="0" t="s">
-        <v>125</v>
-      </c>
-      <c r="I14" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="J14" s="0" t="s">
-        <v>127</v>
-      </c>
-      <c r="K14" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="L14" s="0" t="s">
-        <v>128</v>
-      </c>
-      <c r="M14" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="N14" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="O14" s="0" t="s">
-        <v>130</v>
-      </c>
-      <c r="P14" s="0" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M15" s="0" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="P15" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E16" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G16" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="K16" s="1" t="n">
-        <v>46238</v>
+        <v>148</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="L16" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M16" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N16" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O16" s="0" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P16" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L17" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M17" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O17" s="0" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="P17" s="0" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B18" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="G18" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="H18" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="I18" s="0" t="s">
+        <v>171</v>
+      </c>
+      <c r="J18" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="L18" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="M18" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="O18" s="0" t="s">
+        <v>174</v>
+      </c>
+      <c r="P18" s="0" t="s">
         <v>152</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>153</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>165</v>
-      </c>
-      <c r="E18" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" s="0" t="s">
-        <v>166</v>
-      </c>
-      <c r="G18" s="0" t="s">
-        <v>167</v>
-      </c>
-      <c r="H18" s="0" t="s">
-        <v>168</v>
-      </c>
-      <c r="I18" s="0" t="s">
-        <v>169</v>
-      </c>
-      <c r="J18" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="L18" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="M18" s="0" t="s">
-        <v>171</v>
-      </c>
-      <c r="O18" s="0" t="s">
-        <v>172</v>
-      </c>
-      <c r="P18" s="0" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E19" s="0" t="s">
         <v>20</v>
@@ -3351,7 +3404,7 @@
         <v>20</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H19" s="0" t="s">
         <v>20</v>
@@ -3360,30 +3413,30 @@
         <v>20</v>
       </c>
       <c r="J19" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L19" s="0" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M19" s="0" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P19" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E20" s="0" t="s">
         <v>20</v>
@@ -3392,48 +3445,48 @@
         <v>20</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H20" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J20" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L20" s="0" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M20" s="0" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P20" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F21" s="0" t="s">
         <v>20</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H21" s="0" t="s">
         <v>20</v>
@@ -3442,30 +3495,30 @@
         <v>20</v>
       </c>
       <c r="J21" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L21" s="0" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M21" s="0" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P21" s="0" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E22" s="0" t="s">
         <v>20</v>
@@ -3474,124 +3527,124 @@
         <v>20</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H22" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J22" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L22" s="0" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M22" s="0" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P22" s="0" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="J23" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L23" s="0" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M23" s="0" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="P23" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J24" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L24" s="0" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M24" s="0" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="O24" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P24" s="0" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E25" s="0" t="s">
         <v>20</v>
@@ -3600,376 +3653,376 @@
         <v>20</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H25" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J25" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M25" s="0" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="P25" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E26" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J26" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L26" s="0" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M26" s="0" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P26" s="0" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="J27" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M27" s="0" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P27" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J28" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L28" s="0" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M28" s="0" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P28" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E29" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G29" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="J29" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M29" s="0" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O29" s="0" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P29" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E30" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G30" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J30" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L30" s="0" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M30" s="0" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O30" s="0" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P30" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="J31" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L31" s="0" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M31" s="0" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P31" s="0" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B32" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="C32" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="D32" s="0" t="s">
+        <v>283</v>
+      </c>
+      <c r="E32" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F32" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="G32" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="I32" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="J32" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="L32" s="0" t="s">
+        <v>287</v>
+      </c>
+      <c r="M32" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="O32" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="P32" s="0" t="s">
         <v>238</v>
-      </c>
-      <c r="C32" s="0" t="s">
-        <v>280</v>
-      </c>
-      <c r="D32" s="0" t="s">
-        <v>281</v>
-      </c>
-      <c r="E32" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="F32" s="0" t="s">
-        <v>282</v>
-      </c>
-      <c r="G32" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="H32" s="0" t="s">
-        <v>259</v>
-      </c>
-      <c r="I32" s="0" t="s">
-        <v>283</v>
-      </c>
-      <c r="J32" s="0" t="s">
-        <v>284</v>
-      </c>
-      <c r="L32" s="0" t="s">
-        <v>285</v>
-      </c>
-      <c r="M32" s="0" t="s">
-        <v>286</v>
-      </c>
-      <c r="O32" s="0" t="s">
-        <v>287</v>
-      </c>
-      <c r="P32" s="0" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E33" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G33" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="J33" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L33" s="0" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M33" s="0" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P33" s="0" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E34" s="0" t="s">
         <v>20</v>
@@ -3981,142 +4034,142 @@
         <v>20</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J34" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L34" s="0" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M34" s="0" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="P34" s="0" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B35" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="D35" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="E35" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F35" s="0" t="s">
+        <v>310</v>
+      </c>
+      <c r="G35" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" s="0" t="s">
+        <v>311</v>
+      </c>
+      <c r="I35" s="0" t="s">
+        <v>312</v>
+      </c>
+      <c r="J35" s="0" t="s">
+        <v>313</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="L35" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="M35" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="N35" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="O35" s="0" t="s">
+        <v>317</v>
+      </c>
+      <c r="P35" s="0" t="s">
         <v>305</v>
-      </c>
-      <c r="C35" s="0" t="s">
-        <v>306</v>
-      </c>
-      <c r="D35" s="0" t="s">
-        <v>307</v>
-      </c>
-      <c r="E35" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="F35" s="0" t="s">
-        <v>308</v>
-      </c>
-      <c r="G35" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="H35" s="0" t="s">
-        <v>309</v>
-      </c>
-      <c r="I35" s="0" t="s">
-        <v>310</v>
-      </c>
-      <c r="J35" s="0" t="s">
-        <v>311</v>
-      </c>
-      <c r="K35" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="L35" s="0" t="s">
-        <v>312</v>
-      </c>
-      <c r="M35" s="0" t="s">
-        <v>313</v>
-      </c>
-      <c r="N35" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="O35" s="0" t="s">
-        <v>314</v>
-      </c>
-      <c r="P35" s="0" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H36" s="0" t="s">
         <v>26</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="J36" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="K36" s="1" t="n">
-        <v>46238</v>
+        <v>87</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="L36" s="0" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M36" s="0" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="N36" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O36" s="0" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="P36" s="0" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E37" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G37" s="0" t="s">
         <v>20</v>
@@ -4125,48 +4178,48 @@
         <v>26</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="J37" s="0" t="s">
-        <v>329</v>
-      </c>
-      <c r="K37" s="1" t="n">
-        <v>46232</v>
+        <v>332</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="M37" s="0" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="N37" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O37" s="0" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="P37" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E38" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G38" s="0" t="s">
         <v>20</v>
@@ -4175,48 +4228,48 @@
         <v>26</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J38" s="0" t="s">
-        <v>329</v>
-      </c>
-      <c r="K38" s="1" t="n">
-        <v>46232</v>
+        <v>332</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="L38" s="0" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="M38" s="0" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="N38" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O38" s="0" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="P38" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E39" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G39" s="0" t="s">
         <v>20</v>
@@ -4225,48 +4278,48 @@
         <v>26</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="J39" s="0" t="s">
-        <v>329</v>
-      </c>
-      <c r="K39" s="1" t="n">
-        <v>46232</v>
+        <v>332</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="L39" s="0" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="M39" s="0" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="N39" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O39" s="0" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="P39" s="0" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E40" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G40" s="0" t="s">
         <v>20</v>
@@ -4275,101 +4328,101 @@
         <v>26</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="J40" s="0" t="s">
-        <v>329</v>
-      </c>
-      <c r="K40" s="1" t="n">
-        <v>46232</v>
+        <v>332</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="L40" s="0" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="M40" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="N40" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O40" s="0" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="P40" s="0" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H41" s="0" t="s">
         <v>26</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="J41" s="0" t="s">
-        <v>329</v>
-      </c>
-      <c r="K41" s="1" t="n">
-        <v>46232</v>
+        <v>332</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="L41" s="0" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="M41" s="0" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="N41" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O41" s="0" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="P41" s="0" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E42" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="H42" s="0" t="s">
         <v>26</v>
@@ -4378,40 +4431,40 @@
         <v>20</v>
       </c>
       <c r="J42" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="K42" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="K42" s="2"/>
       <c r="L42" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="M42" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="O42" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="P42" s="0" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E43" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="G43" s="0" t="s">
         <v>20</v>
@@ -4420,236 +4473,236 @@
         <v>26</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="J43" s="0" t="s">
-        <v>329</v>
-      </c>
-      <c r="K43" s="1" t="n">
-        <v>46232</v>
+        <v>332</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="M43" s="0" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N43" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O43" s="0" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="P43" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="H44" s="0" t="s">
         <v>26</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="J44" s="0" t="s">
-        <v>329</v>
-      </c>
-      <c r="K44" s="1" t="n">
-        <v>46232</v>
+        <v>332</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="L44" s="0" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="M44" s="0" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="N44" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O44" s="0" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="P44" s="0" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="J45" s="0" t="s">
-        <v>394</v>
-      </c>
-      <c r="K45" s="1" t="n">
-        <v>46238</v>
+        <v>397</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="L45" s="0" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="M45" s="0" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="N45" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O45" s="0" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="P45" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="G46" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="J46" s="0" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="L46" s="0" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="M46" s="0" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="O46" s="0" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="P46" s="0" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="J47" s="0" t="s">
-        <v>420</v>
-      </c>
-      <c r="K47" s="1" t="n">
-        <v>46238</v>
+        <v>423</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="L47" s="0" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="M47" s="0" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="N47" s="0" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="O47" s="0" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="P47" s="0" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E48" s="0" t="s">
         <v>20</v>
@@ -4661,931 +4714,943 @@
         <v>20</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="J48" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="K48" s="1" t="n">
-        <v>46238</v>
+        <v>435</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="L48" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="M48" s="0" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="N48" s="0" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="O48" s="0" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="P48" s="0" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="J49" s="0" t="s">
-        <v>53</v>
+        <v>87</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="L49" s="0" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="M49" s="0" t="s">
-        <v>448</v>
+        <v>451</v>
+      </c>
+      <c r="N49" s="0" t="s">
+        <v>47</v>
       </c>
       <c r="O49" s="0" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="P49" s="0" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="J50" s="0" t="s">
-        <v>53</v>
+        <v>87</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="L50" s="0" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="M50" s="0" t="s">
-        <v>457</v>
+        <v>463</v>
+      </c>
+      <c r="N50" s="0" t="s">
+        <v>47</v>
       </c>
       <c r="O50" s="0" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="P50" s="0" t="s">
-        <v>140</v>
+        <v>387</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="G51" s="0" t="s">
-        <v>464</v>
+        <v>447</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="J51" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L51" s="0" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="M51" s="0" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="O51" s="0" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="P51" s="0" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>444</v>
+        <v>479</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="J52" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L52" s="0" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="M52" s="0" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="O52" s="0" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="P52" s="0" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>440</v>
+        <v>486</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>484</v>
+        <v>447</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="J53" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>447</v>
+        <v>492</v>
       </c>
       <c r="M53" s="0" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="O53" s="0" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="P53" s="0" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>490</v>
+        <v>443</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>453</v>
+        <v>498</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>444</v>
+        <v>499</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="J54" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L54" s="0" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="M54" s="0" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="O54" s="0" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="P54" s="0" t="s">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="J55" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="M55" s="0" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="O55" s="0" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="P55" s="0" t="s">
-        <v>220</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="J56" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L56" s="0" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="M56" s="0" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="O56" s="0" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="P56" s="0" t="s">
-        <v>163</v>
+        <v>222</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>521</v>
+        <v>447</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="J57" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="M57" s="0" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="O57" s="0" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="P57" s="0" t="s">
-        <v>220</v>
+        <v>165</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>20</v>
+        <v>535</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>20</v>
+        <v>536</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>20</v>
+        <v>537</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>20</v>
+        <v>538</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="J58" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L58" s="0" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="M58" s="0" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="O58" s="0" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="P58" s="0" t="s">
-        <v>101</v>
+        <v>222</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>537</v>
+        <v>20</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>538</v>
+        <v>20</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>539</v>
+        <v>20</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>540</v>
+        <v>20</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="J59" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="M59" s="0" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="O59" s="0" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="P59" s="0" t="s">
-        <v>163</v>
+        <v>102</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>20</v>
+        <v>553</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>20</v>
+        <v>554</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>20</v>
+        <v>555</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>20</v>
+        <v>556</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="J60" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L60" s="0" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="M60" s="0" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="O60" s="0" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="P60" s="0" t="s">
-        <v>425</v>
+        <v>165</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>535</v>
+        <v>562</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>554</v>
+        <v>20</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>555</v>
+        <v>20</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>556</v>
+        <v>20</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>557</v>
+        <v>20</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="J61" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="M61" s="0" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="O61" s="0" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="P61" s="0" t="s">
-        <v>384</v>
+        <v>428</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>557</v>
+        <v>573</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="J62" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L62" s="0" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="M62" s="0" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="O62" s="0" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="P62" s="0" t="s">
-        <v>425</v>
+        <v>387</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C63" s="0" t="s">
+        <v>579</v>
+      </c>
+      <c r="D63" s="0" t="s">
+        <v>580</v>
+      </c>
+      <c r="E63" s="0" t="s">
+        <v>581</v>
+      </c>
+      <c r="F63" s="0" t="s">
+        <v>582</v>
+      </c>
+      <c r="G63" s="0" t="s">
+        <v>583</v>
+      </c>
+      <c r="H63" s="0" t="s">
         <v>573</v>
       </c>
-      <c r="D63" s="0" t="s">
-        <v>574</v>
-      </c>
-      <c r="E63" s="0" t="s">
-        <v>575</v>
-      </c>
-      <c r="F63" s="0" t="s">
-        <v>576</v>
-      </c>
-      <c r="G63" s="0" t="s">
-        <v>575</v>
-      </c>
-      <c r="H63" s="0" t="s">
-        <v>577</v>
-      </c>
       <c r="I63" s="0" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="J63" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="M63" s="0" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="O63" s="0" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="P63" s="0" t="s">
-        <v>384</v>
+        <v>428</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>20</v>
+        <v>591</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="J64" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L64" s="0" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="M64" s="0" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="O64" s="0" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="P64" s="0" t="s">
-        <v>425</v>
+        <v>387</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>20</v>
+        <v>601</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>20</v>
+        <v>602</v>
       </c>
       <c r="G65" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>20</v>
+        <v>603</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>595</v>
+        <v>604</v>
       </c>
       <c r="J65" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>596</v>
+        <v>605</v>
       </c>
       <c r="M65" s="0" t="s">
-        <v>597</v>
+        <v>606</v>
       </c>
       <c r="O65" s="0" t="s">
-        <v>598</v>
+        <v>607</v>
       </c>
       <c r="P65" s="0" t="s">
-        <v>140</v>
+        <v>428</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>599</v>
+        <v>608</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>593</v>
+        <v>609</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>601</v>
+        <v>20</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>602</v>
+        <v>20</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>603</v>
+        <v>20</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>604</v>
+        <v>20</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="J66" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L66" s="0" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="M66" s="0" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="O66" s="0" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="P66" s="0" t="s">
-        <v>220</v>
+        <v>142</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
+        <v>615</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>442</v>
+      </c>
+      <c r="C67" s="0" t="s">
         <v>609</v>
       </c>
-      <c r="B67" s="0" t="s">
-        <v>439</v>
-      </c>
-      <c r="C67" s="0" t="s">
-        <v>593</v>
-      </c>
       <c r="D67" s="0" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="J67" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="M67" s="0" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="O67" s="0" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="P67" s="0" t="s">
-        <v>140</v>
+        <v>222</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>20</v>
+        <v>629</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>20</v>
+        <v>630</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="J68" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L68" s="0" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="M68" s="0" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="O68" s="0" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="P68" s="0" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>20</v>
+        <v>638</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="G69" s="0" t="s">
         <v>20</v>
@@ -5594,171 +5659,171 @@
         <v>20</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="J69" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="M69" s="0" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="O69" s="0" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="P69" s="0" t="s">
-        <v>185</v>
+        <v>152</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="E70" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>640</v>
+        <v>20</v>
       </c>
       <c r="H70" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="J70" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L70" s="0" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="M70" s="0" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="O70" s="0" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="P70" s="0" t="s">
-        <v>163</v>
+        <v>187</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>648</v>
+        <v>20</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>444</v>
+        <v>656</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>650</v>
+        <v>20</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="J71" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="M71" s="0" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="O71" s="0" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="P71" s="0" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>646</v>
+        <v>662</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>20</v>
+        <v>664</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>20</v>
+        <v>665</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>20</v>
+        <v>447</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>20</v>
+        <v>666</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>657</v>
+        <v>667</v>
       </c>
       <c r="J72" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L72" s="0" t="s">
-        <v>658</v>
+        <v>668</v>
       </c>
       <c r="M72" s="0" t="s">
-        <v>659</v>
+        <v>669</v>
       </c>
       <c r="O72" s="0" t="s">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="P72" s="0" t="s">
-        <v>220</v>
+        <v>152</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>661</v>
+        <v>671</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>646</v>
+        <v>662</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>662</v>
+        <v>672</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>663</v>
+        <v>20</v>
       </c>
       <c r="F73" s="0" t="s">
         <v>20</v>
@@ -5770,600 +5835,645 @@
         <v>20</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>664</v>
+        <v>673</v>
       </c>
       <c r="J73" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="M73" s="0" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="O73" s="0" t="s">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="P73" s="0" t="s">
-        <v>384</v>
+        <v>222</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>668</v>
+        <v>677</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>672</v>
+        <v>20</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>673</v>
+        <v>20</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>674</v>
+        <v>20</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="J74" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="M74" s="0" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="O74" s="0" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="P74" s="0" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>673</v>
+        <v>689</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="J75" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>477</v>
+        <v>692</v>
       </c>
       <c r="M75" s="0" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="O75" s="0" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="P75" s="0" t="s">
-        <v>140</v>
+        <v>387</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>680</v>
+        <v>696</v>
       </c>
       <c r="D76" s="0" t="s">
+        <v>697</v>
+      </c>
+      <c r="E76" s="0" t="s">
+        <v>698</v>
+      </c>
+      <c r="F76" s="0" t="s">
+        <v>699</v>
+      </c>
+      <c r="G76" s="0" t="s">
         <v>689</v>
       </c>
-      <c r="E76" s="0" t="s">
-        <v>462</v>
-      </c>
-      <c r="F76" s="0" t="s">
-        <v>690</v>
-      </c>
-      <c r="G76" s="0" t="s">
-        <v>691</v>
-      </c>
       <c r="H76" s="0" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="J76" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L76" s="0" t="s">
-        <v>694</v>
+        <v>492</v>
       </c>
       <c r="M76" s="0" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="O76" s="0" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="P76" s="0" t="s">
-        <v>220</v>
+        <v>142</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>680</v>
+        <v>696</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>699</v>
+        <v>477</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="J77" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="M77" s="0" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="O77" s="0" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="P77" s="0" t="s">
-        <v>384</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>708</v>
+        <v>696</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>20</v>
+        <v>717</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>540</v>
+        <v>718</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="J78" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L78" s="0" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="M78" s="0" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="O78" s="0" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="P78" s="0" t="s">
-        <v>140</v>
+        <v>387</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>708</v>
+        <v>724</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>710</v>
+        <v>726</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>718</v>
+        <v>727</v>
       </c>
       <c r="G79" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>719</v>
+        <v>556</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="J79" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L79" s="0" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="M79" s="0" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="O79" s="0" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="P79" s="0" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
+        <v>732</v>
+      </c>
+      <c r="B80" s="0" t="s">
+        <v>442</v>
+      </c>
+      <c r="C80" s="0" t="s">
         <v>724</v>
       </c>
-      <c r="B80" s="0" t="s">
-        <v>439</v>
-      </c>
-      <c r="C80" s="0" t="s">
-        <v>725</v>
-      </c>
       <c r="D80" s="0" t="s">
+        <v>733</v>
+      </c>
+      <c r="E80" s="0" t="s">
         <v>726</v>
       </c>
-      <c r="E80" s="0" t="s">
-        <v>727</v>
-      </c>
       <c r="F80" s="0" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="G80" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="J80" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L80" s="0" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="M80" s="0" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="O80" s="0" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="P80" s="0" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>20</v>
+        <v>743</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="G81" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="J81" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="M81" s="0" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="O81" s="0" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="P81" s="0" t="s">
-        <v>425</v>
+        <v>165</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>746</v>
+        <v>20</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>673</v>
+        <v>20</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="J82" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L82" s="0" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="M82" s="0" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="O82" s="0" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="P82" s="0" t="s">
-        <v>163</v>
+        <v>428</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>20</v>
+        <v>762</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>20</v>
+        <v>763</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>20</v>
+        <v>689</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>20</v>
+        <v>764</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>756</v>
+        <v>765</v>
       </c>
       <c r="J83" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>757</v>
+        <v>766</v>
       </c>
       <c r="M83" s="0" t="s">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="O83" s="0" t="s">
-        <v>759</v>
+        <v>768</v>
       </c>
       <c r="P83" s="0" t="s">
-        <v>220</v>
+        <v>165</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>761</v>
+        <v>770</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>762</v>
+        <v>771</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>763</v>
+        <v>20</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>764</v>
+        <v>20</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>444</v>
+        <v>20</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>765</v>
+        <v>20</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="J84" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L84" s="0" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="M84" s="0" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="O84" s="0" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="P84" s="0" t="s">
-        <v>384</v>
+        <v>222</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="J85" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L85" s="0" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="M85" s="0" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="O85" s="0" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="P85" s="0" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>781</v>
+        <v>442</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>20</v>
+        <v>789</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>20</v>
+        <v>790</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>20</v>
+        <v>447</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>20</v>
+        <v>791</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="J86" s="0" t="s">
-        <v>785</v>
-      </c>
-      <c r="K86" s="1" t="n">
-        <v>46238</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="K86" s="2"/>
       <c r="L86" s="0" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="M86" s="0" t="s">
-        <v>787</v>
-      </c>
-      <c r="N86" s="0" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="O86" s="0" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="P86" s="0" t="s">
-        <v>236</v>
+        <v>387</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="0" t="s">
+        <v>796</v>
+      </c>
+      <c r="B87" s="0" t="s">
+        <v>797</v>
+      </c>
+      <c r="C87" s="0" t="s">
+        <v>798</v>
+      </c>
+      <c r="D87" s="0" t="s">
+        <v>799</v>
+      </c>
+      <c r="E87" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F87" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G87" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H87" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I87" s="0" t="s">
+        <v>800</v>
+      </c>
+      <c r="J87" s="0" t="s">
+        <v>801</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L87" s="0" t="s">
+        <v>802</v>
+      </c>
+      <c r="M87" s="0" t="s">
+        <v>803</v>
+      </c>
+      <c r="N87" s="0" t="s">
+        <v>804</v>
+      </c>
+      <c r="O87" s="0" t="s">
+        <v>805</v>
+      </c>
+      <c r="P87" s="0" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
+++ b/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="845">
   <si>
     <t>ID</t>
   </si>
@@ -1513,6 +1513,48 @@
     <t>Before the fix, Nova's notification and counters arrived but the already-open Invitations list stayed empty until popup reopen. All non-calendar event activity scopes now share one 30-second SmartList-owned visible-list poll, paused behind dialogs/event chat; no new cache, worker or full-app rerender was added. During the Riley periodic retest, all three sessions remained open. The 14:39:22 screenshot captured mixed 1 / 8 (1) and 1 / 8 (2) projections after the 14:39:13 scheduler run. The 14:39:52 screenshot showed Riley's invitation and Nova, Riley and Casey all at 1 / 8 (2) without refresh or reopen. Accepted occupancy stayed 1 / 8 because Nova and Riley were still pending; the red (2) was the synchronized pending-invitation count.</t>
   </si>
   <si>
+    <t>EVENT-MEMBER-CREATOR-001</t>
+  </si>
+  <si>
+    <t>Defect checkpoint</t>
+  </si>
+  <si>
+    <t>Event creator/admin membership</t>
+  </si>
+  <si>
+    <t>Publish an event with no creator member document, add pending invitations, then compare event-card occupancy with Event Members and the exact member oracle before acceptance</t>
+  </si>
+  <si>
+    <t>INDIRECT only after a real membership mutation</t>
+  </si>
+  <si>
+    <t>DELTA belongs to publish/invite; read-only comparison is X</t>
+  </si>
+  <si>
+    <t>INDIRECT because downstream graph may consume canonical membership</t>
+  </si>
+  <si>
+    <t>X for the read-only comparison</t>
+  </si>
+  <si>
+    <t>Creator appears once as accepted Admin; Members reports 1 member and N pending; cards report 1 / capacity with pending badge N</t>
+  </si>
+  <si>
+    <t>MANUAL UI + FUNCTIONAL PASS; FIX VERIFIED</t>
+  </si>
+  <si>
+    <t>Creator materialization/idempotence, publish/sync invocation, no-fallback mapper and stored-admin-order regressions passed in the 99-test focused profile selection. The existing Java container was stopped for the run, then restarted healthy; no parallel stack or cache was created.</t>
+  </si>
+  <si>
+    <t>Retain Unpublish then CARD-PUBLISH as the regression sample; verify the creator exactly once and keep pending recipients unchanged before acceptance</t>
+  </si>
+  <si>
+    <t>Historical failure: all three event cards displayed 1 / 8 (2) while Event Members and the exact oracle contained no accepted Casey membership. After removing Java creator synthesis, the post-fix Unpublish converged every open projection to the truthful legacy-draft baseline 0 / 8 (2). CARD-PUBLISH repaired the same event identity: all three sessions converged to 1 / 8 (2), Event Members reported 1 member / 2 pending, and Casey appeared exactly once as Admin while Nova and Riley remained pending. The independent oracle stored acceptedMembers 1, pendingMembers 2, Casey in acceptedMemberUserIds and admins, and exactly one accepted Admin creator membership plus the two pending invite memberships. No fixture or direct database mutation was used.</t>
+  </si>
+  <si>
+    <t>P0 99</t>
+  </si>
+  <si>
     <t>EVENT-CAPACITY-SYNC-001</t>
   </si>
   <si>
@@ -1525,22 +1567,16 @@
     <t>DELTA event lifecycle only; occupancy remains authoritative</t>
   </si>
   <si>
-    <t>My Events and Drafts show the same 0 / 8 occupancy before and after reload</t>
-  </si>
-  <si>
-    <t>OPEN / MANUAL REPRODUCED</t>
-  </si>
-  <si>
-    <t>Event converter and publication patch coverage do not prove cross-scope occupancy convergence</t>
-  </si>
-  <si>
-    <t>Retest Unpublish without opening members: compare the immediate My Events card, Drafts card and a fresh reload against the member oracle</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>After Unpublish, the locally patched My Events card displayed 1 / 8 even though MongoDB had no activityMembers and no accepted member IDs. Switching to freshly queried Drafts displayed the correct 0 / 8. This is a transient cross-scope UI projection mismatch, not persisted membership.</t>
+    <t>My Events and Drafts show the same canonical occupancy before and after reload</t>
+  </si>
+  <si>
+    <t>No-fallback mapper and canonical membership regressions passed in the 99-test focused profile selection. The existing Java container was stopped for the run and restarted healthy.</t>
+  </si>
+  <si>
+    <t>Reuse one Unpublish and CARD-PUBLISH transition while multiple isolated event projections remain open; compare each state with the canonical membership oracle</t>
+  </si>
+  <si>
+    <t>Historical failure: Unpublish briefly split My Events at 1 / 8 from the authoritative empty membership and Drafts at 0 / 8. In the post-fix retest, Unpublish converged the open projections and exact draft oracle to 0 / 8 (2). CARD-PUBLISH materialized the creator membership and all three already-open sessions converged to the new canonical 1 / 8 (2), with no frontend fallback or direct database repair.</t>
   </si>
   <si>
     <t>EVENT-EDITOR-004</t>
@@ -1783,13 +1819,16 @@
     <t>Accepted-only controls, chat and resources are hidden and server-denied</t>
   </si>
   <si>
-    <t>Access-control tests partial</t>
-  </si>
-  <si>
-    <t>Use menu check and direct/deep-link denial</t>
-  </si>
-  <si>
-    <t>UI hiding alone is insufficient</t>
+    <t>MANUAL UI PARTIAL; FIREBASE AUTHORIZATION CHECK PENDING</t>
+  </si>
+  <si>
+    <t>Access-control tests partial; demo session bypasses the production authenticated policy gate</t>
+  </si>
+  <si>
+    <t>Repeat direct/deep-link denial in a Firebase-enabled non-demo recipient session; keep Open Event member preview distinct from accepted-only chat/resources</t>
+  </si>
+  <si>
+    <t>Riley opened the invitation and read-only event view. Fields were disabled; invitation-specific View, Accept and Reject actions were present; no event chat or participant resources were visible. Members remained visible because Open Event allows preview. Demo authentication cannot prove server denial, and the Members screen separately exposed EVENT-MEMBER-CREATOR-001.</t>
   </si>
   <si>
     <t>EVENT-INV-003</t>
@@ -1801,45 +1840,54 @@
     <t>INDIRECT membership and later chat deltas</t>
   </si>
   <si>
-    <t>DELTA accepted membership and resolved invitation</t>
+    <t>DELTA accepted membership, resolved invitation and one Admin acceptance notification</t>
   </si>
   <si>
     <t>INDIRECT after membership recompute</t>
   </si>
   <si>
+    <t>CONDITIONAL direct recompute/notification outbox; scheduler X</t>
+  </si>
+  <si>
+    <t>Pending becomes accepted once; accepted recipient and Admin see the same chat; pending control does not; Admin gets exactly one acceptance notification</t>
+  </si>
+  <si>
+    <t>MANUAL MEMBERSHIP PASS; CHAT AND ADMIN NOTIFICATION FAIL</t>
+  </si>
+  <si>
+    <t>Invitation acceptance service tests; independent read-only membership oracle; chat and acceptance-notification regression coverage required</t>
+  </si>
+  <si>
+    <t>After the backend fix, repeat only the failed positive branches: Riley and Casey share one event chat, Riley sends one unique message to Casey, and Casey receives exactly one acceptance notification; retain Nova as the denied control</t>
+  </si>
+  <si>
+    <t>FAIL / PARTIAL PASS</t>
+  </si>
+  <si>
+    <t>Riley accepted once through the recipient UI. The already-open Riley Active Events, Nova Invitations and Casey My Events projections converged without refresh from 1 / 8 with two pending invitations to 2 / 8 with one pending invitation. Event Members and the exact oracle passed: Casey accepted Admin, Riley accepted Member, Nova pending Member, cleared Riley invitation fields and no duplicates. The three open Chats lists then showed no event channel for any identity: Nova's absence was the correct pending negative control, but Riley accepted and Casey Admin both incorrectly lacked the channel. Casey's notification list also lacked the required acceptance notification for Riley and the controlled event; visible controlled notifications were only the earlier invite/lifecycle items.</t>
+  </si>
+  <si>
+    <t>EVENT-INV-004</t>
+  </si>
+  <si>
+    <t>Event membership approval</t>
+  </si>
+  <si>
+    <t>Accept an ordinary-member invite, then approve as admin</t>
+  </si>
+  <si>
+    <t>INDIRECT only after terminal acceptance</t>
+  </si>
+  <si>
+    <t>DELTA pending approval then accepted membership</t>
+  </si>
+  <si>
+    <t>INDIRECT after terminal transition</t>
+  </si>
+  <si>
     <t>CONDITIONAL recompute/outbox; scheduler X</t>
   </si>
   <si>
-    <t>Pending becomes accepted once; accepted-only chat becomes available</t>
-  </si>
-  <si>
-    <t>Invitation acceptance service tests</t>
-  </si>
-  <si>
-    <t>Match membership, resolved bell and one unique chat write</t>
-  </si>
-  <si>
-    <t>Acceptance and chat authorization are separate oracles</t>
-  </si>
-  <si>
-    <t>EVENT-INV-004</t>
-  </si>
-  <si>
-    <t>Event membership approval</t>
-  </si>
-  <si>
-    <t>Accept an ordinary-member invite, then approve as admin</t>
-  </si>
-  <si>
-    <t>INDIRECT only after terminal acceptance</t>
-  </si>
-  <si>
-    <t>DELTA pending approval then accepted membership</t>
-  </si>
-  <si>
-    <t>INDIRECT after terminal transition</t>
-  </si>
-  <si>
     <t>Chat stays denied before admin approval and appears only afterward</t>
   </si>
   <si>
@@ -1888,7 +1936,7 @@
     <t>Event chat authorization</t>
   </si>
   <si>
-    <t>Compare pending, accepted and left membership against chat access</t>
+    <t>Compare Admin, accepted, pending and left membership against the same event chat</t>
   </si>
   <si>
     <t>INDIRECT only for the one proof message</t>
@@ -1900,16 +1948,19 @@
     <t>X unless the message creates documented delivery work</t>
   </si>
   <si>
-    <t>Server denies pending/left users; accepted user reads and writes once</t>
-  </si>
-  <si>
-    <t>Chat/access-control coverage partial</t>
-  </si>
-  <si>
-    <t>Use isolated sessions and one unique message after acceptance</t>
-  </si>
-  <si>
-    <t>Readable history outside accepted membership is P0</t>
+    <t>Admin and accepted member share history; pending/left users have no channel and are server-denied</t>
+  </si>
+  <si>
+    <t>MANUAL POSITIVE AUTHORIZATION FAIL; NEGATIVE CONTROL PASS</t>
+  </si>
+  <si>
+    <t>Chat/access-control coverage partial; regression required for event-chat materialization on terminal acceptance</t>
+  </si>
+  <si>
+    <t>After the backend fix, keep Casey Admin, Riley accepted and Nova pending isolated sessions open; prove Casey/Riley channel visibility, send one unique Riley message to Casey, and retain Nova absence plus direct denial</t>
+  </si>
+  <si>
+    <t>After Riley reached terminal accepted membership, all three open Chats lists were empty. Nova pending correctly had no channel, but Riley accepted and Casey Admin also lacked the event channel, so the positive materialization/authorization branch failed before a proof message could be sent. This is a backend projection defect, not a UI fallback opportunity.</t>
   </si>
   <si>
     <t>EVENT-FEEDBACK-001</t>
@@ -2610,7 +2661,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P89"/>
+  <dimension ref="A1:P90"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.8"/>
@@ -5286,128 +5337,128 @@
         <v>497</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>455</v>
+        <v>498</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>20</v>
+        <v>501</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>20</v>
+        <v>503</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>20</v>
+        <v>504</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="J54" s="0" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="K54" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L54" s="0" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="M54" s="0" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="N54" s="0" t="s">
-        <v>505</v>
+        <v>48</v>
       </c>
       <c r="O54" s="0" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="P54" s="0" t="s">
-        <v>188</v>
+        <v>510</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>510</v>
+        <v>20</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>448</v>
+        <v>20</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>512</v>
+        <v>20</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J55" s="0" t="s">
-        <v>55</v>
+        <v>506</v>
       </c>
       <c r="K55" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="M55" s="0" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="N55" s="0" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="O55" s="0" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="P55" s="0" t="s">
-        <v>143</v>
+        <v>188</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B56" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>444</v>
+        <v>520</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>521</v>
+        <v>448</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="J56" s="0" t="s">
         <v>55</v>
@@ -5416,148 +5467,148 @@
         <v>22</v>
       </c>
       <c r="L56" s="0" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M56" s="0" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N56" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O56" s="0" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="P56" s="0" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B57" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>528</v>
+        <v>444</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>469</v>
+        <v>532</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>448</v>
+        <v>533</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="J57" s="0" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="K57" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="M57" s="0" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="N57" s="0" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="O57" s="0" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="P57" s="0" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B58" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>539</v>
+        <v>469</v>
       </c>
       <c r="G58" s="0" t="s">
         <v>448</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="J58" s="0" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="K58" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="L58" s="0" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="M58" s="0" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="N58" s="0" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="O58" s="0" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="P58" s="0" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B59" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="G59" s="0" t="s">
         <v>448</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="J59" s="0" t="s">
         <v>55</v>
@@ -5566,48 +5617,48 @@
         <v>22</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="M59" s="0" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="N59" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O59" s="0" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="P59" s="0" t="s">
-        <v>166</v>
+        <v>223</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B60" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>555</v>
+        <v>540</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>559</v>
+        <v>448</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="J60" s="0" t="s">
         <v>55</v>
@@ -5616,48 +5667,48 @@
         <v>22</v>
       </c>
       <c r="L60" s="0" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M60" s="0" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N60" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O60" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P60" s="0" t="s">
-        <v>223</v>
+        <v>166</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B61" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>20</v>
+        <v>569</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>20</v>
+        <v>570</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>20</v>
+        <v>571</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>20</v>
+        <v>572</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="J61" s="0" t="s">
         <v>55</v>
@@ -5666,48 +5717,48 @@
         <v>22</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="M61" s="0" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="N61" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O61" s="0" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="P61" s="0" t="s">
-        <v>103</v>
+        <v>223</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="B62" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>575</v>
+        <v>20</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>576</v>
+        <v>20</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>577</v>
+        <v>20</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>578</v>
+        <v>20</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="J62" s="0" t="s">
         <v>55</v>
@@ -5716,48 +5767,48 @@
         <v>22</v>
       </c>
       <c r="L62" s="0" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M62" s="0" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N62" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O62" s="0" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="P62" s="0" t="s">
-        <v>166</v>
+        <v>103</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B63" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>20</v>
+        <v>587</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>20</v>
+        <v>588</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>20</v>
+        <v>589</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>20</v>
+        <v>590</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="J63" s="0" t="s">
         <v>55</v>
@@ -5766,116 +5817,116 @@
         <v>22</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="M63" s="0" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="N63" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O63" s="0" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="P63" s="0" t="s">
-        <v>429</v>
+        <v>166</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B64" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>573</v>
+        <v>596</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>592</v>
+        <v>20</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>593</v>
+        <v>20</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>594</v>
+        <v>20</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>595</v>
+        <v>20</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="J64" s="0" t="s">
-        <v>55</v>
+        <v>599</v>
       </c>
       <c r="K64" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="L64" s="0" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="M64" s="0" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="N64" s="0" t="s">
-        <v>22</v>
+        <v>439</v>
       </c>
       <c r="O64" s="0" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="P64" s="0" t="s">
-        <v>388</v>
+        <v>429</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B65" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>595</v>
+        <v>608</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="J65" s="0" t="s">
-        <v>55</v>
+        <v>610</v>
       </c>
       <c r="K65" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="M65" s="0" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="N65" s="0" t="s">
-        <v>22</v>
+        <v>613</v>
       </c>
       <c r="O65" s="0" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="P65" s="0" t="s">
         <v>429</v>
@@ -5883,31 +5934,31 @@
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="B66" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="J66" s="0" t="s">
         <v>55</v>
@@ -5916,48 +5967,48 @@
         <v>22</v>
       </c>
       <c r="L66" s="0" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="M66" s="0" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="N66" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O66" s="0" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="P66" s="0" t="s">
-        <v>388</v>
+        <v>429</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="B67" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>20</v>
+        <v>629</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="J67" s="0" t="s">
         <v>55</v>
@@ -5966,98 +6017,98 @@
         <v>22</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="M67" s="0" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="N67" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O67" s="0" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="P67" s="0" t="s">
-        <v>429</v>
+        <v>388</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="B68" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>20</v>
+        <v>639</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>20</v>
+        <v>640</v>
       </c>
       <c r="G68" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>20</v>
+        <v>641</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>633</v>
+        <v>642</v>
       </c>
       <c r="J68" s="0" t="s">
-        <v>55</v>
+        <v>643</v>
       </c>
       <c r="K68" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="L68" s="0" t="s">
-        <v>634</v>
+        <v>644</v>
       </c>
       <c r="M68" s="0" t="s">
-        <v>635</v>
+        <v>645</v>
       </c>
       <c r="N68" s="0" t="s">
-        <v>22</v>
+        <v>613</v>
       </c>
       <c r="O68" s="0" t="s">
-        <v>636</v>
+        <v>646</v>
       </c>
       <c r="P68" s="0" t="s">
-        <v>143</v>
+        <v>429</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>637</v>
+        <v>647</v>
       </c>
       <c r="B69" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>631</v>
+        <v>648</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>638</v>
+        <v>649</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>639</v>
+        <v>20</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>640</v>
+        <v>20</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>641</v>
+        <v>20</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>642</v>
+        <v>20</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="J69" s="0" t="s">
         <v>55</v>
@@ -6066,48 +6117,48 @@
         <v>22</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="M69" s="0" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="N69" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O69" s="0" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="P69" s="0" t="s">
-        <v>223</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="B70" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>631</v>
+        <v>648</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="J70" s="0" t="s">
         <v>55</v>
@@ -6116,48 +6167,48 @@
         <v>22</v>
       </c>
       <c r="L70" s="0" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="M70" s="0" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="N70" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O70" s="0" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="P70" s="0" t="s">
-        <v>143</v>
+        <v>223</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="B71" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>20</v>
+        <v>668</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>20</v>
+        <v>669</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="J71" s="0" t="s">
         <v>55</v>
@@ -6166,39 +6217,39 @@
         <v>22</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="M71" s="0" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="N71" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O71" s="0" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="P71" s="0" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="B72" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>20</v>
+        <v>677</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
       <c r="G72" s="0" t="s">
         <v>20</v>
@@ -6207,7 +6258,7 @@
         <v>20</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>670</v>
+        <v>679</v>
       </c>
       <c r="J72" s="0" t="s">
         <v>55</v>
@@ -6216,48 +6267,48 @@
         <v>22</v>
       </c>
       <c r="L72" s="0" t="s">
-        <v>671</v>
+        <v>680</v>
       </c>
       <c r="M72" s="0" t="s">
-        <v>672</v>
+        <v>681</v>
       </c>
       <c r="N72" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O72" s="0" t="s">
-        <v>673</v>
+        <v>682</v>
       </c>
       <c r="P72" s="0" t="s">
-        <v>188</v>
+        <v>153</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>674</v>
+        <v>683</v>
       </c>
       <c r="B73" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="E73" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>677</v>
+        <v>686</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>678</v>
+        <v>20</v>
       </c>
       <c r="H73" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="J73" s="0" t="s">
         <v>55</v>
@@ -6266,48 +6317,48 @@
         <v>22</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="M73" s="0" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="N73" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O73" s="0" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="P73" s="0" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="B74" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>686</v>
+        <v>20</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>448</v>
+        <v>695</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>688</v>
+        <v>20</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="J74" s="0" t="s">
         <v>55</v>
@@ -6316,48 +6367,48 @@
         <v>22</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="M74" s="0" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="N74" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O74" s="0" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="P74" s="0" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="B75" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>684</v>
+        <v>701</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>20</v>
+        <v>703</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>20</v>
+        <v>704</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>20</v>
+        <v>448</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>20</v>
+        <v>705</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="J75" s="0" t="s">
         <v>55</v>
@@ -6366,36 +6417,36 @@
         <v>22</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>696</v>
+        <v>707</v>
       </c>
       <c r="M75" s="0" t="s">
-        <v>697</v>
+        <v>708</v>
       </c>
       <c r="N75" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O75" s="0" t="s">
-        <v>698</v>
+        <v>709</v>
       </c>
       <c r="P75" s="0" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>699</v>
+        <v>710</v>
       </c>
       <c r="B76" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>684</v>
+        <v>701</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>700</v>
+        <v>711</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>701</v>
+        <v>20</v>
       </c>
       <c r="F76" s="0" t="s">
         <v>20</v>
@@ -6407,7 +6458,7 @@
         <v>20</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>702</v>
+        <v>712</v>
       </c>
       <c r="J76" s="0" t="s">
         <v>55</v>
@@ -6416,48 +6467,48 @@
         <v>22</v>
       </c>
       <c r="L76" s="0" t="s">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="M76" s="0" t="s">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="N76" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O76" s="0" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="P76" s="0" t="s">
-        <v>388</v>
+        <v>223</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="B77" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>708</v>
+        <v>717</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>709</v>
+        <v>718</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>710</v>
+        <v>20</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>711</v>
+        <v>20</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>712</v>
+        <v>20</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="J77" s="0" t="s">
         <v>55</v>
@@ -6466,16 +6517,16 @@
         <v>22</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="M77" s="0" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="N77" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O77" s="0" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="P77" s="0" t="s">
         <v>388</v>
@@ -6483,31 +6534,31 @@
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="B78" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>711</v>
+        <v>728</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="J78" s="0" t="s">
         <v>55</v>
@@ -6516,48 +6567,48 @@
         <v>22</v>
       </c>
       <c r="L78" s="0" t="s">
-        <v>514</v>
+        <v>731</v>
       </c>
       <c r="M78" s="0" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="N78" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O78" s="0" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P78" s="0" t="s">
-        <v>143</v>
+        <v>388</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="B79" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>718</v>
+        <v>735</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>727</v>
+        <v>736</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>478</v>
+        <v>737</v>
       </c>
       <c r="F79" s="0" t="s">
+        <v>738</v>
+      </c>
+      <c r="G79" s="0" t="s">
         <v>728</v>
       </c>
-      <c r="G79" s="0" t="s">
-        <v>729</v>
-      </c>
       <c r="H79" s="0" t="s">
-        <v>730</v>
+        <v>739</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>731</v>
+        <v>740</v>
       </c>
       <c r="J79" s="0" t="s">
         <v>55</v>
@@ -6566,48 +6617,48 @@
         <v>22</v>
       </c>
       <c r="L79" s="0" t="s">
-        <v>732</v>
+        <v>526</v>
       </c>
       <c r="M79" s="0" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="N79" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O79" s="0" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="P79" s="0" t="s">
-        <v>223</v>
+        <v>143</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="B80" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>718</v>
+        <v>735</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>737</v>
+        <v>478</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="J80" s="0" t="s">
         <v>55</v>
@@ -6616,48 +6667,48 @@
         <v>22</v>
       </c>
       <c r="L80" s="0" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="M80" s="0" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="N80" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O80" s="0" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="P80" s="0" t="s">
-        <v>388</v>
+        <v>223</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="B81" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>20</v>
+        <v>756</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>578</v>
+        <v>757</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="J81" s="0" t="s">
         <v>55</v>
@@ -6666,48 +6717,48 @@
         <v>22</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="M81" s="0" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="N81" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O81" s="0" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="P81" s="0" t="s">
-        <v>143</v>
+        <v>388</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B82" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>746</v>
+        <v>763</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>755</v>
+        <v>764</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>756</v>
+        <v>766</v>
       </c>
       <c r="G82" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>757</v>
+        <v>590</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="J82" s="0" t="s">
         <v>55</v>
@@ -6716,24 +6767,24 @@
         <v>22</v>
       </c>
       <c r="L82" s="0" t="s">
-        <v>759</v>
+        <v>768</v>
       </c>
       <c r="M82" s="0" t="s">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="N82" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O82" s="0" t="s">
-        <v>761</v>
+        <v>770</v>
       </c>
       <c r="P82" s="0" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>762</v>
+        <v>771</v>
       </c>
       <c r="B83" s="0" t="s">
         <v>443</v>
@@ -6742,22 +6793,22 @@
         <v>763</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="E83" s="0" t="s">
         <v>765</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="G83" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="J83" s="0" t="s">
         <v>55</v>
@@ -6766,16 +6817,16 @@
         <v>22</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="M83" s="0" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="N83" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O83" s="0" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="P83" s="0" t="s">
         <v>166</v>
@@ -6783,31 +6834,31 @@
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="B84" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>20</v>
+        <v>782</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="G84" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="J84" s="0" t="s">
         <v>55</v>
@@ -6816,48 +6867,48 @@
         <v>22</v>
       </c>
       <c r="L84" s="0" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="M84" s="0" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="N84" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O84" s="0" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="P84" s="0" t="s">
-        <v>429</v>
+        <v>166</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="B85" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>784</v>
+        <v>20</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>711</v>
+        <v>20</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="J85" s="0" t="s">
         <v>55</v>
@@ -6866,48 +6917,48 @@
         <v>22</v>
       </c>
       <c r="L85" s="0" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="M85" s="0" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="N85" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O85" s="0" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="P85" s="0" t="s">
-        <v>166</v>
+        <v>429</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="B86" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>20</v>
+        <v>801</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>20</v>
+        <v>802</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>20</v>
+        <v>728</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>20</v>
+        <v>803</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>794</v>
+        <v>804</v>
       </c>
       <c r="J86" s="0" t="s">
         <v>55</v>
@@ -6916,48 +6967,48 @@
         <v>22</v>
       </c>
       <c r="L86" s="0" t="s">
-        <v>795</v>
+        <v>805</v>
       </c>
       <c r="M86" s="0" t="s">
-        <v>796</v>
+        <v>806</v>
       </c>
       <c r="N86" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O86" s="0" t="s">
-        <v>797</v>
+        <v>807</v>
       </c>
       <c r="P86" s="0" t="s">
-        <v>223</v>
+        <v>166</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>798</v>
+        <v>808</v>
       </c>
       <c r="B87" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>799</v>
+        <v>809</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>800</v>
+        <v>810</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>801</v>
+        <v>20</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>802</v>
+        <v>20</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>448</v>
+        <v>20</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>803</v>
+        <v>20</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="J87" s="0" t="s">
         <v>55</v>
@@ -6966,48 +7017,48 @@
         <v>22</v>
       </c>
       <c r="L87" s="0" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="M87" s="0" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="N87" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O87" s="0" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="P87" s="0" t="s">
-        <v>388</v>
+        <v>223</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="B88" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="G88" s="0" t="s">
         <v>448</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="J88" s="0" t="s">
         <v>55</v>
@@ -7016,16 +7067,16 @@
         <v>22</v>
       </c>
       <c r="L88" s="0" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="M88" s="0" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="N88" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O88" s="0" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="P88" s="0" t="s">
         <v>388</v>
@@ -7033,51 +7084,101 @@
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>819</v>
+        <v>443</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>20</v>
+        <v>828</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>20</v>
+        <v>829</v>
       </c>
       <c r="G89" s="0" t="s">
-        <v>20</v>
+        <v>448</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>20</v>
+        <v>830</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>822</v>
+        <v>831</v>
       </c>
       <c r="J89" s="0" t="s">
-        <v>823</v>
+        <v>55</v>
       </c>
       <c r="K89" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="L89" s="0" t="s">
+        <v>832</v>
+      </c>
+      <c r="M89" s="0" t="s">
+        <v>833</v>
+      </c>
+      <c r="N89" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="O89" s="0" t="s">
+        <v>834</v>
+      </c>
+      <c r="P89" s="0" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="0" t="s">
+        <v>835</v>
+      </c>
+      <c r="B90" s="0" t="s">
+        <v>836</v>
+      </c>
+      <c r="C90" s="0" t="s">
+        <v>837</v>
+      </c>
+      <c r="D90" s="0" t="s">
+        <v>838</v>
+      </c>
+      <c r="E90" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F90" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G90" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H90" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I90" s="0" t="s">
+        <v>839</v>
+      </c>
+      <c r="J90" s="0" t="s">
+        <v>840</v>
+      </c>
+      <c r="K90" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="L89" s="0" t="s">
-        <v>824</v>
-      </c>
-      <c r="M89" s="0" t="s">
-        <v>825</v>
-      </c>
-      <c r="N89" s="0" t="s">
-        <v>826</v>
-      </c>
-      <c r="O89" s="0" t="s">
-        <v>827</v>
-      </c>
-      <c r="P89" s="0" t="s">
+      <c r="L90" s="0" t="s">
+        <v>841</v>
+      </c>
+      <c r="M90" s="0" t="s">
+        <v>842</v>
+      </c>
+      <c r="N90" s="0" t="s">
+        <v>843</v>
+      </c>
+      <c r="O90" s="0" t="s">
+        <v>844</v>
+      </c>
+      <c r="P90" s="0" t="s">
         <v>239</v>
       </c>
     </row>

--- a/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
+++ b/guides/plans/ADMIN_DYNAMIC_SURFACES_QA_MATRIX.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="845">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="858">
   <si>
     <t>ID</t>
   </si>
@@ -1447,6 +1447,42 @@
     <t>Casey published once: the same h1785836388222 identity became active, remained once in My Events, left Drafts and kept 18:00-20:00 local / 16:00Z-18:00Z persisted. One deduplicated recompute task refreshed, outbox stayed zero, and Nova received no invitation/counter and saw no Aug 6 event in Explore. A helper-only dynamic-ID selector defect was corrected before the final oracle.</t>
   </si>
   <si>
+    <t>EVENT-PUBLISH-CHAT-001</t>
+  </si>
+  <si>
+    <t>Defect retest / lifecycle checkpoint</t>
+  </si>
+  <si>
+    <t>Event publish + chat authorization and persisted counters</t>
+  </si>
+  <si>
+    <t>Stage one isolated Draft with Casey accepted and Nova/Riley pending, record all three Chat baselines, then publish once from the Casey Draft card</t>
+  </si>
+  <si>
+    <t>DELTA publish lifecycle, event recompute, exactly one main-event chat and updated Users.activities counts</t>
+  </si>
+  <si>
+    <t>DELTA normal publish recompute; scheduler X</t>
+  </si>
+  <si>
+    <t>Casey gains exactly one unread event-chat row and immediate +1 top Chats / Chat All / Event counters; My Events remains 1 while Drafts changes 1 to 0; reload agrees with backend; Nova and Riley chat rows and counters remain unchanged; active card is 1 / 8 with pending badge 2; acceptance notification X</t>
+  </si>
+  <si>
+    <t>IMPLEMENTATION COMPLETE; CLEAN MANUAL RETEST STAGED</t>
+  </si>
+  <si>
+    <t>Running hot-deploy frontend/backend builds green; focused local frontend suites 12/12; backend unit rerun stopped under memory pressure and remains pending</t>
+  </si>
+  <si>
+    <t>Publish once from Casey Drafts. Require immediate Casey top Chats +1, exactly one Casey event chat, My Events still 1, the same counters after reload, no Nova/Riley chat change and no invitation-accepted notification.</t>
+  </si>
+  <si>
+    <t>CLEAN RETEST READY / PRIOR FAIL RETAINED</t>
+  </si>
+  <si>
+    <t>Historical failure first omitted the Admin event chat, then the materialized chat did not update the top Chats badge. The mutation persists only Users.activities counts and returns only operation-owned unit bucket directions (-1/+1), never a global counter diff; the periodic poll reconciles concurrent changes. Components only patch their cache from that response. A new deterministic Draft is staged as manual-qa-checkpoint:v1:event-domain:event with zero chats and zero action deltas.</t>
+  </si>
+  <si>
     <t>EVENT-EDITOR-003</t>
   </si>
   <si>
@@ -1852,112 +1888,115 @@
     <t>Pending becomes accepted once; accepted recipient and Admin see the same chat; pending control does not; Admin gets exactly one acceptance notification</t>
   </si>
   <si>
-    <t>MANUAL MEMBERSHIP PASS; CHAT AND ADMIN NOTIFICATION FAIL</t>
-  </si>
-  <si>
-    <t>Invitation acceptance service tests; independent read-only membership oracle; chat and acceptance-notification regression coverage required</t>
-  </si>
-  <si>
-    <t>After the backend fix, repeat only the failed positive branches: Riley and Casey share one event chat, Riley sends one unique message to Casey, and Casey receives exactly one acceptance notification; retain Nova as the denied control</t>
+    <t>BACKEND FIX AND REGRESSION PASS; FOCUSED MANUAL RETEST READY</t>
+  </si>
+  <si>
+    <t>Invitation acceptance, event-chat materialization and Admin acceptance-notification service regressions pass 64/64; independent read-only membership, chat and notification oracle</t>
+  </si>
+  <si>
+    <t>In Riley's already-open Invitations view, accept once. Without refresh, verify convergence to 2 / 8 and one pending invitation; verify Riley and Casey share the event chat, Riley can send one unique message to Casey, Nova remains denied, and Casey receives exactly one acceptance notification.</t>
+  </si>
+  <si>
+    <t>RETEST READY / PRIOR FAIL RETAINED</t>
+  </si>
+  <si>
+    <t>The original run passed membership and projection convergence but failed the accepted-user/Admin chat and Admin acceptance-notification branches; Nova correctly remained the denied pending control. After the backend fix and 64/64 regression pass, the guarded manual retest preparation re-armed only Riley on the same event: Casey is accepted Admin, Nova and Riley are pending Members, occupancy is 1 / 8 with two pending invitations, and no event chat or acceptance notification exists. The original failed evidence remains part of this checkpoint history.</t>
+  </si>
+  <si>
+    <t>EVENT-INV-004</t>
+  </si>
+  <si>
+    <t>Event membership approval</t>
+  </si>
+  <si>
+    <t>Accept an ordinary-member invite, then approve as admin</t>
+  </si>
+  <si>
+    <t>INDIRECT only after terminal acceptance</t>
+  </si>
+  <si>
+    <t>DELTA pending approval then accepted membership</t>
+  </si>
+  <si>
+    <t>INDIRECT after terminal transition</t>
+  </si>
+  <si>
+    <t>CONDITIONAL recompute/outbox; scheduler X</t>
+  </si>
+  <si>
+    <t>Chat stays denied before admin approval and appears only afterward</t>
+  </si>
+  <si>
+    <t>Invitation approval service tests partial</t>
+  </si>
+  <si>
+    <t>Capture both pending states and the final accepted state</t>
+  </si>
+  <si>
+    <t>Recipient acceptance alone must not bypass approval</t>
+  </si>
+  <si>
+    <t>EVENT-INV-005</t>
+  </si>
+  <si>
+    <t>Event membership edges</t>
+  </si>
+  <si>
+    <t>Reject, cancel, capacity-block and repeat acceptance independently</t>
+  </si>
+  <si>
+    <t>INDIRECT only for real state changes</t>
+  </si>
+  <si>
+    <t>DELTA per real mutation; no-op repeats X</t>
+  </si>
+  <si>
+    <t>CONDITIONAL; duplicate tasks/outbox forbidden</t>
+  </si>
+  <si>
+    <t>No duplicate member, overbooking, stale bell or rejected-user chat access</t>
+  </si>
+  <si>
+    <t>Capacity/idempotence service tests partial</t>
+  </si>
+  <si>
+    <t>Run every branch as its own named checkpoint lineage</t>
+  </si>
+  <si>
+    <t>Negative branches remain independently passable</t>
+  </si>
+  <si>
+    <t>CHAT-AUTH-001</t>
+  </si>
+  <si>
+    <t>Event chat authorization</t>
+  </si>
+  <si>
+    <t>Compare Admin, accepted, pending and left membership against the same event chat</t>
+  </si>
+  <si>
+    <t>INDIRECT only for the one proof message</t>
+  </si>
+  <si>
+    <t>DELTA chat write only after accepted state</t>
+  </si>
+  <si>
+    <t>X unless the message creates documented delivery work</t>
+  </si>
+  <si>
+    <t>Admin and accepted member share history; pending/left users have no channel and are server-denied</t>
+  </si>
+  <si>
+    <t>MANUAL POSITIVE AUTHORIZATION FAIL; NEGATIVE CONTROL PASS</t>
+  </si>
+  <si>
+    <t>Chat/access-control coverage partial; regression required for event-chat materialization on terminal acceptance</t>
+  </si>
+  <si>
+    <t>After the backend fix, keep Casey Admin, Riley accepted and Nova pending isolated sessions open; prove Casey/Riley channel visibility, send one unique Riley message to Casey, and retain Nova absence plus direct denial</t>
   </si>
   <si>
     <t>FAIL / PARTIAL PASS</t>
-  </si>
-  <si>
-    <t>Riley accepted once through the recipient UI. The already-open Riley Active Events, Nova Invitations and Casey My Events projections converged without refresh from 1 / 8 with two pending invitations to 2 / 8 with one pending invitation. Event Members and the exact oracle passed: Casey accepted Admin, Riley accepted Member, Nova pending Member, cleared Riley invitation fields and no duplicates. The three open Chats lists then showed no event channel for any identity: Nova's absence was the correct pending negative control, but Riley accepted and Casey Admin both incorrectly lacked the channel. Casey's notification list also lacked the required acceptance notification for Riley and the controlled event; visible controlled notifications were only the earlier invite/lifecycle items.</t>
-  </si>
-  <si>
-    <t>EVENT-INV-004</t>
-  </si>
-  <si>
-    <t>Event membership approval</t>
-  </si>
-  <si>
-    <t>Accept an ordinary-member invite, then approve as admin</t>
-  </si>
-  <si>
-    <t>INDIRECT only after terminal acceptance</t>
-  </si>
-  <si>
-    <t>DELTA pending approval then accepted membership</t>
-  </si>
-  <si>
-    <t>INDIRECT after terminal transition</t>
-  </si>
-  <si>
-    <t>CONDITIONAL recompute/outbox; scheduler X</t>
-  </si>
-  <si>
-    <t>Chat stays denied before admin approval and appears only afterward</t>
-  </si>
-  <si>
-    <t>Invitation approval service tests partial</t>
-  </si>
-  <si>
-    <t>Capture both pending states and the final accepted state</t>
-  </si>
-  <si>
-    <t>Recipient acceptance alone must not bypass approval</t>
-  </si>
-  <si>
-    <t>EVENT-INV-005</t>
-  </si>
-  <si>
-    <t>Event membership edges</t>
-  </si>
-  <si>
-    <t>Reject, cancel, capacity-block and repeat acceptance independently</t>
-  </si>
-  <si>
-    <t>INDIRECT only for real state changes</t>
-  </si>
-  <si>
-    <t>DELTA per real mutation; no-op repeats X</t>
-  </si>
-  <si>
-    <t>CONDITIONAL; duplicate tasks/outbox forbidden</t>
-  </si>
-  <si>
-    <t>No duplicate member, overbooking, stale bell or rejected-user chat access</t>
-  </si>
-  <si>
-    <t>Capacity/idempotence service tests partial</t>
-  </si>
-  <si>
-    <t>Run every branch as its own named checkpoint lineage</t>
-  </si>
-  <si>
-    <t>Negative branches remain independently passable</t>
-  </si>
-  <si>
-    <t>CHAT-AUTH-001</t>
-  </si>
-  <si>
-    <t>Event chat authorization</t>
-  </si>
-  <si>
-    <t>Compare Admin, accepted, pending and left membership against the same event chat</t>
-  </si>
-  <si>
-    <t>INDIRECT only for the one proof message</t>
-  </si>
-  <si>
-    <t>DELTA chat write only after accepted state</t>
-  </si>
-  <si>
-    <t>X unless the message creates documented delivery work</t>
-  </si>
-  <si>
-    <t>Admin and accepted member share history; pending/left users have no channel and are server-denied</t>
-  </si>
-  <si>
-    <t>MANUAL POSITIVE AUTHORIZATION FAIL; NEGATIVE CONTROL PASS</t>
-  </si>
-  <si>
-    <t>Chat/access-control coverage partial; regression required for event-chat materialization on terminal acceptance</t>
-  </si>
-  <si>
-    <t>After the backend fix, keep Casey Admin, Riley accepted and Nova pending isolated sessions open; prove Casey/Riley channel visibility, send one unique Riley message to Casey, and retain Nova absence plus direct denial</t>
   </si>
   <si>
     <t>After Riley reached terminal accepted membership, all three open Chats lists were empty. Nova pending correctly had no channel, but Riley accepted and Casey Admin also lacked the event channel, so the positive materialization/authorization branch failed before a proof message could be sent. This is a backend projection defect, not a UI fallback opportunity.</t>
@@ -2661,7 +2700,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P90"/>
+  <dimension ref="A1:P91"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.8"/>
@@ -5237,31 +5276,31 @@
         <v>475</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>443</v>
+        <v>476</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="F52" s="0" t="s">
         <v>479</v>
       </c>
       <c r="G52" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H52" s="0" t="s">
         <v>480</v>
       </c>
-      <c r="H52" s="0" t="s">
+      <c r="I52" s="0" t="s">
         <v>481</v>
       </c>
-      <c r="I52" s="0" t="s">
+      <c r="J52" s="0" t="s">
         <v>482</v>
-      </c>
-      <c r="J52" s="0" t="s">
-        <v>88</v>
       </c>
       <c r="K52" s="0" t="s">
         <v>45</v>
@@ -5273,21 +5312,21 @@
         <v>484</v>
       </c>
       <c r="N52" s="0" t="s">
-        <v>48</v>
+        <v>485</v>
       </c>
       <c r="O52" s="0" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P52" s="0" t="s">
-        <v>166</v>
+        <v>429</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>487</v>
+        <v>443</v>
       </c>
       <c r="C53" s="0" t="s">
         <v>488</v>
@@ -5296,219 +5335,219 @@
         <v>489</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>20</v>
+        <v>490</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>20</v>
+        <v>492</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="J53" s="0" t="s">
-        <v>493</v>
+        <v>88</v>
       </c>
       <c r="K53" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M53" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N53" s="0" t="s">
         <v>48</v>
       </c>
       <c r="O53" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P53" s="0" t="s">
-        <v>81</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>501</v>
+        <v>20</v>
       </c>
       <c r="F54" s="0" t="s">
         <v>502</v>
       </c>
       <c r="G54" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H54" s="0" t="s">
         <v>503</v>
       </c>
-      <c r="H54" s="0" t="s">
+      <c r="I54" s="0" t="s">
         <v>504</v>
       </c>
-      <c r="I54" s="0" t="s">
+      <c r="J54" s="0" t="s">
         <v>505</v>
-      </c>
-      <c r="J54" s="0" t="s">
-        <v>506</v>
       </c>
       <c r="K54" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L54" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="M54" s="0" t="s">
         <v>507</v>
-      </c>
-      <c r="M54" s="0" t="s">
-        <v>508</v>
       </c>
       <c r="N54" s="0" t="s">
         <v>48</v>
       </c>
       <c r="O54" s="0" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="P54" s="0" t="s">
-        <v>510</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
+        <v>509</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>510</v>
+      </c>
+      <c r="C55" s="0" t="s">
         <v>511</v>
       </c>
-      <c r="B55" s="0" t="s">
-        <v>455</v>
-      </c>
-      <c r="C55" s="0" t="s">
+      <c r="D55" s="0" t="s">
         <v>512</v>
       </c>
-      <c r="D55" s="0" t="s">
+      <c r="E55" s="0" t="s">
         <v>513</v>
-      </c>
-      <c r="E55" s="0" t="s">
-        <v>20</v>
       </c>
       <c r="F55" s="0" t="s">
         <v>514</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>20</v>
+        <v>515</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>20</v>
+        <v>516</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J55" s="0" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="K55" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="M55" s="0" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="N55" s="0" t="s">
         <v>48</v>
       </c>
       <c r="O55" s="0" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="P55" s="0" t="s">
-        <v>188</v>
+        <v>522</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>522</v>
+        <v>20</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>448</v>
+        <v>20</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>524</v>
+        <v>20</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="J56" s="0" t="s">
-        <v>55</v>
+        <v>518</v>
       </c>
       <c r="K56" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="L56" s="0" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M56" s="0" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="N56" s="0" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="O56" s="0" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="P56" s="0" t="s">
-        <v>143</v>
+        <v>188</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B57" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>444</v>
+        <v>532</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>533</v>
+        <v>448</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="J57" s="0" t="s">
         <v>55</v>
@@ -5517,148 +5556,148 @@
         <v>22</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="M57" s="0" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="N57" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O57" s="0" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="P57" s="0" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B58" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>540</v>
+        <v>444</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>469</v>
+        <v>544</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>448</v>
+        <v>545</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="J58" s="0" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="K58" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="L58" s="0" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="M58" s="0" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="N58" s="0" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="O58" s="0" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="P58" s="0" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B59" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>551</v>
+        <v>469</v>
       </c>
       <c r="G59" s="0" t="s">
         <v>448</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="J59" s="0" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="K59" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="M59" s="0" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="N59" s="0" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="O59" s="0" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="P59" s="0" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B60" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="G60" s="0" t="s">
         <v>448</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="J60" s="0" t="s">
         <v>55</v>
@@ -5667,48 +5706,48 @@
         <v>22</v>
       </c>
       <c r="L60" s="0" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="M60" s="0" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="N60" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O60" s="0" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="P60" s="0" t="s">
-        <v>166</v>
+        <v>223</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="B61" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>567</v>
+        <v>552</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>571</v>
+        <v>448</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="J61" s="0" t="s">
         <v>55</v>
@@ -5717,48 +5756,48 @@
         <v>22</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M61" s="0" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N61" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O61" s="0" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="P61" s="0" t="s">
-        <v>223</v>
+        <v>166</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B62" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>20</v>
+        <v>581</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>20</v>
+        <v>582</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>20</v>
+        <v>583</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>20</v>
+        <v>584</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="J62" s="0" t="s">
         <v>55</v>
@@ -5767,48 +5806,48 @@
         <v>22</v>
       </c>
       <c r="L62" s="0" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="M62" s="0" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="N62" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O62" s="0" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="P62" s="0" t="s">
-        <v>103</v>
+        <v>223</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="B63" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>587</v>
+        <v>20</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>588</v>
+        <v>20</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>589</v>
+        <v>20</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>590</v>
+        <v>20</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="J63" s="0" t="s">
         <v>55</v>
@@ -5817,113 +5856,113 @@
         <v>22</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M63" s="0" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N63" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O63" s="0" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="P63" s="0" t="s">
-        <v>166</v>
+        <v>103</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B64" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>20</v>
+        <v>599</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>20</v>
+        <v>600</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>20</v>
+        <v>601</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>20</v>
+        <v>602</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="J64" s="0" t="s">
-        <v>599</v>
+        <v>55</v>
       </c>
       <c r="K64" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="L64" s="0" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="M64" s="0" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="N64" s="0" t="s">
-        <v>439</v>
+        <v>22</v>
       </c>
       <c r="O64" s="0" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="P64" s="0" t="s">
-        <v>429</v>
+        <v>166</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B65" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>585</v>
+        <v>608</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>605</v>
+        <v>20</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>606</v>
+        <v>20</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>607</v>
+        <v>20</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>608</v>
+        <v>20</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="J65" s="0" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K65" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M65" s="0" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N65" s="0" t="s">
-        <v>613</v>
+        <v>439</v>
       </c>
       <c r="O65" s="0" t="s">
         <v>614</v>
@@ -5940,31 +5979,31 @@
         <v>443</v>
       </c>
       <c r="C66" s="0" t="s">
+        <v>597</v>
+      </c>
+      <c r="D66" s="0" t="s">
         <v>616</v>
       </c>
-      <c r="D66" s="0" t="s">
+      <c r="E66" s="0" t="s">
         <v>617</v>
       </c>
-      <c r="E66" s="0" t="s">
+      <c r="F66" s="0" t="s">
         <v>618</v>
       </c>
-      <c r="F66" s="0" t="s">
+      <c r="G66" s="0" t="s">
         <v>619</v>
       </c>
-      <c r="G66" s="0" t="s">
+      <c r="H66" s="0" t="s">
         <v>620</v>
       </c>
-      <c r="H66" s="0" t="s">
+      <c r="I66" s="0" t="s">
         <v>621</v>
       </c>
-      <c r="I66" s="0" t="s">
+      <c r="J66" s="0" t="s">
         <v>622</v>
       </c>
-      <c r="J66" s="0" t="s">
-        <v>55</v>
-      </c>
       <c r="K66" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="L66" s="0" t="s">
         <v>623</v>
@@ -5973,10 +6012,10 @@
         <v>624</v>
       </c>
       <c r="N66" s="0" t="s">
-        <v>22</v>
+        <v>625</v>
       </c>
       <c r="O66" s="0" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="P66" s="0" t="s">
         <v>429</v>
@@ -5984,31 +6023,31 @@
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B67" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="J67" s="0" t="s">
         <v>55</v>
@@ -6017,148 +6056,148 @@
         <v>22</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="M67" s="0" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="N67" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O67" s="0" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="P67" s="0" t="s">
-        <v>388</v>
+        <v>429</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B68" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>20</v>
+        <v>641</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="J68" s="0" t="s">
-        <v>643</v>
+        <v>55</v>
       </c>
       <c r="K68" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="L68" s="0" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M68" s="0" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N68" s="0" t="s">
-        <v>613</v>
+        <v>22</v>
       </c>
       <c r="O68" s="0" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="P68" s="0" t="s">
-        <v>429</v>
+        <v>388</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B69" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>20</v>
+        <v>651</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>20</v>
+        <v>652</v>
       </c>
       <c r="G69" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>20</v>
+        <v>653</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="J69" s="0" t="s">
-        <v>55</v>
+        <v>655</v>
       </c>
       <c r="K69" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="M69" s="0" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="N69" s="0" t="s">
-        <v>22</v>
+        <v>658</v>
       </c>
       <c r="O69" s="0" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="P69" s="0" t="s">
-        <v>143</v>
+        <v>429</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="B70" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>648</v>
+        <v>661</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>656</v>
+        <v>20</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>657</v>
+        <v>20</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>658</v>
+        <v>20</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>659</v>
+        <v>20</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="J70" s="0" t="s">
         <v>55</v>
@@ -6167,48 +6206,48 @@
         <v>22</v>
       </c>
       <c r="L70" s="0" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="M70" s="0" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="N70" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O70" s="0" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="P70" s="0" t="s">
-        <v>223</v>
+        <v>143</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="B71" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>648</v>
+        <v>661</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="J71" s="0" t="s">
         <v>55</v>
@@ -6217,48 +6256,48 @@
         <v>22</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="M71" s="0" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="N71" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O71" s="0" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="P71" s="0" t="s">
-        <v>143</v>
+        <v>223</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="B72" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>675</v>
+        <v>661</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>20</v>
+        <v>681</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>20</v>
+        <v>682</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="J72" s="0" t="s">
         <v>55</v>
@@ -6267,39 +6306,39 @@
         <v>22</v>
       </c>
       <c r="L72" s="0" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="M72" s="0" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="N72" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O72" s="0" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="P72" s="0" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B73" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>20</v>
+        <v>690</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="G73" s="0" t="s">
         <v>20</v>
@@ -6308,7 +6347,7 @@
         <v>20</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="J73" s="0" t="s">
         <v>55</v>
@@ -6317,48 +6356,48 @@
         <v>22</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="M73" s="0" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="N73" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O73" s="0" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="P73" s="0" t="s">
-        <v>188</v>
+        <v>153</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="B74" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="E74" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>695</v>
+        <v>20</v>
       </c>
       <c r="H74" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="J74" s="0" t="s">
         <v>55</v>
@@ -6367,48 +6406,48 @@
         <v>22</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="M74" s="0" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="N74" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O74" s="0" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="P74" s="0" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="B75" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>703</v>
+        <v>20</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>448</v>
+        <v>708</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>705</v>
+        <v>20</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="J75" s="0" t="s">
         <v>55</v>
@@ -6417,48 +6456,48 @@
         <v>22</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="M75" s="0" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="N75" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O75" s="0" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="P75" s="0" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="B76" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>701</v>
+        <v>714</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>20</v>
+        <v>716</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>20</v>
+        <v>717</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>20</v>
+        <v>448</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>20</v>
+        <v>718</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="J76" s="0" t="s">
         <v>55</v>
@@ -6467,36 +6506,36 @@
         <v>22</v>
       </c>
       <c r="L76" s="0" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="M76" s="0" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="N76" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O76" s="0" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="P76" s="0" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="B77" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>701</v>
+        <v>714</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>718</v>
+        <v>20</v>
       </c>
       <c r="F77" s="0" t="s">
         <v>20</v>
@@ -6508,7 +6547,7 @@
         <v>20</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="J77" s="0" t="s">
         <v>55</v>
@@ -6517,48 +6556,48 @@
         <v>22</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="M77" s="0" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="N77" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O77" s="0" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="P77" s="0" t="s">
-        <v>388</v>
+        <v>223</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="B78" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>724</v>
+        <v>714</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>727</v>
+        <v>20</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>728</v>
+        <v>20</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>729</v>
+        <v>20</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="J78" s="0" t="s">
         <v>55</v>
@@ -6567,16 +6606,16 @@
         <v>22</v>
       </c>
       <c r="L78" s="0" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="M78" s="0" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="N78" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O78" s="0" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="P78" s="0" t="s">
         <v>388</v>
@@ -6584,31 +6623,31 @@
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B79" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>728</v>
+        <v>741</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="J79" s="0" t="s">
         <v>55</v>
@@ -6617,48 +6656,48 @@
         <v>22</v>
       </c>
       <c r="L79" s="0" t="s">
-        <v>526</v>
+        <v>744</v>
       </c>
       <c r="M79" s="0" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="N79" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O79" s="0" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="P79" s="0" t="s">
-        <v>143</v>
+        <v>388</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B80" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>735</v>
+        <v>748</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>478</v>
+        <v>750</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="J80" s="0" t="s">
         <v>55</v>
@@ -6667,48 +6706,48 @@
         <v>22</v>
       </c>
       <c r="L80" s="0" t="s">
-        <v>749</v>
+        <v>538</v>
       </c>
       <c r="M80" s="0" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="N80" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O80" s="0" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="P80" s="0" t="s">
-        <v>223</v>
+        <v>143</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="B81" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>735</v>
+        <v>748</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>754</v>
+        <v>490</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="J81" s="0" t="s">
         <v>55</v>
@@ -6717,48 +6756,48 @@
         <v>22</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="M81" s="0" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="N81" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O81" s="0" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="P81" s="0" t="s">
-        <v>388</v>
+        <v>223</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="B82" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>763</v>
+        <v>748</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>20</v>
+        <v>769</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>590</v>
+        <v>770</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="J82" s="0" t="s">
         <v>55</v>
@@ -6767,48 +6806,48 @@
         <v>22</v>
       </c>
       <c r="L82" s="0" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="M82" s="0" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="N82" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O82" s="0" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="P82" s="0" t="s">
-        <v>143</v>
+        <v>388</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="B83" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>763</v>
+        <v>776</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>765</v>
+        <v>778</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="G83" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>774</v>
+        <v>602</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="J83" s="0" t="s">
         <v>55</v>
@@ -6817,48 +6856,48 @@
         <v>22</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="M83" s="0" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="N83" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O83" s="0" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="P83" s="0" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="B84" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="G84" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="J84" s="0" t="s">
         <v>55</v>
@@ -6867,16 +6906,16 @@
         <v>22</v>
       </c>
       <c r="L84" s="0" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="M84" s="0" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="N84" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O84" s="0" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="P84" s="0" t="s">
         <v>166</v>
@@ -6884,31 +6923,31 @@
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="B85" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>20</v>
+        <v>795</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="G85" s="0" t="s">
         <v>20</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="J85" s="0" t="s">
         <v>55</v>
@@ -6917,48 +6956,48 @@
         <v>22</v>
       </c>
       <c r="L85" s="0" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="M85" s="0" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="N85" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O85" s="0" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="P85" s="0" t="s">
-        <v>429</v>
+        <v>166</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="B86" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>801</v>
+        <v>20</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>728</v>
+        <v>20</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="J86" s="0" t="s">
         <v>55</v>
@@ -6967,48 +7006,48 @@
         <v>22</v>
       </c>
       <c r="L86" s="0" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="M86" s="0" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="N86" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O86" s="0" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="P86" s="0" t="s">
-        <v>166</v>
+        <v>429</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="B87" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>20</v>
+        <v>814</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>20</v>
+        <v>815</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>20</v>
+        <v>741</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>20</v>
+        <v>816</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="J87" s="0" t="s">
         <v>55</v>
@@ -7017,48 +7056,48 @@
         <v>22</v>
       </c>
       <c r="L87" s="0" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="M87" s="0" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="N87" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O87" s="0" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="P87" s="0" t="s">
-        <v>223</v>
+        <v>166</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="B88" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>818</v>
+        <v>20</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>819</v>
+        <v>20</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>448</v>
+        <v>20</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>820</v>
+        <v>20</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="J88" s="0" t="s">
         <v>55</v>
@@ -7067,48 +7106,48 @@
         <v>22</v>
       </c>
       <c r="L88" s="0" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="M88" s="0" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="N88" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O88" s="0" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="P88" s="0" t="s">
-        <v>388</v>
+        <v>223</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="B89" s="0" t="s">
         <v>443</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="G89" s="0" t="s">
         <v>448</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="J89" s="0" t="s">
         <v>55</v>
@@ -7117,16 +7156,16 @@
         <v>22</v>
       </c>
       <c r="L89" s="0" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="M89" s="0" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="N89" s="0" t="s">
         <v>22</v>
       </c>
       <c r="O89" s="0" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="P89" s="0" t="s">
         <v>388</v>
@@ -7134,51 +7173,101 @@
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>836</v>
+        <v>443</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>20</v>
+        <v>841</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>20</v>
+        <v>842</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>20</v>
+        <v>448</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>20</v>
+        <v>843</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="J90" s="0" t="s">
-        <v>840</v>
+        <v>55</v>
       </c>
       <c r="K90" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="L90" s="0" t="s">
+        <v>845</v>
+      </c>
+      <c r="M90" s="0" t="s">
+        <v>846</v>
+      </c>
+      <c r="N90" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="O90" s="0" t="s">
+        <v>847</v>
+      </c>
+      <c r="P90" s="0" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="0" t="s">
+        <v>848</v>
+      </c>
+      <c r="B91" s="0" t="s">
+        <v>849</v>
+      </c>
+      <c r="C91" s="0" t="s">
+        <v>850</v>
+      </c>
+      <c r="D91" s="0" t="s">
+        <v>851</v>
+      </c>
+      <c r="E91" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F91" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G91" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H91" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I91" s="0" t="s">
+        <v>852</v>
+      </c>
+      <c r="J91" s="0" t="s">
+        <v>853</v>
+      </c>
+      <c r="K91" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="L90" s="0" t="s">
-        <v>841</v>
-      </c>
-      <c r="M90" s="0" t="s">
-        <v>842</v>
-      </c>
-      <c r="N90" s="0" t="s">
-        <v>843</v>
-      </c>
-      <c r="O90" s="0" t="s">
-        <v>844</v>
-      </c>
-      <c r="P90" s="0" t="s">
+      <c r="L91" s="0" t="s">
+        <v>854</v>
+      </c>
+      <c r="M91" s="0" t="s">
+        <v>855</v>
+      </c>
+      <c r="N91" s="0" t="s">
+        <v>856</v>
+      </c>
+      <c r="O91" s="0" t="s">
+        <v>857</v>
+      </c>
+      <c r="P91" s="0" t="s">
         <v>239</v>
       </c>
     </row>
